--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215736</v>
+        <v>129215903</v>
       </c>
       <c r="B10" t="n">
-        <v>79654</v>
+        <v>88926</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,34 +1486,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434605</v>
+        <v>434350</v>
       </c>
       <c r="R10" t="n">
-        <v>6806750</v>
+        <v>6806600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,6 +1557,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1572,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215813</v>
+        <v>129215736</v>
       </c>
       <c r="B11" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434803</v>
+        <v>434605</v>
       </c>
       <c r="R11" t="n">
-        <v>6806683</v>
+        <v>6806750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1863,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129215903</v>
+        <v>129215795</v>
       </c>
       <c r="B14" t="n">
-        <v>88926</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,26 +1878,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1901,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434350</v>
+        <v>434758</v>
       </c>
       <c r="R14" t="n">
-        <v>6806600</v>
+        <v>6806435</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,7 +1954,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1964,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215795</v>
+        <v>129215813</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,42 +1983,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434758</v>
+        <v>434803</v>
       </c>
       <c r="R15" t="n">
-        <v>6806435</v>
+        <v>6806683</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,53 +2069,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129215766</v>
+        <v>129215893</v>
       </c>
       <c r="B16" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434601</v>
+        <v>434908</v>
       </c>
       <c r="R16" t="n">
-        <v>6806475</v>
+        <v>6806633</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129215757</v>
+        <v>129215890</v>
       </c>
       <c r="B17" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,21 +2177,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2209,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434905</v>
+        <v>434799</v>
       </c>
       <c r="R17" t="n">
-        <v>6806832</v>
+        <v>6806670</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,45 +2263,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129215893</v>
+        <v>129215766</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434908</v>
+        <v>434601</v>
       </c>
       <c r="R18" t="n">
-        <v>6806633</v>
+        <v>6806475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129215890</v>
+        <v>129215757</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434799</v>
+        <v>434905</v>
       </c>
       <c r="R19" t="n">
-        <v>6806670</v>
+        <v>6806832</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215737</v>
+        <v>129215859</v>
       </c>
       <c r="B20" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434585</v>
+        <v>434177</v>
       </c>
       <c r="R20" t="n">
-        <v>6806746</v>
+        <v>6806592</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215758</v>
+        <v>129215737</v>
       </c>
       <c r="B21" t="n">
-        <v>79625</v>
+        <v>79654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434928</v>
+        <v>434585</v>
       </c>
       <c r="R21" t="n">
-        <v>6806794</v>
+        <v>6806746</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215793</v>
+        <v>129215735</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>79654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2864,42 +2864,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434920</v>
+        <v>434571</v>
       </c>
       <c r="R24" t="n">
-        <v>6806792</v>
+        <v>6806718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2958,10 +2950,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215800</v>
+        <v>129215744</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2969,31 +2961,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3001,10 +2988,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434596</v>
+        <v>434950</v>
       </c>
       <c r="R25" t="n">
-        <v>6806728</v>
+        <v>6806749</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3045,6 +3032,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3063,10 +3051,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215735</v>
+        <v>129215878</v>
       </c>
       <c r="B26" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,34 +3062,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434571</v>
+        <v>434621</v>
       </c>
       <c r="R26" t="n">
-        <v>6806718</v>
+        <v>6806786</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3142,6 +3133,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3160,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215878</v>
+        <v>129215793</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3171,26 +3163,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3198,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434621</v>
+        <v>434920</v>
       </c>
       <c r="R27" t="n">
-        <v>6806786</v>
+        <v>6806792</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3242,7 +3239,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3261,10 +3257,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215859</v>
+        <v>129215800</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3272,34 +3268,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434177</v>
+        <v>434596</v>
       </c>
       <c r="R28" t="n">
-        <v>6806592</v>
+        <v>6806728</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3358,37 +3362,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215744</v>
+        <v>129215782</v>
       </c>
       <c r="B29" t="n">
-        <v>79654</v>
+        <v>56913</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3396,10 +3405,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434950</v>
+        <v>434568</v>
       </c>
       <c r="R29" t="n">
-        <v>6806749</v>
+        <v>6806730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,7 +3449,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3459,53 +3467,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215782</v>
+        <v>129215758</v>
       </c>
       <c r="B30" t="n">
-        <v>56913</v>
+        <v>79625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434568</v>
+        <v>434928</v>
       </c>
       <c r="R30" t="n">
-        <v>6806730</v>
+        <v>6806794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3564,42 +3564,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215780</v>
+        <v>129215881</v>
       </c>
       <c r="B31" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3607,10 +3602,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434449</v>
+        <v>434834</v>
       </c>
       <c r="R31" t="n">
-        <v>6806667</v>
+        <v>6806837</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3651,6 +3646,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3669,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215810</v>
+        <v>129215750</v>
       </c>
       <c r="B32" t="n">
-        <v>78793</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3680,21 +3676,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3704,10 +3700,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434908</v>
+        <v>434775</v>
       </c>
       <c r="R32" t="n">
-        <v>6806733</v>
+        <v>6806482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3766,37 +3762,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215881</v>
+        <v>129215780</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3804,10 +3805,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434834</v>
+        <v>434449</v>
       </c>
       <c r="R33" t="n">
-        <v>6806837</v>
+        <v>6806667</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,7 +3849,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129215750</v>
+        <v>129215810</v>
       </c>
       <c r="B34" t="n">
-        <v>79654</v>
+        <v>78793</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434775</v>
+        <v>434908</v>
       </c>
       <c r="R34" t="n">
-        <v>6806482</v>
+        <v>6806733</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129215756</v>
+        <v>129215822</v>
       </c>
       <c r="B35" t="n">
-        <v>79625</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3975,37 +3975,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434857</v>
+        <v>434936</v>
       </c>
       <c r="R35" t="n">
-        <v>6806824</v>
+        <v>6806756</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4046,7 +4043,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4065,10 +4061,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129215798</v>
+        <v>129215823</v>
       </c>
       <c r="B36" t="n">
-        <v>57720</v>
+        <v>78792</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4076,42 +4072,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434244</v>
+        <v>434906</v>
       </c>
       <c r="R36" t="n">
-        <v>6806571</v>
+        <v>6806734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4170,10 +4158,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129215822</v>
+        <v>129215902</v>
       </c>
       <c r="B37" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,34 +4169,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434936</v>
+        <v>434784</v>
       </c>
       <c r="R37" t="n">
-        <v>6806756</v>
+        <v>6806543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4243,12 +4234,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4267,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129215823</v>
+        <v>129215738</v>
       </c>
       <c r="B38" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,21 +4275,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4302,10 +4299,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434906</v>
+        <v>434764</v>
       </c>
       <c r="R38" t="n">
-        <v>6806734</v>
+        <v>6806804</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4364,7 +4361,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129215902</v>
+        <v>129215854</v>
       </c>
       <c r="B39" t="n">
         <v>79035</v>
@@ -4393,19 +4390,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434784</v>
+        <v>434268</v>
       </c>
       <c r="R39" t="n">
-        <v>6806543</v>
+        <v>6806557</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4440,18 +4434,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4470,10 +4458,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129215738</v>
+        <v>129215869</v>
       </c>
       <c r="B40" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4481,21 +4469,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4505,10 +4493,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434764</v>
+        <v>434432</v>
       </c>
       <c r="R40" t="n">
-        <v>6806804</v>
+        <v>6806606</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4567,10 +4555,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215809</v>
+        <v>129215756</v>
       </c>
       <c r="B41" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,34 +4566,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434843</v>
+        <v>434857</v>
       </c>
       <c r="R41" t="n">
-        <v>6806853</v>
+        <v>6806824</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,6 +4637,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4664,10 +4656,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215854</v>
+        <v>129215809</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>78793</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,21 +4667,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4699,10 +4691,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434268</v>
+        <v>434843</v>
       </c>
       <c r="R42" t="n">
-        <v>6806557</v>
+        <v>6806853</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4761,10 +4753,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215869</v>
+        <v>129215798</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,34 +4764,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434432</v>
+        <v>434244</v>
       </c>
       <c r="R43" t="n">
-        <v>6806606</v>
+        <v>6806571</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129215753</v>
+        <v>129215882</v>
       </c>
       <c r="B44" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,21 +4869,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434571</v>
+        <v>434851</v>
       </c>
       <c r="R44" t="n">
-        <v>6806718</v>
+        <v>6806867</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4955,7 +4955,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129215882</v>
+        <v>129215845</v>
       </c>
       <c r="B45" t="n">
         <v>79035</v>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434851</v>
+        <v>434585</v>
       </c>
       <c r="R45" t="n">
-        <v>6806867</v>
+        <v>6806500</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215845</v>
+        <v>129215799</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,34 +5063,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434585</v>
+        <v>434142</v>
       </c>
       <c r="R46" t="n">
-        <v>6806500</v>
+        <v>6806549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5149,10 +5157,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129215799</v>
+        <v>129215753</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>79625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5160,42 +5168,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434142</v>
+        <v>434571</v>
       </c>
       <c r="R47" t="n">
-        <v>6806549</v>
+        <v>6806718</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129215857</v>
+        <v>129215755</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434179</v>
+        <v>434812</v>
       </c>
       <c r="R48" t="n">
-        <v>6806557</v>
+        <v>6806771</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215755</v>
+        <v>129215760</v>
       </c>
       <c r="B49" t="n">
         <v>79625</v>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434812</v>
+        <v>434895</v>
       </c>
       <c r="R49" t="n">
-        <v>6806771</v>
+        <v>6806736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215760</v>
+        <v>129215808</v>
       </c>
       <c r="B50" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434895</v>
+        <v>434355</v>
       </c>
       <c r="R50" t="n">
-        <v>6806736</v>
+        <v>6806519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215808</v>
+        <v>129215857</v>
       </c>
       <c r="B51" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434355</v>
+        <v>434179</v>
       </c>
       <c r="R51" t="n">
-        <v>6806519</v>
+        <v>6806557</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215880</v>
+        <v>129215819</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6567,34 +6567,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434845</v>
+        <v>434773</v>
       </c>
       <c r="R61" t="n">
-        <v>6806812</v>
+        <v>6806803</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6635,6 +6638,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6653,10 +6657,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129215739</v>
+        <v>129215880</v>
       </c>
       <c r="B62" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6664,21 +6668,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6688,10 +6692,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434817</v>
+        <v>434845</v>
       </c>
       <c r="R62" t="n">
-        <v>6806766</v>
+        <v>6806812</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6750,10 +6754,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215824</v>
+        <v>129215739</v>
       </c>
       <c r="B63" t="n">
-        <v>78792</v>
+        <v>79654</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6761,21 +6765,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6785,10 +6789,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434922</v>
+        <v>434817</v>
       </c>
       <c r="R63" t="n">
-        <v>6806746</v>
+        <v>6806766</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6847,10 +6851,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215885</v>
+        <v>129215824</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6858,21 +6862,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6882,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434884</v>
+        <v>434922</v>
       </c>
       <c r="R64" t="n">
-        <v>6806816</v>
+        <v>6806746</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6944,10 +6948,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215743</v>
+        <v>129215885</v>
       </c>
       <c r="B65" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6955,21 +6959,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6979,10 +6983,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434922</v>
+        <v>434884</v>
       </c>
       <c r="R65" t="n">
-        <v>6806795</v>
+        <v>6806816</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7041,10 +7045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215862</v>
+        <v>129215743</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7052,21 +7056,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7076,10 +7080,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434270</v>
+        <v>434922</v>
       </c>
       <c r="R66" t="n">
-        <v>6806602</v>
+        <v>6806795</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7138,10 +7142,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129215819</v>
+        <v>129215862</v>
       </c>
       <c r="B67" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7149,37 +7153,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434773</v>
+        <v>434270</v>
       </c>
       <c r="R67" t="n">
-        <v>6806803</v>
+        <v>6806602</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7220,7 +7221,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7239,38 +7239,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215807</v>
+        <v>129215742</v>
       </c>
       <c r="B68" t="n">
-        <v>97536</v>
+        <v>79654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7278,10 +7277,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434541</v>
+        <v>434910</v>
       </c>
       <c r="R68" t="n">
-        <v>6806479</v>
+        <v>6806856</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7923,37 +7922,42 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215742</v>
+        <v>129215764</v>
       </c>
       <c r="B75" t="n">
-        <v>79654</v>
+        <v>56913</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -7961,10 +7965,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434910</v>
+        <v>434687</v>
       </c>
       <c r="R75" t="n">
-        <v>6806856</v>
+        <v>6806459</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,7 +8009,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8024,10 +8027,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215764</v>
+        <v>129215807</v>
       </c>
       <c r="B76" t="n">
-        <v>56913</v>
+        <v>97536</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8035,31 +8038,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8067,10 +8066,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434687</v>
+        <v>434541</v>
       </c>
       <c r="R76" t="n">
-        <v>6806459</v>
+        <v>6806479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8111,6 +8110,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8129,45 +8129,53 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215887</v>
+        <v>129215773</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434936</v>
+        <v>434241</v>
       </c>
       <c r="R77" t="n">
-        <v>6806726</v>
+        <v>6806606</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8226,10 +8234,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215858</v>
+        <v>129215805</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8237,34 +8245,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434135</v>
+        <v>434761</v>
       </c>
       <c r="R78" t="n">
-        <v>6806556</v>
+        <v>6806449</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8428,10 +8444,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215805</v>
+        <v>129215887</v>
       </c>
       <c r="B80" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8439,42 +8455,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434761</v>
+        <v>434936</v>
       </c>
       <c r="R80" t="n">
-        <v>6806449</v>
+        <v>6806726</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8533,53 +8541,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129215773</v>
+        <v>129215858</v>
       </c>
       <c r="B81" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434241</v>
+        <v>434135</v>
       </c>
       <c r="R81" t="n">
-        <v>6806606</v>
+        <v>6806556</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8638,53 +8638,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215771</v>
+        <v>129215886</v>
       </c>
       <c r="B82" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434229</v>
+        <v>434934</v>
       </c>
       <c r="R82" t="n">
-        <v>6806613</v>
+        <v>6806762</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8743,53 +8735,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215774</v>
+        <v>129215741</v>
       </c>
       <c r="B83" t="n">
-        <v>56913</v>
+        <v>79654</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434307</v>
+        <v>434844</v>
       </c>
       <c r="R83" t="n">
-        <v>6806608</v>
+        <v>6806852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8848,7 +8832,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215886</v>
+        <v>129215863</v>
       </c>
       <c r="B84" t="n">
         <v>79035</v>
@@ -8883,10 +8867,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434934</v>
+        <v>434279</v>
       </c>
       <c r="R84" t="n">
-        <v>6806762</v>
+        <v>6806587</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8945,10 +8929,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215741</v>
+        <v>129215853</v>
       </c>
       <c r="B85" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8956,21 +8940,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8980,10 +8964,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434844</v>
+        <v>434280</v>
       </c>
       <c r="R85" t="n">
-        <v>6806852</v>
+        <v>6806556</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9042,7 +9026,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215863</v>
+        <v>129215850</v>
       </c>
       <c r="B86" t="n">
         <v>79035</v>
@@ -9077,10 +9061,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434279</v>
+        <v>434376</v>
       </c>
       <c r="R86" t="n">
-        <v>6806587</v>
+        <v>6806560</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9139,7 +9123,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215853</v>
+        <v>129215843</v>
       </c>
       <c r="B87" t="n">
         <v>79035</v>
@@ -9174,10 +9158,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434280</v>
+        <v>434628</v>
       </c>
       <c r="R87" t="n">
-        <v>6806556</v>
+        <v>6806457</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9236,7 +9220,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215850</v>
+        <v>129215861</v>
       </c>
       <c r="B88" t="n">
         <v>79035</v>
@@ -9265,16 +9249,19 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434376</v>
+        <v>434259</v>
       </c>
       <c r="R88" t="n">
-        <v>6806560</v>
+        <v>6806607</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9315,6 +9302,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9333,10 +9321,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215843</v>
+        <v>129215804</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9344,34 +9332,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434628</v>
+        <v>434880</v>
       </c>
       <c r="R89" t="n">
-        <v>6806457</v>
+        <v>6806584</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9430,10 +9426,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215861</v>
+        <v>129215803</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9441,26 +9437,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9468,10 +9469,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434259</v>
+        <v>434895</v>
       </c>
       <c r="R90" t="n">
-        <v>6806607</v>
+        <v>6806664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9512,7 +9513,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9531,32 +9531,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215803</v>
+        <v>129215771</v>
       </c>
       <c r="B91" t="n">
-        <v>57720</v>
+        <v>56913</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9564,7 +9564,7 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434895</v>
+        <v>434229</v>
       </c>
       <c r="R91" t="n">
-        <v>6806664</v>
+        <v>6806613</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9741,32 +9741,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215804</v>
+        <v>129215787</v>
       </c>
       <c r="B93" t="n">
-        <v>57720</v>
+        <v>56913</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434880</v>
+        <v>434813</v>
       </c>
       <c r="R93" t="n">
-        <v>6806584</v>
+        <v>6806656</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,7 +9846,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215787</v>
+        <v>129215774</v>
       </c>
       <c r="B94" t="n">
         <v>56913</v>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434813</v>
+        <v>434307</v>
       </c>
       <c r="R94" t="n">
-        <v>6806656</v>
+        <v>6806608</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10157,10 +10157,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129215818</v>
+        <v>129215777</v>
       </c>
       <c r="B97" t="n">
-        <v>58093</v>
+        <v>56913</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10168,21 +10168,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10190,7 +10190,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434849</v>
+        <v>434432</v>
       </c>
       <c r="R97" t="n">
-        <v>6806700</v>
+        <v>6806670</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10262,10 +10262,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215777</v>
+        <v>129215818</v>
       </c>
       <c r="B98" t="n">
-        <v>56913</v>
+        <v>58093</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10273,21 +10273,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10295,7 +10295,7 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -10305,10 +10305,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434432</v>
+        <v>434849</v>
       </c>
       <c r="R98" t="n">
-        <v>6806670</v>
+        <v>6806700</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10367,10 +10367,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215883</v>
+        <v>129215759</v>
       </c>
       <c r="B99" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10378,37 +10378,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434920</v>
+        <v>434930</v>
       </c>
       <c r="R99" t="n">
-        <v>6806876</v>
+        <v>6806768</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10443,18 +10440,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10473,7 +10464,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215860</v>
+        <v>129215883</v>
       </c>
       <c r="B100" t="n">
         <v>79035</v>
@@ -10502,16 +10493,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434241</v>
+        <v>434920</v>
       </c>
       <c r="R100" t="n">
-        <v>6806618</v>
+        <v>6806876</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,12 +10540,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10570,10 +10570,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215759</v>
+        <v>129215860</v>
       </c>
       <c r="B101" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10581,21 +10581,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10605,10 +10605,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434930</v>
+        <v>434241</v>
       </c>
       <c r="R101" t="n">
-        <v>6806768</v>
+        <v>6806618</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215849</v>
+        <v>129215794</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>57883</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11276,34 +11276,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434437</v>
+        <v>434852</v>
       </c>
       <c r="R108" t="n">
-        <v>6806501</v>
+        <v>6806551</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11362,7 +11370,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215848</v>
+        <v>129215849</v>
       </c>
       <c r="B109" t="n">
         <v>79035</v>
@@ -11397,10 +11405,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434473</v>
+        <v>434437</v>
       </c>
       <c r="R109" t="n">
-        <v>6806453</v>
+        <v>6806501</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11459,7 +11467,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215879</v>
+        <v>129215848</v>
       </c>
       <c r="B110" t="n">
         <v>79035</v>
@@ -11494,10 +11502,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434627</v>
+        <v>434473</v>
       </c>
       <c r="R110" t="n">
-        <v>6806787</v>
+        <v>6806453</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11556,7 +11564,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215892</v>
+        <v>129215879</v>
       </c>
       <c r="B111" t="n">
         <v>79035</v>
@@ -11591,10 +11599,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434884</v>
+        <v>434627</v>
       </c>
       <c r="R111" t="n">
-        <v>6806606</v>
+        <v>6806787</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11653,53 +11661,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215765</v>
+        <v>129215892</v>
       </c>
       <c r="B112" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434630</v>
+        <v>434884</v>
       </c>
       <c r="R112" t="n">
-        <v>6806465</v>
+        <v>6806606</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11758,32 +11758,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215794</v>
+        <v>129215765</v>
       </c>
       <c r="B113" t="n">
-        <v>57883</v>
+        <v>56913</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11791,7 +11791,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -11801,10 +11801,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434852</v>
+        <v>434630</v>
       </c>
       <c r="R113" t="n">
-        <v>6806551</v>
+        <v>6806465</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215812</v>
+        <v>129215900</v>
       </c>
       <c r="B115" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434922</v>
+        <v>434775</v>
       </c>
       <c r="R115" t="n">
-        <v>6806746</v>
+        <v>6806423</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12065,7 +12065,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215900</v>
+        <v>129215867</v>
       </c>
       <c r="B116" t="n">
         <v>79035</v>
@@ -12100,10 +12100,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434775</v>
+        <v>434375</v>
       </c>
       <c r="R116" t="n">
-        <v>6806423</v>
+        <v>6806574</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12162,10 +12162,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215867</v>
+        <v>129215734</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12173,21 +12173,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434375</v>
+        <v>434546</v>
       </c>
       <c r="R117" t="n">
-        <v>6806574</v>
+        <v>6806737</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215734</v>
+        <v>129215844</v>
       </c>
       <c r="B118" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12270,21 +12270,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434546</v>
+        <v>434623</v>
       </c>
       <c r="R118" t="n">
-        <v>6806737</v>
+        <v>6806466</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12356,7 +12356,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215844</v>
+        <v>129215868</v>
       </c>
       <c r="B119" t="n">
         <v>79035</v>
@@ -12391,10 +12391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434623</v>
+        <v>434415</v>
       </c>
       <c r="R119" t="n">
-        <v>6806466</v>
+        <v>6806576</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12453,10 +12453,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215754</v>
+        <v>129215797</v>
       </c>
       <c r="B120" t="n">
-        <v>79625</v>
+        <v>57720</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12464,34 +12464,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434774</v>
+        <v>434602</v>
       </c>
       <c r="R120" t="n">
-        <v>6806803</v>
+        <v>6806495</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12550,10 +12558,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215868</v>
+        <v>129215796</v>
       </c>
       <c r="B121" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12561,34 +12569,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434415</v>
+        <v>434635</v>
       </c>
       <c r="R121" t="n">
-        <v>6806576</v>
+        <v>6806453</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12647,10 +12663,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215796</v>
+        <v>129215812</v>
       </c>
       <c r="B122" t="n">
-        <v>57720</v>
+        <v>78793</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12658,42 +12674,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434635</v>
+        <v>434922</v>
       </c>
       <c r="R122" t="n">
-        <v>6806453</v>
+        <v>6806746</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12752,10 +12760,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215797</v>
+        <v>129215754</v>
       </c>
       <c r="B123" t="n">
-        <v>57720</v>
+        <v>79625</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12763,42 +12771,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434602</v>
+        <v>434774</v>
       </c>
       <c r="R123" t="n">
-        <v>6806495</v>
+        <v>6806803</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129215752</v>
+        <v>129215889</v>
       </c>
       <c r="B125" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,21 +12965,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434263</v>
+        <v>434813</v>
       </c>
       <c r="R125" t="n">
-        <v>6806561</v>
+        <v>6806692</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13148,10 +13148,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129215751</v>
+        <v>129215745</v>
       </c>
       <c r="B127" t="n">
-        <v>79625</v>
+        <v>79654</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13159,21 +13159,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434673</v>
+        <v>434934</v>
       </c>
       <c r="R127" t="n">
-        <v>6806460</v>
+        <v>6806753</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,7 +13245,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129215889</v>
+        <v>129215871</v>
       </c>
       <c r="B128" t="n">
         <v>79035</v>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434813</v>
+        <v>434443</v>
       </c>
       <c r="R128" t="n">
-        <v>6806692</v>
+        <v>6806595</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129215745</v>
+        <v>129215752</v>
       </c>
       <c r="B129" t="n">
-        <v>79654</v>
+        <v>79625</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13353,21 +13353,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>434934</v>
+        <v>434263</v>
       </c>
       <c r="R129" t="n">
-        <v>6806753</v>
+        <v>6806561</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129215871</v>
+        <v>129215751</v>
       </c>
       <c r="B130" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,21 +13450,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434443</v>
+        <v>434673</v>
       </c>
       <c r="R130" t="n">
-        <v>6806595</v>
+        <v>6806460</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215876</v>
+        <v>129215864</v>
       </c>
       <c r="B2" t="n">
         <v>79035</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434591</v>
+        <v>434319</v>
       </c>
       <c r="R2" t="n">
-        <v>6806739</v>
+        <v>6806589</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215864</v>
+        <v>129215761</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434319</v>
+        <v>434924</v>
       </c>
       <c r="R3" t="n">
-        <v>6806589</v>
+        <v>6806749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +869,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215761</v>
+        <v>129215767</v>
       </c>
       <c r="B4" t="n">
-        <v>79625</v>
+        <v>56913</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434924</v>
+        <v>434546</v>
       </c>
       <c r="R4" t="n">
-        <v>6806749</v>
+        <v>6806482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +974,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215767</v>
+        <v>129215775</v>
       </c>
       <c r="B5" t="n">
         <v>56913</v>
@@ -1009,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434546</v>
+        <v>434334</v>
       </c>
       <c r="R5" t="n">
-        <v>6806482</v>
+        <v>6806593</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215775</v>
+        <v>129215770</v>
       </c>
       <c r="B6" t="n">
         <v>56913</v>
@@ -1114,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434334</v>
+        <v>434136</v>
       </c>
       <c r="R6" t="n">
-        <v>6806593</v>
+        <v>6806558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,53 +1184,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215770</v>
+        <v>129215876</v>
       </c>
       <c r="B7" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434136</v>
+        <v>434591</v>
       </c>
       <c r="R7" t="n">
-        <v>6806558</v>
+        <v>6806739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215859</v>
+        <v>129215737</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434177</v>
+        <v>434585</v>
       </c>
       <c r="R20" t="n">
-        <v>6806592</v>
+        <v>6806746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215737</v>
+        <v>129215877</v>
       </c>
       <c r="B21" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,21 +2573,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434585</v>
+        <v>434596</v>
       </c>
       <c r="R21" t="n">
-        <v>6806746</v>
+        <v>6806729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215877</v>
+        <v>129215856</v>
       </c>
       <c r="B22" t="n">
         <v>79035</v>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434596</v>
+        <v>434194</v>
       </c>
       <c r="R22" t="n">
-        <v>6806729</v>
+        <v>6806560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215856</v>
+        <v>129215735</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434194</v>
+        <v>434571</v>
       </c>
       <c r="R23" t="n">
-        <v>6806560</v>
+        <v>6806718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215735</v>
+        <v>129215744</v>
       </c>
       <c r="B24" t="n">
         <v>79654</v>
@@ -2882,16 +2882,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434571</v>
+        <v>434950</v>
       </c>
       <c r="R24" t="n">
-        <v>6806718</v>
+        <v>6806749</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2932,6 +2935,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2950,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215744</v>
+        <v>129215878</v>
       </c>
       <c r="B25" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,21 +2965,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2988,10 +2992,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434950</v>
+        <v>434621</v>
       </c>
       <c r="R25" t="n">
-        <v>6806749</v>
+        <v>6806786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,37 +3055,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215878</v>
+        <v>129215782</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3089,10 +3098,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434621</v>
+        <v>434568</v>
       </c>
       <c r="R26" t="n">
-        <v>6806786</v>
+        <v>6806730</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3133,7 +3142,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3257,10 +3265,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215800</v>
+        <v>129215859</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3268,42 +3276,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434596</v>
+        <v>434177</v>
       </c>
       <c r="R28" t="n">
-        <v>6806728</v>
+        <v>6806592</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3362,32 +3362,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215782</v>
+        <v>129215800</v>
       </c>
       <c r="B29" t="n">
-        <v>56913</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3395,7 +3395,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434568</v>
+        <v>434596</v>
       </c>
       <c r="R29" t="n">
-        <v>6806730</v>
+        <v>6806728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3564,37 +3564,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215881</v>
+        <v>129215780</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3602,10 +3607,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434834</v>
+        <v>434449</v>
       </c>
       <c r="R31" t="n">
-        <v>6806837</v>
+        <v>6806667</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3646,7 +3651,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3665,10 +3669,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215750</v>
+        <v>129215881</v>
       </c>
       <c r="B32" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,34 +3680,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434775</v>
+        <v>434834</v>
       </c>
       <c r="R32" t="n">
-        <v>6806482</v>
+        <v>6806837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3744,6 +3751,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3762,53 +3770,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215780</v>
+        <v>129215750</v>
       </c>
       <c r="B33" t="n">
-        <v>56913</v>
+        <v>79654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434449</v>
+        <v>434775</v>
       </c>
       <c r="R33" t="n">
-        <v>6806667</v>
+        <v>6806482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129215882</v>
+        <v>129215799</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,34 +4869,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434851</v>
+        <v>434142</v>
       </c>
       <c r="R44" t="n">
-        <v>6806867</v>
+        <v>6806549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4955,10 +4963,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129215845</v>
+        <v>129215753</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4966,21 +4974,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4990,10 +4998,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434585</v>
+        <v>434571</v>
       </c>
       <c r="R45" t="n">
-        <v>6806500</v>
+        <v>6806718</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5052,10 +5060,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215799</v>
+        <v>129215882</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,42 +5071,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434142</v>
+        <v>434851</v>
       </c>
       <c r="R46" t="n">
-        <v>6806549</v>
+        <v>6806867</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129215753</v>
+        <v>129215845</v>
       </c>
       <c r="B47" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434571</v>
+        <v>434585</v>
       </c>
       <c r="R47" t="n">
-        <v>6806718</v>
+        <v>6806500</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7239,37 +7239,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215742</v>
+        <v>129215807</v>
       </c>
       <c r="B68" t="n">
-        <v>79654</v>
+        <v>97536</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7277,10 +7278,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434910</v>
+        <v>434541</v>
       </c>
       <c r="R68" t="n">
-        <v>6806856</v>
+        <v>6806479</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7340,10 +7341,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129215891</v>
+        <v>129215742</v>
       </c>
       <c r="B69" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7351,34 +7352,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434812</v>
+        <v>434910</v>
       </c>
       <c r="R69" t="n">
-        <v>6806610</v>
+        <v>6806856</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7419,6 +7423,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7437,7 +7442,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129215898</v>
+        <v>129215891</v>
       </c>
       <c r="B70" t="n">
         <v>79035</v>
@@ -7472,10 +7477,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434759</v>
+        <v>434812</v>
       </c>
       <c r="R70" t="n">
-        <v>6806455</v>
+        <v>6806610</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,10 +7539,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215821</v>
+        <v>129215898</v>
       </c>
       <c r="B71" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,21 +7550,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7569,10 +7574,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434913</v>
+        <v>434759</v>
       </c>
       <c r="R71" t="n">
-        <v>6806785</v>
+        <v>6806455</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7631,10 +7636,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215895</v>
+        <v>129215821</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,21 +7647,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7666,10 +7671,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434858</v>
+        <v>434913</v>
       </c>
       <c r="R72" t="n">
-        <v>6806562</v>
+        <v>6806785</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7728,7 +7733,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129215899</v>
+        <v>129215895</v>
       </c>
       <c r="B73" t="n">
         <v>79035</v>
@@ -7763,10 +7768,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434763</v>
+        <v>434858</v>
       </c>
       <c r="R73" t="n">
-        <v>6806436</v>
+        <v>6806562</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7825,7 +7830,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215851</v>
+        <v>129215899</v>
       </c>
       <c r="B74" t="n">
         <v>79035</v>
@@ -7860,10 +7865,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434362</v>
+        <v>434763</v>
       </c>
       <c r="R74" t="n">
-        <v>6806519</v>
+        <v>6806436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7922,53 +7927,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215764</v>
+        <v>129215851</v>
       </c>
       <c r="B75" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434687</v>
+        <v>434362</v>
       </c>
       <c r="R75" t="n">
-        <v>6806459</v>
+        <v>6806519</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8027,10 +8024,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215807</v>
+        <v>129215764</v>
       </c>
       <c r="B76" t="n">
-        <v>97536</v>
+        <v>56913</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8038,27 +8035,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8066,10 +8067,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434541</v>
+        <v>434687</v>
       </c>
       <c r="R76" t="n">
-        <v>6806479</v>
+        <v>6806459</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8110,7 +8111,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8129,53 +8129,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215773</v>
+        <v>129215887</v>
       </c>
       <c r="B77" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434241</v>
+        <v>434936</v>
       </c>
       <c r="R77" t="n">
-        <v>6806606</v>
+        <v>6806726</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8234,10 +8226,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215805</v>
+        <v>129215858</v>
       </c>
       <c r="B78" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8245,42 +8237,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434761</v>
+        <v>434135</v>
       </c>
       <c r="R78" t="n">
-        <v>6806449</v>
+        <v>6806556</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8339,7 +8323,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215801</v>
+        <v>129215805</v>
       </c>
       <c r="B79" t="n">
         <v>57720</v>
@@ -8372,7 +8356,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8382,10 +8366,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434883</v>
+        <v>434761</v>
       </c>
       <c r="R79" t="n">
-        <v>6806894</v>
+        <v>6806449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8444,10 +8428,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215887</v>
+        <v>129215801</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8455,34 +8439,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434936</v>
+        <v>434883</v>
       </c>
       <c r="R80" t="n">
-        <v>6806726</v>
+        <v>6806894</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8541,45 +8533,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129215858</v>
+        <v>129215773</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434135</v>
+        <v>434241</v>
       </c>
       <c r="R81" t="n">
-        <v>6806556</v>
+        <v>6806606</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8638,45 +8638,53 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215886</v>
+        <v>129215771</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434934</v>
+        <v>434229</v>
       </c>
       <c r="R82" t="n">
-        <v>6806762</v>
+        <v>6806613</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8735,45 +8743,53 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215741</v>
+        <v>129215768</v>
       </c>
       <c r="B83" t="n">
-        <v>79654</v>
+        <v>56913</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434844</v>
+        <v>434422</v>
       </c>
       <c r="R83" t="n">
-        <v>6806852</v>
+        <v>6806522</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,45 +8848,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215863</v>
+        <v>129215787</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434279</v>
+        <v>434813</v>
       </c>
       <c r="R84" t="n">
-        <v>6806587</v>
+        <v>6806656</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8929,45 +8953,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215853</v>
+        <v>129215774</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434280</v>
+        <v>434307</v>
       </c>
       <c r="R85" t="n">
-        <v>6806556</v>
+        <v>6806608</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9026,7 +9058,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215850</v>
+        <v>129215886</v>
       </c>
       <c r="B86" t="n">
         <v>79035</v>
@@ -9061,10 +9093,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434376</v>
+        <v>434934</v>
       </c>
       <c r="R86" t="n">
-        <v>6806560</v>
+        <v>6806762</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9123,10 +9155,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215843</v>
+        <v>129215741</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9134,21 +9166,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9158,10 +9190,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434628</v>
+        <v>434844</v>
       </c>
       <c r="R87" t="n">
-        <v>6806457</v>
+        <v>6806852</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9220,7 +9252,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215861</v>
+        <v>129215863</v>
       </c>
       <c r="B88" t="n">
         <v>79035</v>
@@ -9249,19 +9281,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434259</v>
+        <v>434279</v>
       </c>
       <c r="R88" t="n">
-        <v>6806607</v>
+        <v>6806587</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9302,7 +9331,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9321,10 +9349,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215804</v>
+        <v>129215853</v>
       </c>
       <c r="B89" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9332,42 +9360,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434880</v>
+        <v>434280</v>
       </c>
       <c r="R89" t="n">
-        <v>6806584</v>
+        <v>6806556</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9426,10 +9446,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215803</v>
+        <v>129215850</v>
       </c>
       <c r="B90" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9437,42 +9457,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434895</v>
+        <v>434376</v>
       </c>
       <c r="R90" t="n">
-        <v>6806664</v>
+        <v>6806560</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9531,53 +9543,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215771</v>
+        <v>129215843</v>
       </c>
       <c r="B91" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434229</v>
+        <v>434628</v>
       </c>
       <c r="R91" t="n">
-        <v>6806613</v>
+        <v>6806457</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9636,42 +9640,37 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215768</v>
+        <v>129215861</v>
       </c>
       <c r="B92" t="n">
-        <v>56913</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9679,10 +9678,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434422</v>
+        <v>434259</v>
       </c>
       <c r="R92" t="n">
-        <v>6806522</v>
+        <v>6806607</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,6 +9722,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9741,32 +9741,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215787</v>
+        <v>129215804</v>
       </c>
       <c r="B93" t="n">
-        <v>56913</v>
+        <v>57720</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434813</v>
+        <v>434880</v>
       </c>
       <c r="R93" t="n">
-        <v>6806656</v>
+        <v>6806584</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,32 +9846,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215774</v>
+        <v>129215803</v>
       </c>
       <c r="B94" t="n">
-        <v>56913</v>
+        <v>57720</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9879,7 +9879,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434307</v>
+        <v>434895</v>
       </c>
       <c r="R94" t="n">
-        <v>6806608</v>
+        <v>6806664</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10262,42 +10262,37 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215818</v>
+        <v>129215883</v>
       </c>
       <c r="B98" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10305,10 +10300,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434849</v>
+        <v>434920</v>
       </c>
       <c r="R98" t="n">
-        <v>6806700</v>
+        <v>6806876</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10343,12 +10338,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10367,10 +10368,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215759</v>
+        <v>129215860</v>
       </c>
       <c r="B99" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10378,21 +10379,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10402,10 +10403,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434930</v>
+        <v>434241</v>
       </c>
       <c r="R99" t="n">
-        <v>6806768</v>
+        <v>6806618</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10464,7 +10465,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215883</v>
+        <v>129215865</v>
       </c>
       <c r="B100" t="n">
         <v>79035</v>
@@ -10493,19 +10494,16 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434920</v>
+        <v>434358</v>
       </c>
       <c r="R100" t="n">
-        <v>6806876</v>
+        <v>6806608</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10540,18 +10538,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10570,10 +10562,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215860</v>
+        <v>129215759</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10581,21 +10573,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10605,10 +10597,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434241</v>
+        <v>434930</v>
       </c>
       <c r="R101" t="n">
-        <v>6806618</v>
+        <v>6806768</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10667,45 +10659,53 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215865</v>
+        <v>129215818</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>58093</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434358</v>
+        <v>434849</v>
       </c>
       <c r="R102" t="n">
-        <v>6806608</v>
+        <v>6806700</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215794</v>
+        <v>129215849</v>
       </c>
       <c r="B108" t="n">
-        <v>57883</v>
+        <v>79035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11276,42 +11276,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434852</v>
+        <v>434437</v>
       </c>
       <c r="R108" t="n">
-        <v>6806551</v>
+        <v>6806501</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11370,7 +11362,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215849</v>
+        <v>129215848</v>
       </c>
       <c r="B109" t="n">
         <v>79035</v>
@@ -11405,10 +11397,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434437</v>
+        <v>434473</v>
       </c>
       <c r="R109" t="n">
-        <v>6806501</v>
+        <v>6806453</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11467,7 +11459,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215848</v>
+        <v>129215879</v>
       </c>
       <c r="B110" t="n">
         <v>79035</v>
@@ -11502,10 +11494,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434473</v>
+        <v>434627</v>
       </c>
       <c r="R110" t="n">
-        <v>6806453</v>
+        <v>6806787</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11564,7 +11556,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215879</v>
+        <v>129215892</v>
       </c>
       <c r="B111" t="n">
         <v>79035</v>
@@ -11599,10 +11591,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434627</v>
+        <v>434884</v>
       </c>
       <c r="R111" t="n">
-        <v>6806787</v>
+        <v>6806606</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11661,45 +11653,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215892</v>
+        <v>129215765</v>
       </c>
       <c r="B112" t="n">
-        <v>79035</v>
+        <v>56913</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434884</v>
+        <v>434630</v>
       </c>
       <c r="R112" t="n">
-        <v>6806606</v>
+        <v>6806465</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11758,7 +11758,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215765</v>
+        <v>129215769</v>
       </c>
       <c r="B113" t="n">
         <v>56913</v>
@@ -11801,10 +11801,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434630</v>
+        <v>434382</v>
       </c>
       <c r="R113" t="n">
-        <v>6806465</v>
+        <v>6806548</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11863,32 +11863,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215769</v>
+        <v>129215794</v>
       </c>
       <c r="B114" t="n">
-        <v>56913</v>
+        <v>57883</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11896,7 +11896,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434382</v>
+        <v>434852</v>
       </c>
       <c r="R114" t="n">
-        <v>6806548</v>
+        <v>6806551</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215864</v>
+        <v>129215876</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434319</v>
+        <v>434591</v>
       </c>
       <c r="R2" t="n">
-        <v>6806589</v>
+        <v>6806739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215761</v>
+        <v>129215864</v>
       </c>
       <c r="B3" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434924</v>
+        <v>434319</v>
       </c>
       <c r="R3" t="n">
-        <v>6806749</v>
+        <v>6806589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129215767</v>
       </c>
       <c r="B4" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129215775</v>
       </c>
       <c r="B5" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>129215770</v>
       </c>
       <c r="B6" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215876</v>
+        <v>129215761</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434591</v>
+        <v>434924</v>
       </c>
       <c r="R7" t="n">
-        <v>6806739</v>
+        <v>6806749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>129215846</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129215888</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215903</v>
+        <v>129215736</v>
       </c>
       <c r="B10" t="n">
-        <v>88926</v>
+        <v>79658</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,37 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434350</v>
+        <v>434605</v>
       </c>
       <c r="R10" t="n">
-        <v>6806600</v>
+        <v>6806750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1554,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1576,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215736</v>
+        <v>129215847</v>
       </c>
       <c r="B11" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,21 +1583,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434605</v>
+        <v>434523</v>
       </c>
       <c r="R11" t="n">
-        <v>6806750</v>
+        <v>6806508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215847</v>
+        <v>129215875</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1708,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434523</v>
+        <v>434516</v>
       </c>
       <c r="R12" t="n">
-        <v>6806508</v>
+        <v>6806695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,10 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215875</v>
+        <v>129215903</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>88930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,34 +1777,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434516</v>
+        <v>434350</v>
       </c>
       <c r="R13" t="n">
-        <v>6806695</v>
+        <v>6806600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,6 +1848,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>129215795</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>129215813</v>
       </c>
       <c r="B15" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>129215893</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>129215890</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>129215766</v>
       </c>
       <c r="B18" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>129215757</v>
       </c>
       <c r="B19" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215737</v>
+        <v>129215800</v>
       </c>
       <c r="B20" t="n">
-        <v>79654</v>
+        <v>57722</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,34 +2476,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434585</v>
+        <v>434596</v>
       </c>
       <c r="R20" t="n">
-        <v>6806746</v>
+        <v>6806728</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,10 +2570,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215877</v>
+        <v>129215758</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,21 +2581,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2597,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434596</v>
+        <v>434928</v>
       </c>
       <c r="R21" t="n">
-        <v>6806729</v>
+        <v>6806794</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,10 +2667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215856</v>
+        <v>129215737</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2678,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2702,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434194</v>
+        <v>434585</v>
       </c>
       <c r="R22" t="n">
-        <v>6806560</v>
+        <v>6806746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2764,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215735</v>
+        <v>129215877</v>
       </c>
       <c r="B23" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2775,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2799,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434571</v>
+        <v>434596</v>
       </c>
       <c r="R23" t="n">
-        <v>6806718</v>
+        <v>6806729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,10 +2861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215744</v>
+        <v>129215856</v>
       </c>
       <c r="B24" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2864,37 +2872,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434950</v>
+        <v>434194</v>
       </c>
       <c r="R24" t="n">
-        <v>6806749</v>
+        <v>6806560</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,7 +2940,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2954,10 +2958,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215878</v>
+        <v>129215735</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2965,37 +2969,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434621</v>
+        <v>434571</v>
       </c>
       <c r="R25" t="n">
-        <v>6806786</v>
+        <v>6806718</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3036,7 +3037,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3055,42 +3055,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215782</v>
+        <v>129215744</v>
       </c>
       <c r="B26" t="n">
-        <v>56913</v>
+        <v>79658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3098,10 +3093,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434568</v>
+        <v>434950</v>
       </c>
       <c r="R26" t="n">
-        <v>6806730</v>
+        <v>6806749</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3142,6 +3137,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3160,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215793</v>
+        <v>129215878</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3171,31 +3167,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3203,10 +3194,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434920</v>
+        <v>434621</v>
       </c>
       <c r="R27" t="n">
-        <v>6806792</v>
+        <v>6806786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3247,6 +3238,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3268,7 +3260,7 @@
         <v>129215859</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3362,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215800</v>
+        <v>129215782</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>56915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3395,7 +3387,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3405,10 +3397,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434596</v>
+        <v>434568</v>
       </c>
       <c r="R29" t="n">
-        <v>6806728</v>
+        <v>6806730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3467,10 +3459,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215758</v>
+        <v>129215793</v>
       </c>
       <c r="B30" t="n">
-        <v>79625</v>
+        <v>57885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3478,34 +3470,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434928</v>
+        <v>434920</v>
       </c>
       <c r="R30" t="n">
-        <v>6806794</v>
+        <v>6806792</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3564,42 +3564,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215780</v>
+        <v>129215881</v>
       </c>
       <c r="B31" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3607,10 +3602,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434449</v>
+        <v>434834</v>
       </c>
       <c r="R31" t="n">
-        <v>6806667</v>
+        <v>6806837</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3651,6 +3646,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3669,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215881</v>
+        <v>129215750</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3680,37 +3676,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434834</v>
+        <v>434775</v>
       </c>
       <c r="R32" t="n">
-        <v>6806837</v>
+        <v>6806482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,7 +3744,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3770,45 +3762,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215750</v>
+        <v>129215780</v>
       </c>
       <c r="B33" t="n">
-        <v>79654</v>
+        <v>56915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434775</v>
+        <v>434449</v>
       </c>
       <c r="R33" t="n">
-        <v>6806482</v>
+        <v>6806667</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3870,7 +3870,7 @@
         <v>129215810</v>
       </c>
       <c r="B34" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>129215822</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>129215823</v>
       </c>
       <c r="B36" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>129215902</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>129215738</v>
       </c>
       <c r="B38" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>129215854</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>129215869</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215756</v>
+        <v>129215798</v>
       </c>
       <c r="B41" t="n">
-        <v>79625</v>
+        <v>57722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4566,26 +4566,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4593,10 +4598,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434857</v>
+        <v>434244</v>
       </c>
       <c r="R41" t="n">
-        <v>6806824</v>
+        <v>6806571</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4637,7 +4642,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4656,10 +4660,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215809</v>
+        <v>129215756</v>
       </c>
       <c r="B42" t="n">
-        <v>78793</v>
+        <v>79629</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4667,34 +4671,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434843</v>
+        <v>434857</v>
       </c>
       <c r="R42" t="n">
-        <v>6806853</v>
+        <v>6806824</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4735,6 +4742,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4753,10 +4761,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215798</v>
+        <v>129215809</v>
       </c>
       <c r="B43" t="n">
-        <v>57720</v>
+        <v>78797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4764,42 +4772,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434244</v>
+        <v>434843</v>
       </c>
       <c r="R43" t="n">
-        <v>6806571</v>
+        <v>6806853</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129215799</v>
+        <v>129215882</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,42 +4869,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434142</v>
+        <v>434851</v>
       </c>
       <c r="R44" t="n">
-        <v>6806549</v>
+        <v>6806867</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,10 +4955,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129215753</v>
+        <v>129215845</v>
       </c>
       <c r="B45" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4974,21 +4966,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4998,10 +4990,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434571</v>
+        <v>434585</v>
       </c>
       <c r="R45" t="n">
-        <v>6806718</v>
+        <v>6806500</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5060,10 +5052,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215882</v>
+        <v>129215799</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5071,34 +5063,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434851</v>
+        <v>434142</v>
       </c>
       <c r="R46" t="n">
-        <v>6806867</v>
+        <v>6806549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5157,10 +5157,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129215845</v>
+        <v>129215753</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5168,21 +5168,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434585</v>
+        <v>434571</v>
       </c>
       <c r="R47" t="n">
-        <v>6806500</v>
+        <v>6806718</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129215755</v>
+        <v>129215857</v>
       </c>
       <c r="B48" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434812</v>
+        <v>434179</v>
       </c>
       <c r="R48" t="n">
-        <v>6806771</v>
+        <v>6806557</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215760</v>
+        <v>129215904</v>
       </c>
       <c r="B49" t="n">
-        <v>79625</v>
+        <v>79658</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434895</v>
+        <v>434857</v>
       </c>
       <c r="R49" t="n">
-        <v>6806736</v>
+        <v>6806833</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,45 +5448,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215808</v>
+        <v>129215790</v>
       </c>
       <c r="B50" t="n">
-        <v>78793</v>
+        <v>56915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434355</v>
+        <v>434809</v>
       </c>
       <c r="R50" t="n">
-        <v>6806519</v>
+        <v>6806535</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5545,45 +5553,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215857</v>
+        <v>129215786</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434179</v>
+        <v>434883</v>
       </c>
       <c r="R51" t="n">
-        <v>6806557</v>
+        <v>6806675</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5642,10 +5658,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215904</v>
+        <v>129215755</v>
       </c>
       <c r="B52" t="n">
-        <v>79654</v>
+        <v>79629</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5653,21 +5669,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5677,10 +5693,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434857</v>
+        <v>434812</v>
       </c>
       <c r="R52" t="n">
-        <v>6806833</v>
+        <v>6806771</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5739,53 +5755,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215790</v>
+        <v>129215760</v>
       </c>
       <c r="B53" t="n">
-        <v>56913</v>
+        <v>79629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434809</v>
+        <v>434895</v>
       </c>
       <c r="R53" t="n">
-        <v>6806535</v>
+        <v>6806736</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5844,53 +5852,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129215786</v>
+        <v>129215808</v>
       </c>
       <c r="B54" t="n">
-        <v>56913</v>
+        <v>78797</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434883</v>
+        <v>434355</v>
       </c>
       <c r="R54" t="n">
-        <v>6806675</v>
+        <v>6806519</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5952,7 +5952,7 @@
         <v>129215841</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>129215874</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>129215896</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>129215781</v>
       </c>
       <c r="B58" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>129215779</v>
       </c>
       <c r="B59" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>129215783</v>
       </c>
       <c r="B60" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>129215819</v>
       </c>
       <c r="B61" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>129215880</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>129215739</v>
       </c>
       <c r="B63" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>129215824</v>
       </c>
       <c r="B64" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>129215885</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>129215743</v>
       </c>
       <c r="B66" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>129215862</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7239,38 +7239,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215807</v>
+        <v>129215742</v>
       </c>
       <c r="B68" t="n">
-        <v>97536</v>
+        <v>79658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7278,10 +7277,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434541</v>
+        <v>434910</v>
       </c>
       <c r="R68" t="n">
-        <v>6806479</v>
+        <v>6806856</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7341,10 +7340,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129215742</v>
+        <v>129215891</v>
       </c>
       <c r="B69" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,37 +7351,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434910</v>
+        <v>434812</v>
       </c>
       <c r="R69" t="n">
-        <v>6806856</v>
+        <v>6806610</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7423,7 +7419,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7442,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129215891</v>
+        <v>129215898</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7477,10 +7472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434812</v>
+        <v>434759</v>
       </c>
       <c r="R70" t="n">
-        <v>6806610</v>
+        <v>6806455</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7539,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215898</v>
+        <v>129215821</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7550,21 +7545,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7574,10 +7569,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434759</v>
+        <v>434913</v>
       </c>
       <c r="R71" t="n">
-        <v>6806455</v>
+        <v>6806785</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7636,10 +7631,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215821</v>
+        <v>129215895</v>
       </c>
       <c r="B72" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7647,21 +7642,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7671,10 +7666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434913</v>
+        <v>434858</v>
       </c>
       <c r="R72" t="n">
-        <v>6806785</v>
+        <v>6806562</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7733,10 +7728,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129215895</v>
+        <v>129215899</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7768,10 +7763,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434858</v>
+        <v>434763</v>
       </c>
       <c r="R73" t="n">
-        <v>6806562</v>
+        <v>6806436</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7830,10 +7825,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215899</v>
+        <v>129215851</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434763</v>
+        <v>434362</v>
       </c>
       <c r="R74" t="n">
-        <v>6806436</v>
+        <v>6806519</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7927,45 +7922,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215851</v>
+        <v>129215764</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434362</v>
+        <v>434687</v>
       </c>
       <c r="R75" t="n">
-        <v>6806519</v>
+        <v>6806459</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8024,10 +8027,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215764</v>
+        <v>129215807</v>
       </c>
       <c r="B76" t="n">
-        <v>56913</v>
+        <v>97546</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8035,31 +8038,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8067,10 +8066,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434687</v>
+        <v>434541</v>
       </c>
       <c r="R76" t="n">
-        <v>6806459</v>
+        <v>6806479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8111,6 +8110,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>129215887</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>129215858</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8323,10 +8323,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215805</v>
+        <v>129215801</v>
       </c>
       <c r="B79" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434761</v>
+        <v>434883</v>
       </c>
       <c r="R79" t="n">
-        <v>6806449</v>
+        <v>6806894</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8428,10 +8428,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215801</v>
+        <v>129215805</v>
       </c>
       <c r="B80" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434883</v>
+        <v>434761</v>
       </c>
       <c r="R80" t="n">
-        <v>6806894</v>
+        <v>6806449</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8536,7 +8536,7 @@
         <v>129215773</v>
       </c>
       <c r="B81" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8638,53 +8638,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215771</v>
+        <v>129215886</v>
       </c>
       <c r="B82" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434229</v>
+        <v>434934</v>
       </c>
       <c r="R82" t="n">
-        <v>6806613</v>
+        <v>6806762</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8743,53 +8735,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215768</v>
+        <v>129215741</v>
       </c>
       <c r="B83" t="n">
-        <v>56913</v>
+        <v>79658</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434422</v>
+        <v>434844</v>
       </c>
       <c r="R83" t="n">
-        <v>6806522</v>
+        <v>6806852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8848,53 +8832,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215787</v>
+        <v>129215863</v>
       </c>
       <c r="B84" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434813</v>
+        <v>434279</v>
       </c>
       <c r="R84" t="n">
-        <v>6806656</v>
+        <v>6806587</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8953,53 +8929,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215774</v>
+        <v>129215853</v>
       </c>
       <c r="B85" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434307</v>
+        <v>434280</v>
       </c>
       <c r="R85" t="n">
-        <v>6806608</v>
+        <v>6806556</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9058,10 +9026,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215886</v>
+        <v>129215850</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9093,10 +9061,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434934</v>
+        <v>434376</v>
       </c>
       <c r="R86" t="n">
-        <v>6806762</v>
+        <v>6806560</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9155,10 +9123,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215741</v>
+        <v>129215843</v>
       </c>
       <c r="B87" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9166,21 +9134,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9190,10 +9158,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434844</v>
+        <v>434628</v>
       </c>
       <c r="R87" t="n">
-        <v>6806852</v>
+        <v>6806457</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9252,10 +9220,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215863</v>
+        <v>129215861</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9281,16 +9249,19 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434279</v>
+        <v>434259</v>
       </c>
       <c r="R88" t="n">
-        <v>6806587</v>
+        <v>6806607</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9331,6 +9302,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9349,10 +9321,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215853</v>
+        <v>129215803</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9360,34 +9332,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434280</v>
+        <v>434895</v>
       </c>
       <c r="R89" t="n">
-        <v>6806556</v>
+        <v>6806664</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9446,10 +9426,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215850</v>
+        <v>129215804</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9457,34 +9437,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434376</v>
+        <v>434880</v>
       </c>
       <c r="R90" t="n">
-        <v>6806560</v>
+        <v>6806584</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9543,45 +9531,53 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215843</v>
+        <v>129215771</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434628</v>
+        <v>434229</v>
       </c>
       <c r="R91" t="n">
-        <v>6806457</v>
+        <v>6806613</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9640,37 +9636,42 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215861</v>
+        <v>129215768</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9678,10 +9679,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434259</v>
+        <v>434422</v>
       </c>
       <c r="R92" t="n">
-        <v>6806607</v>
+        <v>6806522</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9722,7 +9723,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9741,32 +9741,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215804</v>
+        <v>129215787</v>
       </c>
       <c r="B93" t="n">
-        <v>57720</v>
+        <v>56915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434880</v>
+        <v>434813</v>
       </c>
       <c r="R93" t="n">
-        <v>6806584</v>
+        <v>6806656</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,32 +9846,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215803</v>
+        <v>129215774</v>
       </c>
       <c r="B94" t="n">
-        <v>57720</v>
+        <v>56915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9879,7 +9879,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434895</v>
+        <v>434307</v>
       </c>
       <c r="R94" t="n">
-        <v>6806664</v>
+        <v>6806608</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9954,7 +9954,7 @@
         <v>129215872</v>
       </c>
       <c r="B95" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10052,42 +10052,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129215776</v>
+        <v>129215883</v>
       </c>
       <c r="B96" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10095,10 +10090,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>434445</v>
+        <v>434920</v>
       </c>
       <c r="R96" t="n">
-        <v>6806699</v>
+        <v>6806876</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10133,12 +10128,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10157,53 +10158,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129215777</v>
+        <v>129215860</v>
       </c>
       <c r="B97" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434432</v>
+        <v>434241</v>
       </c>
       <c r="R97" t="n">
-        <v>6806670</v>
+        <v>6806618</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10262,10 +10255,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215883</v>
+        <v>129215865</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10291,19 +10284,16 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434920</v>
+        <v>434358</v>
       </c>
       <c r="R98" t="n">
-        <v>6806876</v>
+        <v>6806608</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10338,18 +10328,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10368,45 +10352,53 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215860</v>
+        <v>129215776</v>
       </c>
       <c r="B99" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434241</v>
+        <v>434445</v>
       </c>
       <c r="R99" t="n">
-        <v>6806618</v>
+        <v>6806699</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10465,45 +10457,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215865</v>
+        <v>129215777</v>
       </c>
       <c r="B100" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434358</v>
+        <v>434432</v>
       </c>
       <c r="R100" t="n">
-        <v>6806608</v>
+        <v>6806670</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10562,45 +10562,53 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215759</v>
+        <v>129215818</v>
       </c>
       <c r="B101" t="n">
-        <v>79625</v>
+        <v>58095</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434930</v>
+        <v>434849</v>
       </c>
       <c r="R101" t="n">
-        <v>6806768</v>
+        <v>6806700</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10659,53 +10667,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215818</v>
+        <v>129215759</v>
       </c>
       <c r="B102" t="n">
-        <v>58093</v>
+        <v>79629</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103015</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434849</v>
+        <v>434930</v>
       </c>
       <c r="R102" t="n">
-        <v>6806700</v>
+        <v>6806768</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10764,45 +10764,53 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215873</v>
+        <v>129215784</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>56915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434463</v>
+        <v>434853</v>
       </c>
       <c r="R103" t="n">
-        <v>6806664</v>
+        <v>6806697</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10861,10 +10869,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129215884</v>
+        <v>129215873</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10896,10 +10904,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434890</v>
+        <v>434463</v>
       </c>
       <c r="R104" t="n">
-        <v>6806827</v>
+        <v>6806664</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10958,10 +10966,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129215825</v>
+        <v>129215884</v>
       </c>
       <c r="B105" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10969,21 +10977,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10993,10 +11001,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434799</v>
+        <v>434890</v>
       </c>
       <c r="R105" t="n">
-        <v>6806687</v>
+        <v>6806827</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11055,10 +11063,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129215802</v>
+        <v>129215825</v>
       </c>
       <c r="B106" t="n">
-        <v>57720</v>
+        <v>78796</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11066,42 +11074,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>434910</v>
+        <v>434799</v>
       </c>
       <c r="R106" t="n">
-        <v>6806898</v>
+        <v>6806687</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11160,32 +11160,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129215784</v>
+        <v>129215802</v>
       </c>
       <c r="B107" t="n">
-        <v>56913</v>
+        <v>57722</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11193,7 +11193,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>434853</v>
+        <v>434910</v>
       </c>
       <c r="R107" t="n">
-        <v>6806697</v>
+        <v>6806898</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215849</v>
+        <v>129215794</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>57885</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11276,34 +11276,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434437</v>
+        <v>434852</v>
       </c>
       <c r="R108" t="n">
-        <v>6806501</v>
+        <v>6806551</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11362,10 +11370,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215848</v>
+        <v>129215849</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11397,10 +11405,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434473</v>
+        <v>434437</v>
       </c>
       <c r="R109" t="n">
-        <v>6806453</v>
+        <v>6806501</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11459,10 +11467,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215879</v>
+        <v>129215848</v>
       </c>
       <c r="B110" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11494,10 +11502,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434627</v>
+        <v>434473</v>
       </c>
       <c r="R110" t="n">
-        <v>6806787</v>
+        <v>6806453</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11556,10 +11564,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215892</v>
+        <v>129215879</v>
       </c>
       <c r="B111" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11591,10 +11599,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434884</v>
+        <v>434627</v>
       </c>
       <c r="R111" t="n">
-        <v>6806606</v>
+        <v>6806787</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11653,53 +11661,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215765</v>
+        <v>129215892</v>
       </c>
       <c r="B112" t="n">
-        <v>56913</v>
+        <v>79039</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434630</v>
+        <v>434884</v>
       </c>
       <c r="R112" t="n">
-        <v>6806465</v>
+        <v>6806606</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11758,10 +11758,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215769</v>
+        <v>129215765</v>
       </c>
       <c r="B113" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11801,10 +11801,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434382</v>
+        <v>434630</v>
       </c>
       <c r="R113" t="n">
-        <v>6806548</v>
+        <v>6806465</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11863,32 +11863,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215794</v>
+        <v>129215769</v>
       </c>
       <c r="B114" t="n">
-        <v>57883</v>
+        <v>56915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11896,7 +11896,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434852</v>
+        <v>434382</v>
       </c>
       <c r="R114" t="n">
-        <v>6806551</v>
+        <v>6806548</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215900</v>
+        <v>129215812</v>
       </c>
       <c r="B115" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434775</v>
+        <v>434922</v>
       </c>
       <c r="R115" t="n">
-        <v>6806423</v>
+        <v>6806746</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215867</v>
+        <v>129215754</v>
       </c>
       <c r="B116" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12076,21 +12076,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12100,10 +12100,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434375</v>
+        <v>434774</v>
       </c>
       <c r="R116" t="n">
-        <v>6806574</v>
+        <v>6806803</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12162,10 +12162,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215734</v>
+        <v>129215796</v>
       </c>
       <c r="B117" t="n">
-        <v>79654</v>
+        <v>57722</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12173,34 +12173,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434546</v>
+        <v>434635</v>
       </c>
       <c r="R117" t="n">
-        <v>6806737</v>
+        <v>6806453</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12259,10 +12267,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215844</v>
+        <v>129215797</v>
       </c>
       <c r="B118" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12270,34 +12278,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434623</v>
+        <v>434602</v>
       </c>
       <c r="R118" t="n">
-        <v>6806466</v>
+        <v>6806495</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12356,10 +12372,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215868</v>
+        <v>129215900</v>
       </c>
       <c r="B119" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12391,10 +12407,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434415</v>
+        <v>434775</v>
       </c>
       <c r="R119" t="n">
-        <v>6806576</v>
+        <v>6806423</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12453,10 +12469,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215797</v>
+        <v>129215867</v>
       </c>
       <c r="B120" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12464,42 +12480,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434602</v>
+        <v>434375</v>
       </c>
       <c r="R120" t="n">
-        <v>6806495</v>
+        <v>6806574</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12558,10 +12566,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215796</v>
+        <v>129215734</v>
       </c>
       <c r="B121" t="n">
-        <v>57720</v>
+        <v>79658</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,42 +12577,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434635</v>
+        <v>434546</v>
       </c>
       <c r="R121" t="n">
-        <v>6806453</v>
+        <v>6806737</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,10 +12663,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215812</v>
+        <v>129215844</v>
       </c>
       <c r="B122" t="n">
-        <v>78793</v>
+        <v>79039</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12674,21 +12674,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12698,10 +12698,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434922</v>
+        <v>434623</v>
       </c>
       <c r="R122" t="n">
-        <v>6806746</v>
+        <v>6806466</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215754</v>
+        <v>129215868</v>
       </c>
       <c r="B123" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12771,21 +12771,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12795,10 +12795,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434774</v>
+        <v>434415</v>
       </c>
       <c r="R123" t="n">
-        <v>6806803</v>
+        <v>6806576</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12860,7 +12860,7 @@
         <v>129215852</v>
       </c>
       <c r="B124" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129215889</v>
+        <v>129215901</v>
       </c>
       <c r="B125" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434813</v>
+        <v>434918</v>
       </c>
       <c r="R125" t="n">
-        <v>6806692</v>
+        <v>6806737</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13051,10 +13051,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129215901</v>
+        <v>129215889</v>
       </c>
       <c r="B126" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434918</v>
+        <v>434813</v>
       </c>
       <c r="R126" t="n">
-        <v>6806737</v>
+        <v>6806692</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13151,7 +13151,7 @@
         <v>129215745</v>
       </c>
       <c r="B127" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>129215871</v>
       </c>
       <c r="B128" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>129215752</v>
       </c>
       <c r="B129" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>129215751</v>
       </c>
       <c r="B130" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215736</v>
+        <v>129215903</v>
       </c>
       <c r="B10" t="n">
-        <v>79658</v>
+        <v>88930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,34 +1486,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434605</v>
+        <v>434350</v>
       </c>
       <c r="R10" t="n">
-        <v>6806750</v>
+        <v>6806600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,6 +1557,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1572,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215847</v>
+        <v>129215736</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434523</v>
+        <v>434605</v>
       </c>
       <c r="R11" t="n">
-        <v>6806508</v>
+        <v>6806750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,7 +1673,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215875</v>
+        <v>129215847</v>
       </c>
       <c r="B12" t="n">
         <v>79039</v>
@@ -1704,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434516</v>
+        <v>434523</v>
       </c>
       <c r="R12" t="n">
-        <v>6806695</v>
+        <v>6806508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215903</v>
+        <v>129215875</v>
       </c>
       <c r="B13" t="n">
-        <v>88930</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,37 +1781,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434350</v>
+        <v>434516</v>
       </c>
       <c r="R13" t="n">
-        <v>6806600</v>
+        <v>6806695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,7 +1849,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215800</v>
+        <v>129215737</v>
       </c>
       <c r="B20" t="n">
-        <v>57722</v>
+        <v>79658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,42 +2476,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434596</v>
+        <v>434585</v>
       </c>
       <c r="R20" t="n">
-        <v>6806728</v>
+        <v>6806746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2570,10 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215758</v>
+        <v>129215877</v>
       </c>
       <c r="B21" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2581,21 +2573,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2605,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434928</v>
+        <v>434596</v>
       </c>
       <c r="R21" t="n">
-        <v>6806794</v>
+        <v>6806729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2667,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215737</v>
+        <v>129215856</v>
       </c>
       <c r="B22" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2678,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2702,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434585</v>
+        <v>434194</v>
       </c>
       <c r="R22" t="n">
-        <v>6806746</v>
+        <v>6806560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2764,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215877</v>
+        <v>129215735</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2775,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2799,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434596</v>
+        <v>434571</v>
       </c>
       <c r="R23" t="n">
-        <v>6806729</v>
+        <v>6806718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2861,10 +2853,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215856</v>
+        <v>129215744</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2872,34 +2864,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434194</v>
+        <v>434950</v>
       </c>
       <c r="R24" t="n">
-        <v>6806560</v>
+        <v>6806749</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2940,6 +2935,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2958,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215735</v>
+        <v>129215878</v>
       </c>
       <c r="B25" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2969,34 +2965,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434571</v>
+        <v>434621</v>
       </c>
       <c r="R25" t="n">
-        <v>6806718</v>
+        <v>6806786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3037,6 +3036,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3055,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215744</v>
+        <v>129215859</v>
       </c>
       <c r="B26" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,37 +3066,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434950</v>
+        <v>434177</v>
       </c>
       <c r="R26" t="n">
-        <v>6806749</v>
+        <v>6806592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3137,7 +3134,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3156,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215878</v>
+        <v>129215800</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,26 +3163,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3194,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434621</v>
+        <v>434596</v>
       </c>
       <c r="R27" t="n">
-        <v>6806786</v>
+        <v>6806728</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3238,7 +3239,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3257,45 +3257,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215859</v>
+        <v>129215782</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>56915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434177</v>
+        <v>434568</v>
       </c>
       <c r="R28" t="n">
-        <v>6806592</v>
+        <v>6806730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3354,32 +3362,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215782</v>
+        <v>129215793</v>
       </c>
       <c r="B29" t="n">
-        <v>56915</v>
+        <v>57885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3387,7 +3395,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3397,10 +3405,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434568</v>
+        <v>434920</v>
       </c>
       <c r="R29" t="n">
-        <v>6806730</v>
+        <v>6806792</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3459,10 +3467,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215793</v>
+        <v>129215758</v>
       </c>
       <c r="B30" t="n">
-        <v>57885</v>
+        <v>79629</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3470,42 +3478,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434920</v>
+        <v>434928</v>
       </c>
       <c r="R30" t="n">
-        <v>6806792</v>
+        <v>6806794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215799</v>
+        <v>129215753</v>
       </c>
       <c r="B46" t="n">
-        <v>57722</v>
+        <v>79629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,42 +5063,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434142</v>
+        <v>434571</v>
       </c>
       <c r="R46" t="n">
-        <v>6806549</v>
+        <v>6806718</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5157,10 +5149,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129215753</v>
+        <v>129215799</v>
       </c>
       <c r="B47" t="n">
-        <v>79629</v>
+        <v>57722</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5168,34 +5160,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434571</v>
+        <v>434142</v>
       </c>
       <c r="R47" t="n">
-        <v>6806718</v>
+        <v>6806549</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -10764,32 +10764,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215784</v>
+        <v>129215802</v>
       </c>
       <c r="B103" t="n">
-        <v>56915</v>
+        <v>57722</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10797,7 +10797,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434853</v>
+        <v>434910</v>
       </c>
       <c r="R103" t="n">
-        <v>6806697</v>
+        <v>6806898</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10869,45 +10869,53 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129215873</v>
+        <v>129215784</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>56915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434463</v>
+        <v>434853</v>
       </c>
       <c r="R104" t="n">
-        <v>6806664</v>
+        <v>6806697</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11063,10 +11071,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129215825</v>
+        <v>129215873</v>
       </c>
       <c r="B106" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11074,21 +11082,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11098,10 +11106,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>434799</v>
+        <v>434463</v>
       </c>
       <c r="R106" t="n">
-        <v>6806687</v>
+        <v>6806664</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11160,10 +11168,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129215802</v>
+        <v>129215825</v>
       </c>
       <c r="B107" t="n">
-        <v>57722</v>
+        <v>78796</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11171,42 +11179,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>434910</v>
+        <v>434799</v>
       </c>
       <c r="R107" t="n">
-        <v>6806898</v>
+        <v>6806687</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215812</v>
+        <v>129215900</v>
       </c>
       <c r="B115" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434922</v>
+        <v>434775</v>
       </c>
       <c r="R115" t="n">
-        <v>6806746</v>
+        <v>6806423</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215754</v>
+        <v>129215867</v>
       </c>
       <c r="B116" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12076,21 +12076,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12100,10 +12100,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434774</v>
+        <v>434375</v>
       </c>
       <c r="R116" t="n">
-        <v>6806803</v>
+        <v>6806574</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12162,10 +12162,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215796</v>
+        <v>129215734</v>
       </c>
       <c r="B117" t="n">
-        <v>57722</v>
+        <v>79658</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12173,42 +12173,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434635</v>
+        <v>434546</v>
       </c>
       <c r="R117" t="n">
-        <v>6806453</v>
+        <v>6806737</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12267,10 +12259,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215797</v>
+        <v>129215844</v>
       </c>
       <c r="B118" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12278,42 +12270,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434602</v>
+        <v>434623</v>
       </c>
       <c r="R118" t="n">
-        <v>6806495</v>
+        <v>6806466</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12372,7 +12356,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215900</v>
+        <v>129215868</v>
       </c>
       <c r="B119" t="n">
         <v>79039</v>
@@ -12407,10 +12391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434775</v>
+        <v>434415</v>
       </c>
       <c r="R119" t="n">
-        <v>6806423</v>
+        <v>6806576</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12469,10 +12453,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215867</v>
+        <v>129215796</v>
       </c>
       <c r="B120" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12480,34 +12464,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434375</v>
+        <v>434635</v>
       </c>
       <c r="R120" t="n">
-        <v>6806574</v>
+        <v>6806453</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,10 +12558,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215734</v>
+        <v>129215797</v>
       </c>
       <c r="B121" t="n">
-        <v>79658</v>
+        <v>57722</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12577,34 +12569,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434546</v>
+        <v>434602</v>
       </c>
       <c r="R121" t="n">
-        <v>6806737</v>
+        <v>6806495</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,10 +12663,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215844</v>
+        <v>129215812</v>
       </c>
       <c r="B122" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12674,21 +12674,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12698,10 +12698,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434623</v>
+        <v>434922</v>
       </c>
       <c r="R122" t="n">
-        <v>6806466</v>
+        <v>6806746</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215868</v>
+        <v>129215754</v>
       </c>
       <c r="B123" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12771,21 +12771,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12795,10 +12795,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434415</v>
+        <v>434774</v>
       </c>
       <c r="R123" t="n">
-        <v>6806576</v>
+        <v>6806803</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215876</v>
+        <v>129215761</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434591</v>
+        <v>434924</v>
       </c>
       <c r="R2" t="n">
-        <v>6806739</v>
+        <v>6806749</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215864</v>
+        <v>129215876</v>
       </c>
       <c r="B3" t="n">
         <v>79039</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434319</v>
+        <v>434591</v>
       </c>
       <c r="R3" t="n">
-        <v>6806589</v>
+        <v>6806739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,53 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215767</v>
+        <v>129215864</v>
       </c>
       <c r="B4" t="n">
-        <v>56915</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434546</v>
+        <v>434319</v>
       </c>
       <c r="R4" t="n">
-        <v>6806482</v>
+        <v>6806589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215775</v>
+        <v>129215767</v>
       </c>
       <c r="B5" t="n">
         <v>56915</v>
@@ -1017,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434334</v>
+        <v>434546</v>
       </c>
       <c r="R5" t="n">
-        <v>6806593</v>
+        <v>6806482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1071,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215770</v>
+        <v>129215775</v>
       </c>
       <c r="B6" t="n">
         <v>56915</v>
@@ -1122,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434136</v>
+        <v>434334</v>
       </c>
       <c r="R6" t="n">
-        <v>6806558</v>
+        <v>6806593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,45 +1176,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215761</v>
+        <v>129215770</v>
       </c>
       <c r="B7" t="n">
-        <v>79629</v>
+        <v>56915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434924</v>
+        <v>434136</v>
       </c>
       <c r="R7" t="n">
-        <v>6806749</v>
+        <v>6806558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1478,7 +1478,7 @@
         <v>129215903</v>
       </c>
       <c r="B10" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215736</v>
+        <v>129215847</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434605</v>
+        <v>434523</v>
       </c>
       <c r="R11" t="n">
-        <v>6806750</v>
+        <v>6806508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215847</v>
+        <v>129215875</v>
       </c>
       <c r="B12" t="n">
         <v>79039</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434523</v>
+        <v>434516</v>
       </c>
       <c r="R12" t="n">
-        <v>6806508</v>
+        <v>6806695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215875</v>
+        <v>129215736</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434516</v>
+        <v>434605</v>
       </c>
       <c r="R13" t="n">
-        <v>6806695</v>
+        <v>6806750</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129215795</v>
+        <v>129215813</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>78797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,42 +1878,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434758</v>
+        <v>434803</v>
       </c>
       <c r="R14" t="n">
-        <v>6806435</v>
+        <v>6806683</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1972,10 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215813</v>
+        <v>129215795</v>
       </c>
       <c r="B15" t="n">
-        <v>78797</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,34 +1975,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434803</v>
+        <v>434758</v>
       </c>
       <c r="R15" t="n">
-        <v>6806683</v>
+        <v>6806435</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215737</v>
+        <v>129215877</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434585</v>
+        <v>434596</v>
       </c>
       <c r="R20" t="n">
-        <v>6806746</v>
+        <v>6806729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215877</v>
+        <v>129215856</v>
       </c>
       <c r="B21" t="n">
         <v>79039</v>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434596</v>
+        <v>434194</v>
       </c>
       <c r="R21" t="n">
-        <v>6806729</v>
+        <v>6806560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215856</v>
+        <v>129215878</v>
       </c>
       <c r="B22" t="n">
         <v>79039</v>
@@ -2688,16 +2688,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434194</v>
+        <v>434621</v>
       </c>
       <c r="R22" t="n">
-        <v>6806560</v>
+        <v>6806786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2738,6 +2741,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2756,10 +2760,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215735</v>
+        <v>129215859</v>
       </c>
       <c r="B23" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2771,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2795,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434571</v>
+        <v>434177</v>
       </c>
       <c r="R23" t="n">
-        <v>6806718</v>
+        <v>6806592</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,7 +2857,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215744</v>
+        <v>129215737</v>
       </c>
       <c r="B24" t="n">
         <v>79658</v>
@@ -2882,19 +2886,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434950</v>
+        <v>434585</v>
       </c>
       <c r="R24" t="n">
-        <v>6806749</v>
+        <v>6806746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,7 +2936,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215878</v>
+        <v>129215735</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2965,37 +2965,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434621</v>
+        <v>434571</v>
       </c>
       <c r="R25" t="n">
-        <v>6806786</v>
+        <v>6806718</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3036,7 +3033,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3055,10 +3051,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215859</v>
+        <v>129215744</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,34 +3062,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434177</v>
+        <v>434950</v>
       </c>
       <c r="R26" t="n">
-        <v>6806592</v>
+        <v>6806749</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3134,6 +3133,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3257,53 +3257,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215782</v>
+        <v>129215758</v>
       </c>
       <c r="B28" t="n">
-        <v>56915</v>
+        <v>79629</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434568</v>
+        <v>434928</v>
       </c>
       <c r="R28" t="n">
-        <v>6806730</v>
+        <v>6806794</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3362,32 +3354,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215793</v>
+        <v>129215782</v>
       </c>
       <c r="B29" t="n">
-        <v>57885</v>
+        <v>56915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3395,7 +3387,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3405,10 +3397,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434920</v>
+        <v>434568</v>
       </c>
       <c r="R29" t="n">
-        <v>6806792</v>
+        <v>6806730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3467,10 +3459,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215758</v>
+        <v>129215793</v>
       </c>
       <c r="B30" t="n">
-        <v>79629</v>
+        <v>57885</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3478,34 +3470,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434928</v>
+        <v>434920</v>
       </c>
       <c r="R30" t="n">
-        <v>6806794</v>
+        <v>6806792</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3564,37 +3564,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215881</v>
+        <v>129215780</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>56915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3602,10 +3607,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434834</v>
+        <v>434449</v>
       </c>
       <c r="R31" t="n">
-        <v>6806837</v>
+        <v>6806667</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3646,7 +3651,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3665,10 +3669,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215750</v>
+        <v>129215881</v>
       </c>
       <c r="B32" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,34 +3680,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434775</v>
+        <v>434834</v>
       </c>
       <c r="R32" t="n">
-        <v>6806482</v>
+        <v>6806837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3744,6 +3751,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3762,53 +3770,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215780</v>
+        <v>129215750</v>
       </c>
       <c r="B33" t="n">
-        <v>56915</v>
+        <v>79658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434449</v>
+        <v>434775</v>
       </c>
       <c r="R33" t="n">
-        <v>6806667</v>
+        <v>6806482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129215822</v>
+        <v>129215902</v>
       </c>
       <c r="B35" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3975,34 +3975,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434936</v>
+        <v>434784</v>
       </c>
       <c r="R35" t="n">
-        <v>6806756</v>
+        <v>6806543</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4037,12 +4040,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4061,10 +4070,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129215823</v>
+        <v>129215854</v>
       </c>
       <c r="B36" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4072,21 +4081,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4096,10 +4105,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434906</v>
+        <v>434268</v>
       </c>
       <c r="R36" t="n">
-        <v>6806734</v>
+        <v>6806557</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4158,7 +4167,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129215902</v>
+        <v>129215869</v>
       </c>
       <c r="B37" t="n">
         <v>79039</v>
@@ -4187,19 +4196,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434784</v>
+        <v>434432</v>
       </c>
       <c r="R37" t="n">
-        <v>6806543</v>
+        <v>6806606</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4234,18 +4240,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129215738</v>
+        <v>129215822</v>
       </c>
       <c r="B38" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434764</v>
+        <v>434936</v>
       </c>
       <c r="R38" t="n">
-        <v>6806804</v>
+        <v>6806756</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129215854</v>
+        <v>129215823</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4372,21 +4372,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434268</v>
+        <v>434906</v>
       </c>
       <c r="R39" t="n">
-        <v>6806557</v>
+        <v>6806734</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129215869</v>
+        <v>129215738</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4469,21 +4469,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434432</v>
+        <v>434764</v>
       </c>
       <c r="R40" t="n">
-        <v>6806606</v>
+        <v>6806804</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5052,10 +5052,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215753</v>
+        <v>129215799</v>
       </c>
       <c r="B46" t="n">
-        <v>79629</v>
+        <v>57722</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,34 +5063,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434571</v>
+        <v>434142</v>
       </c>
       <c r="R46" t="n">
-        <v>6806718</v>
+        <v>6806549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5149,10 +5157,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129215799</v>
+        <v>129215753</v>
       </c>
       <c r="B47" t="n">
-        <v>57722</v>
+        <v>79629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5160,42 +5168,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434142</v>
+        <v>434571</v>
       </c>
       <c r="R47" t="n">
-        <v>6806549</v>
+        <v>6806718</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215904</v>
+        <v>129215755</v>
       </c>
       <c r="B49" t="n">
-        <v>79658</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434857</v>
+        <v>434812</v>
       </c>
       <c r="R49" t="n">
-        <v>6806833</v>
+        <v>6806771</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,53 +5448,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215790</v>
+        <v>129215760</v>
       </c>
       <c r="B50" t="n">
-        <v>56915</v>
+        <v>79629</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434809</v>
+        <v>434895</v>
       </c>
       <c r="R50" t="n">
-        <v>6806535</v>
+        <v>6806736</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5553,53 +5545,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215786</v>
+        <v>129215808</v>
       </c>
       <c r="B51" t="n">
-        <v>56915</v>
+        <v>78797</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434883</v>
+        <v>434355</v>
       </c>
       <c r="R51" t="n">
-        <v>6806675</v>
+        <v>6806519</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,10 +5642,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215755</v>
+        <v>129215904</v>
       </c>
       <c r="B52" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5669,21 +5653,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5693,10 +5677,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434812</v>
+        <v>434857</v>
       </c>
       <c r="R52" t="n">
-        <v>6806771</v>
+        <v>6806833</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,45 +5739,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215760</v>
+        <v>129215790</v>
       </c>
       <c r="B53" t="n">
-        <v>79629</v>
+        <v>56915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434895</v>
+        <v>434809</v>
       </c>
       <c r="R53" t="n">
-        <v>6806736</v>
+        <v>6806535</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,45 +5844,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129215808</v>
+        <v>129215786</v>
       </c>
       <c r="B54" t="n">
-        <v>78797</v>
+        <v>56915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434355</v>
+        <v>434883</v>
       </c>
       <c r="R54" t="n">
-        <v>6806519</v>
+        <v>6806675</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129215841</v>
+        <v>129215874</v>
       </c>
       <c r="B55" t="n">
         <v>79039</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434433</v>
+        <v>434483</v>
       </c>
       <c r="R55" t="n">
-        <v>6806597</v>
+        <v>6806662</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,7 +6028,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6047,7 +6046,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129215874</v>
+        <v>129215896</v>
       </c>
       <c r="B56" t="n">
         <v>79039</v>
@@ -6082,10 +6081,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434483</v>
+        <v>434783</v>
       </c>
       <c r="R56" t="n">
-        <v>6806662</v>
+        <v>6806478</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6144,7 +6143,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129215896</v>
+        <v>129215841</v>
       </c>
       <c r="B57" t="n">
         <v>79039</v>
@@ -6179,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434783</v>
+        <v>434433</v>
       </c>
       <c r="R57" t="n">
-        <v>6806478</v>
+        <v>6806597</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6223,6 +6222,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215819</v>
+        <v>129215885</v>
       </c>
       <c r="B61" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6567,37 +6567,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434773</v>
+        <v>434884</v>
       </c>
       <c r="R61" t="n">
-        <v>6806803</v>
+        <v>6806816</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6638,7 +6635,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6657,7 +6653,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129215880</v>
+        <v>129215862</v>
       </c>
       <c r="B62" t="n">
         <v>79039</v>
@@ -6692,10 +6688,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434845</v>
+        <v>434270</v>
       </c>
       <c r="R62" t="n">
-        <v>6806812</v>
+        <v>6806602</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6754,10 +6750,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215739</v>
+        <v>129215819</v>
       </c>
       <c r="B63" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6765,34 +6761,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434817</v>
+        <v>434773</v>
       </c>
       <c r="R63" t="n">
-        <v>6806766</v>
+        <v>6806803</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6833,6 +6832,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6851,10 +6851,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215824</v>
+        <v>129215880</v>
       </c>
       <c r="B64" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6862,21 +6862,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434922</v>
+        <v>434845</v>
       </c>
       <c r="R64" t="n">
-        <v>6806746</v>
+        <v>6806812</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215885</v>
+        <v>129215739</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434884</v>
+        <v>434817</v>
       </c>
       <c r="R65" t="n">
-        <v>6806816</v>
+        <v>6806766</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215743</v>
+        <v>129215824</v>
       </c>
       <c r="B66" t="n">
-        <v>79658</v>
+        <v>78796</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7083,7 +7083,7 @@
         <v>434922</v>
       </c>
       <c r="R66" t="n">
-        <v>6806795</v>
+        <v>6806746</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129215862</v>
+        <v>129215743</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434270</v>
+        <v>434922</v>
       </c>
       <c r="R67" t="n">
-        <v>6806602</v>
+        <v>6806795</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215742</v>
+        <v>129215895</v>
       </c>
       <c r="B68" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7250,37 +7250,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434910</v>
+        <v>434858</v>
       </c>
       <c r="R68" t="n">
-        <v>6806856</v>
+        <v>6806562</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7321,7 +7318,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7340,7 +7336,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129215891</v>
+        <v>129215899</v>
       </c>
       <c r="B69" t="n">
         <v>79039</v>
@@ -7375,10 +7371,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434812</v>
+        <v>434763</v>
       </c>
       <c r="R69" t="n">
-        <v>6806610</v>
+        <v>6806436</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7437,7 +7433,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129215898</v>
+        <v>129215851</v>
       </c>
       <c r="B70" t="n">
         <v>79039</v>
@@ -7472,10 +7468,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434759</v>
+        <v>434362</v>
       </c>
       <c r="R70" t="n">
-        <v>6806455</v>
+        <v>6806519</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7534,10 +7530,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215821</v>
+        <v>129215742</v>
       </c>
       <c r="B71" t="n">
-        <v>78796</v>
+        <v>79658</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,34 +7541,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434913</v>
+        <v>434910</v>
       </c>
       <c r="R71" t="n">
-        <v>6806785</v>
+        <v>6806856</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7613,6 +7612,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215895</v>
+        <v>129215891</v>
       </c>
       <c r="B72" t="n">
         <v>79039</v>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434858</v>
+        <v>434812</v>
       </c>
       <c r="R72" t="n">
-        <v>6806562</v>
+        <v>6806610</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7728,7 +7728,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129215899</v>
+        <v>129215898</v>
       </c>
       <c r="B73" t="n">
         <v>79039</v>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434763</v>
+        <v>434759</v>
       </c>
       <c r="R73" t="n">
-        <v>6806436</v>
+        <v>6806455</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215851</v>
+        <v>129215821</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7836,21 +7836,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434362</v>
+        <v>434913</v>
       </c>
       <c r="R74" t="n">
-        <v>6806519</v>
+        <v>6806785</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8030,7 +8030,7 @@
         <v>129215807</v>
       </c>
       <c r="B76" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8735,10 +8735,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215741</v>
+        <v>129215863</v>
       </c>
       <c r="B83" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8746,21 +8746,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434844</v>
+        <v>434279</v>
       </c>
       <c r="R83" t="n">
-        <v>6806852</v>
+        <v>6806587</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,7 +8832,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215863</v>
+        <v>129215853</v>
       </c>
       <c r="B84" t="n">
         <v>79039</v>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434279</v>
+        <v>434280</v>
       </c>
       <c r="R84" t="n">
-        <v>6806587</v>
+        <v>6806556</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8929,7 +8929,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215853</v>
+        <v>129215843</v>
       </c>
       <c r="B85" t="n">
         <v>79039</v>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434280</v>
+        <v>434628</v>
       </c>
       <c r="R85" t="n">
-        <v>6806556</v>
+        <v>6806457</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9026,10 +9026,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215850</v>
+        <v>129215741</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9037,21 +9037,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434376</v>
+        <v>434844</v>
       </c>
       <c r="R86" t="n">
-        <v>6806560</v>
+        <v>6806852</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9123,7 +9123,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215843</v>
+        <v>129215850</v>
       </c>
       <c r="B87" t="n">
         <v>79039</v>
@@ -9158,10 +9158,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434628</v>
+        <v>434376</v>
       </c>
       <c r="R87" t="n">
-        <v>6806457</v>
+        <v>6806560</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10764,10 +10764,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215802</v>
+        <v>129215884</v>
       </c>
       <c r="B103" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10775,42 +10775,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434910</v>
+        <v>434890</v>
       </c>
       <c r="R103" t="n">
-        <v>6806898</v>
+        <v>6806827</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10869,53 +10861,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129215784</v>
+        <v>129215825</v>
       </c>
       <c r="B104" t="n">
-        <v>56915</v>
+        <v>78796</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434853</v>
+        <v>434799</v>
       </c>
       <c r="R104" t="n">
-        <v>6806697</v>
+        <v>6806687</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10974,10 +10958,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129215884</v>
+        <v>129215802</v>
       </c>
       <c r="B105" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10985,34 +10969,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434890</v>
+        <v>434910</v>
       </c>
       <c r="R105" t="n">
-        <v>6806827</v>
+        <v>6806898</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11071,45 +11063,53 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129215873</v>
+        <v>129215784</v>
       </c>
       <c r="B106" t="n">
-        <v>79039</v>
+        <v>56915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>434463</v>
+        <v>434853</v>
       </c>
       <c r="R106" t="n">
-        <v>6806664</v>
+        <v>6806697</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11168,10 +11168,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129215825</v>
+        <v>129215873</v>
       </c>
       <c r="B107" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11179,21 +11179,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>434799</v>
+        <v>434463</v>
       </c>
       <c r="R107" t="n">
-        <v>6806687</v>
+        <v>6806664</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215794</v>
+        <v>129215848</v>
       </c>
       <c r="B108" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11276,42 +11276,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434852</v>
+        <v>434473</v>
       </c>
       <c r="R108" t="n">
-        <v>6806551</v>
+        <v>6806453</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11370,7 +11362,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215849</v>
+        <v>129215879</v>
       </c>
       <c r="B109" t="n">
         <v>79039</v>
@@ -11405,10 +11397,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434437</v>
+        <v>434627</v>
       </c>
       <c r="R109" t="n">
-        <v>6806501</v>
+        <v>6806787</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11467,7 +11459,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215848</v>
+        <v>129215892</v>
       </c>
       <c r="B110" t="n">
         <v>79039</v>
@@ -11502,10 +11494,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434473</v>
+        <v>434884</v>
       </c>
       <c r="R110" t="n">
-        <v>6806453</v>
+        <v>6806606</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11564,45 +11556,53 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215879</v>
+        <v>129215765</v>
       </c>
       <c r="B111" t="n">
-        <v>79039</v>
+        <v>56915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434627</v>
+        <v>434630</v>
       </c>
       <c r="R111" t="n">
-        <v>6806787</v>
+        <v>6806465</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11661,45 +11661,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215892</v>
+        <v>129215769</v>
       </c>
       <c r="B112" t="n">
-        <v>79039</v>
+        <v>56915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434884</v>
+        <v>434382</v>
       </c>
       <c r="R112" t="n">
-        <v>6806606</v>
+        <v>6806548</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11758,53 +11766,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215765</v>
+        <v>129215849</v>
       </c>
       <c r="B113" t="n">
-        <v>56915</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434630</v>
+        <v>434437</v>
       </c>
       <c r="R113" t="n">
-        <v>6806465</v>
+        <v>6806501</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11863,32 +11863,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215769</v>
+        <v>129215794</v>
       </c>
       <c r="B114" t="n">
-        <v>56915</v>
+        <v>57885</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11896,7 +11896,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434382</v>
+        <v>434852</v>
       </c>
       <c r="R114" t="n">
-        <v>6806548</v>
+        <v>6806551</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12162,10 +12162,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215734</v>
+        <v>129215844</v>
       </c>
       <c r="B117" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12173,21 +12173,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434546</v>
+        <v>434623</v>
       </c>
       <c r="R117" t="n">
-        <v>6806737</v>
+        <v>6806466</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215844</v>
+        <v>129215868</v>
       </c>
       <c r="B118" t="n">
         <v>79039</v>
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434623</v>
+        <v>434415</v>
       </c>
       <c r="R118" t="n">
-        <v>6806466</v>
+        <v>6806576</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12356,10 +12356,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215868</v>
+        <v>129215734</v>
       </c>
       <c r="B119" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12367,21 +12367,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12391,10 +12391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434415</v>
+        <v>434546</v>
       </c>
       <c r="R119" t="n">
-        <v>6806576</v>
+        <v>6806737</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12857,7 +12857,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129215852</v>
+        <v>129215901</v>
       </c>
       <c r="B124" t="n">
         <v>79039</v>
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434335</v>
+        <v>434918</v>
       </c>
       <c r="R124" t="n">
-        <v>6806532</v>
+        <v>6806737</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129215901</v>
+        <v>129215745</v>
       </c>
       <c r="B125" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,21 +12965,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434918</v>
+        <v>434934</v>
       </c>
       <c r="R125" t="n">
-        <v>6806737</v>
+        <v>6806753</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13051,10 +13051,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129215889</v>
+        <v>129215752</v>
       </c>
       <c r="B126" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13062,21 +13062,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434813</v>
+        <v>434263</v>
       </c>
       <c r="R126" t="n">
-        <v>6806692</v>
+        <v>6806561</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13148,10 +13148,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129215745</v>
+        <v>129215751</v>
       </c>
       <c r="B127" t="n">
-        <v>79658</v>
+        <v>79629</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13159,21 +13159,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434934</v>
+        <v>434673</v>
       </c>
       <c r="R127" t="n">
-        <v>6806753</v>
+        <v>6806460</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,7 +13245,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129215871</v>
+        <v>129215852</v>
       </c>
       <c r="B128" t="n">
         <v>79039</v>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434443</v>
+        <v>434335</v>
       </c>
       <c r="R128" t="n">
-        <v>6806595</v>
+        <v>6806532</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129215752</v>
+        <v>129215889</v>
       </c>
       <c r="B129" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13353,21 +13353,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>434263</v>
+        <v>434813</v>
       </c>
       <c r="R129" t="n">
-        <v>6806561</v>
+        <v>6806692</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129215751</v>
+        <v>129215871</v>
       </c>
       <c r="B130" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,21 +13450,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434673</v>
+        <v>434443</v>
       </c>
       <c r="R130" t="n">
-        <v>6806460</v>
+        <v>6806595</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215761</v>
+        <v>129215767</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434924</v>
+        <v>434546</v>
       </c>
       <c r="R2" t="n">
-        <v>6806749</v>
+        <v>6806482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +780,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215876</v>
+        <v>129215775</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>56917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434591</v>
+        <v>434334</v>
       </c>
       <c r="R3" t="n">
-        <v>6806739</v>
+        <v>6806593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +885,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215864</v>
+        <v>129215770</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>56917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434319</v>
+        <v>434136</v>
       </c>
       <c r="R4" t="n">
-        <v>6806589</v>
+        <v>6806558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,53 +990,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215767</v>
+        <v>129215876</v>
       </c>
       <c r="B5" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434546</v>
+        <v>434591</v>
       </c>
       <c r="R5" t="n">
-        <v>6806482</v>
+        <v>6806739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,53 +1087,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215775</v>
+        <v>129215864</v>
       </c>
       <c r="B6" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434334</v>
+        <v>434319</v>
       </c>
       <c r="R6" t="n">
-        <v>6806593</v>
+        <v>6806589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,53 +1184,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215770</v>
+        <v>129215761</v>
       </c>
       <c r="B7" t="n">
-        <v>56915</v>
+        <v>79631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434136</v>
+        <v>434924</v>
       </c>
       <c r="R7" t="n">
-        <v>6806558</v>
+        <v>6806749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>129215846</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129215888</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215903</v>
+        <v>129215795</v>
       </c>
       <c r="B10" t="n">
-        <v>88937</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,26 +1486,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1513,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434350</v>
+        <v>434758</v>
       </c>
       <c r="R10" t="n">
-        <v>6806600</v>
+        <v>6806435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1562,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1576,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215847</v>
+        <v>129215736</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434523</v>
+        <v>434605</v>
       </c>
       <c r="R11" t="n">
-        <v>6806508</v>
+        <v>6806750</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215875</v>
+        <v>129215847</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1708,10 +1712,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434516</v>
+        <v>434523</v>
       </c>
       <c r="R12" t="n">
-        <v>6806695</v>
+        <v>6806508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215736</v>
+        <v>129215875</v>
       </c>
       <c r="B13" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,21 +1785,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1809,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434605</v>
+        <v>434516</v>
       </c>
       <c r="R13" t="n">
-        <v>6806750</v>
+        <v>6806695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1870,7 +1874,7 @@
         <v>129215813</v>
       </c>
       <c r="B14" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1964,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215795</v>
+        <v>129215903</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>88939</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,31 +1979,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2007,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434758</v>
+        <v>434350</v>
       </c>
       <c r="R15" t="n">
-        <v>6806435</v>
+        <v>6806600</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,6 +2050,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129215893</v>
+        <v>129215757</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2080,21 +2080,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434908</v>
+        <v>434905</v>
       </c>
       <c r="R16" t="n">
-        <v>6806633</v>
+        <v>6806832</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129215890</v>
+        <v>129215893</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434799</v>
+        <v>434908</v>
       </c>
       <c r="R17" t="n">
-        <v>6806670</v>
+        <v>6806633</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2263,53 +2263,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129215766</v>
+        <v>129215890</v>
       </c>
       <c r="B18" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434601</v>
+        <v>434799</v>
       </c>
       <c r="R18" t="n">
-        <v>6806475</v>
+        <v>6806670</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,45 +2360,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129215757</v>
+        <v>129215766</v>
       </c>
       <c r="B19" t="n">
-        <v>79629</v>
+        <v>56917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434905</v>
+        <v>434601</v>
       </c>
       <c r="R19" t="n">
-        <v>6806832</v>
+        <v>6806475</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215877</v>
+        <v>129215800</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,24 +2476,32 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
@@ -2503,7 +2511,7 @@
         <v>434596</v>
       </c>
       <c r="R20" t="n">
-        <v>6806729</v>
+        <v>6806728</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,10 +2570,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215856</v>
+        <v>129215737</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,21 +2581,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2597,10 +2605,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434194</v>
+        <v>434585</v>
       </c>
       <c r="R21" t="n">
-        <v>6806560</v>
+        <v>6806746</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,10 +2667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215878</v>
+        <v>129215877</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2688,19 +2696,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434621</v>
+        <v>434596</v>
       </c>
       <c r="R22" t="n">
-        <v>6806786</v>
+        <v>6806729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2746,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2760,10 +2764,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215859</v>
+        <v>129215856</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2795,10 +2799,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434177</v>
+        <v>434194</v>
       </c>
       <c r="R23" t="n">
-        <v>6806592</v>
+        <v>6806560</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2857,10 +2861,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215737</v>
+        <v>129215735</v>
       </c>
       <c r="B24" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2892,10 +2896,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434585</v>
+        <v>434571</v>
       </c>
       <c r="R24" t="n">
-        <v>6806746</v>
+        <v>6806718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,10 +2958,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215735</v>
+        <v>129215744</v>
       </c>
       <c r="B25" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2983,16 +2987,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434571</v>
+        <v>434950</v>
       </c>
       <c r="R25" t="n">
-        <v>6806718</v>
+        <v>6806749</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,6 +3040,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3051,10 +3059,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215744</v>
+        <v>129215878</v>
       </c>
       <c r="B26" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3062,21 +3070,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3089,10 +3097,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434950</v>
+        <v>434621</v>
       </c>
       <c r="R26" t="n">
-        <v>6806749</v>
+        <v>6806786</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215800</v>
+        <v>129215859</v>
       </c>
       <c r="B27" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3163,42 +3171,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434596</v>
+        <v>434177</v>
       </c>
       <c r="R27" t="n">
-        <v>6806728</v>
+        <v>6806592</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3257,45 +3257,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215758</v>
+        <v>129215782</v>
       </c>
       <c r="B28" t="n">
-        <v>79629</v>
+        <v>56917</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434928</v>
+        <v>434568</v>
       </c>
       <c r="R28" t="n">
-        <v>6806794</v>
+        <v>6806730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3354,32 +3362,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215782</v>
+        <v>129215793</v>
       </c>
       <c r="B29" t="n">
-        <v>56915</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3387,7 +3395,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3397,10 +3405,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434568</v>
+        <v>434920</v>
       </c>
       <c r="R29" t="n">
-        <v>6806730</v>
+        <v>6806792</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3459,10 +3467,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215793</v>
+        <v>129215758</v>
       </c>
       <c r="B30" t="n">
-        <v>57885</v>
+        <v>79631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3470,42 +3478,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434920</v>
+        <v>434928</v>
       </c>
       <c r="R30" t="n">
-        <v>6806792</v>
+        <v>6806794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
         <v>129215780</v>
       </c>
       <c r="B31" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215881</v>
+        <v>129215810</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3680,37 +3680,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434834</v>
+        <v>434908</v>
       </c>
       <c r="R32" t="n">
-        <v>6806837</v>
+        <v>6806733</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,7 +3748,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3770,10 +3766,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215750</v>
+        <v>129215881</v>
       </c>
       <c r="B33" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3781,34 +3777,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434775</v>
+        <v>434834</v>
       </c>
       <c r="R33" t="n">
-        <v>6806482</v>
+        <v>6806837</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3849,6 +3848,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129215810</v>
+        <v>129215750</v>
       </c>
       <c r="B34" t="n">
-        <v>78797</v>
+        <v>79660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434908</v>
+        <v>434775</v>
       </c>
       <c r="R34" t="n">
-        <v>6806733</v>
+        <v>6806482</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129215902</v>
+        <v>129215756</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434784</v>
+        <v>434857</v>
       </c>
       <c r="R35" t="n">
-        <v>6806543</v>
+        <v>6806824</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,11 +4038,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4070,10 +4065,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129215854</v>
+        <v>129215809</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4081,21 +4076,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4105,10 +4100,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434268</v>
+        <v>434843</v>
       </c>
       <c r="R36" t="n">
-        <v>6806557</v>
+        <v>6806853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4167,10 +4162,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129215869</v>
+        <v>129215798</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,34 +4173,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434432</v>
+        <v>434244</v>
       </c>
       <c r="R37" t="n">
-        <v>6806606</v>
+        <v>6806571</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,7 +4270,7 @@
         <v>129215822</v>
       </c>
       <c r="B38" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4364,7 +4367,7 @@
         <v>129215823</v>
       </c>
       <c r="B39" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4458,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129215738</v>
+        <v>129215902</v>
       </c>
       <c r="B40" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4469,34 +4472,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434764</v>
+        <v>434784</v>
       </c>
       <c r="R40" t="n">
-        <v>6806804</v>
+        <v>6806543</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4531,12 +4537,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4555,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215798</v>
+        <v>129215738</v>
       </c>
       <c r="B41" t="n">
-        <v>57722</v>
+        <v>79660</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4566,42 +4578,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434244</v>
+        <v>434764</v>
       </c>
       <c r="R41" t="n">
-        <v>6806571</v>
+        <v>6806804</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4660,10 +4664,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215756</v>
+        <v>129215854</v>
       </c>
       <c r="B42" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4671,37 +4675,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434857</v>
+        <v>434268</v>
       </c>
       <c r="R42" t="n">
-        <v>6806824</v>
+        <v>6806557</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4742,7 +4743,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215809</v>
+        <v>129215869</v>
       </c>
       <c r="B43" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434843</v>
+        <v>434432</v>
       </c>
       <c r="R43" t="n">
-        <v>6806853</v>
+        <v>6806606</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129215882</v>
+        <v>129215799</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,34 +4869,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434851</v>
+        <v>434142</v>
       </c>
       <c r="R44" t="n">
-        <v>6806867</v>
+        <v>6806549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4955,10 +4963,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129215845</v>
+        <v>129215882</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4990,10 +4998,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434585</v>
+        <v>434851</v>
       </c>
       <c r="R45" t="n">
-        <v>6806500</v>
+        <v>6806867</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5052,10 +5060,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215799</v>
+        <v>129215845</v>
       </c>
       <c r="B46" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,42 +5071,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434142</v>
+        <v>434585</v>
       </c>
       <c r="R46" t="n">
-        <v>6806549</v>
+        <v>6806500</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5160,7 +5160,7 @@
         <v>129215753</v>
       </c>
       <c r="B47" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129215857</v>
+        <v>129215755</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434179</v>
+        <v>434812</v>
       </c>
       <c r="R48" t="n">
-        <v>6806557</v>
+        <v>6806771</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215755</v>
+        <v>129215760</v>
       </c>
       <c r="B49" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434812</v>
+        <v>434895</v>
       </c>
       <c r="R49" t="n">
-        <v>6806771</v>
+        <v>6806736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,10 +5448,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215760</v>
+        <v>129215857</v>
       </c>
       <c r="B50" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434895</v>
+        <v>434179</v>
       </c>
       <c r="R50" t="n">
-        <v>6806736</v>
+        <v>6806557</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215808</v>
+        <v>129215904</v>
       </c>
       <c r="B51" t="n">
-        <v>78797</v>
+        <v>79660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434355</v>
+        <v>434857</v>
       </c>
       <c r="R51" t="n">
-        <v>6806519</v>
+        <v>6806833</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5642,45 +5642,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215904</v>
+        <v>129215790</v>
       </c>
       <c r="B52" t="n">
-        <v>79658</v>
+        <v>56917</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434857</v>
+        <v>434809</v>
       </c>
       <c r="R52" t="n">
-        <v>6806833</v>
+        <v>6806535</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5739,10 +5747,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215790</v>
+        <v>129215786</v>
       </c>
       <c r="B53" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5782,10 +5790,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434809</v>
+        <v>434883</v>
       </c>
       <c r="R53" t="n">
-        <v>6806535</v>
+        <v>6806675</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5844,53 +5852,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129215786</v>
+        <v>129215808</v>
       </c>
       <c r="B54" t="n">
-        <v>56915</v>
+        <v>78799</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434883</v>
+        <v>434355</v>
       </c>
       <c r="R54" t="n">
-        <v>6806675</v>
+        <v>6806519</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129215874</v>
+        <v>129215841</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434483</v>
+        <v>434433</v>
       </c>
       <c r="R55" t="n">
-        <v>6806662</v>
+        <v>6806597</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,6 +6028,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6046,10 +6047,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129215896</v>
+        <v>129215874</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6081,10 +6082,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434783</v>
+        <v>434483</v>
       </c>
       <c r="R56" t="n">
-        <v>6806478</v>
+        <v>6806662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6143,10 +6144,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129215841</v>
+        <v>129215896</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6178,10 +6179,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434433</v>
+        <v>434783</v>
       </c>
       <c r="R57" t="n">
-        <v>6806597</v>
+        <v>6806478</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,7 +6223,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>129215781</v>
       </c>
       <c r="B58" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>129215779</v>
       </c>
       <c r="B59" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>129215783</v>
       </c>
       <c r="B60" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215885</v>
+        <v>129215819</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6567,34 +6567,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434884</v>
+        <v>434773</v>
       </c>
       <c r="R61" t="n">
-        <v>6806816</v>
+        <v>6806803</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6635,6 +6638,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6653,10 +6657,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129215862</v>
+        <v>129215880</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6688,10 +6692,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434270</v>
+        <v>434845</v>
       </c>
       <c r="R62" t="n">
-        <v>6806602</v>
+        <v>6806812</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6750,10 +6754,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215819</v>
+        <v>129215739</v>
       </c>
       <c r="B63" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6761,37 +6765,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434773</v>
+        <v>434817</v>
       </c>
       <c r="R63" t="n">
-        <v>6806803</v>
+        <v>6806766</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6832,7 +6833,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6851,10 +6851,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215880</v>
+        <v>129215824</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6862,21 +6862,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434845</v>
+        <v>434922</v>
       </c>
       <c r="R64" t="n">
-        <v>6806812</v>
+        <v>6806746</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215739</v>
+        <v>129215885</v>
       </c>
       <c r="B65" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434817</v>
+        <v>434884</v>
       </c>
       <c r="R65" t="n">
-        <v>6806766</v>
+        <v>6806816</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215824</v>
+        <v>129215743</v>
       </c>
       <c r="B66" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7083,7 +7083,7 @@
         <v>434922</v>
       </c>
       <c r="R66" t="n">
-        <v>6806746</v>
+        <v>6806795</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129215743</v>
+        <v>129215862</v>
       </c>
       <c r="B67" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434922</v>
+        <v>434270</v>
       </c>
       <c r="R67" t="n">
-        <v>6806795</v>
+        <v>6806602</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215895</v>
+        <v>129215742</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7250,34 +7250,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434858</v>
+        <v>434910</v>
       </c>
       <c r="R68" t="n">
-        <v>6806562</v>
+        <v>6806856</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7318,6 +7321,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7336,10 +7340,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129215899</v>
+        <v>129215891</v>
       </c>
       <c r="B69" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7371,10 +7375,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434763</v>
+        <v>434812</v>
       </c>
       <c r="R69" t="n">
-        <v>6806436</v>
+        <v>6806610</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7433,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129215851</v>
+        <v>129215898</v>
       </c>
       <c r="B70" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7468,10 +7472,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434362</v>
+        <v>434759</v>
       </c>
       <c r="R70" t="n">
-        <v>6806519</v>
+        <v>6806455</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7530,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215742</v>
+        <v>129215821</v>
       </c>
       <c r="B71" t="n">
-        <v>79658</v>
+        <v>78798</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7541,37 +7545,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434910</v>
+        <v>434913</v>
       </c>
       <c r="R71" t="n">
-        <v>6806856</v>
+        <v>6806785</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7612,7 +7613,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215891</v>
+        <v>129215895</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7666,10 +7666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434812</v>
+        <v>434858</v>
       </c>
       <c r="R72" t="n">
-        <v>6806610</v>
+        <v>6806562</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129215898</v>
+        <v>129215899</v>
       </c>
       <c r="B73" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434759</v>
+        <v>434763</v>
       </c>
       <c r="R73" t="n">
-        <v>6806455</v>
+        <v>6806436</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215821</v>
+        <v>129215851</v>
       </c>
       <c r="B74" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7836,21 +7836,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434913</v>
+        <v>434362</v>
       </c>
       <c r="R74" t="n">
-        <v>6806785</v>
+        <v>6806519</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7925,7 +7925,7 @@
         <v>129215764</v>
       </c>
       <c r="B75" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>129215807</v>
       </c>
       <c r="B76" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8129,10 +8129,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215887</v>
+        <v>129215801</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8140,34 +8140,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434936</v>
+        <v>434883</v>
       </c>
       <c r="R77" t="n">
-        <v>6806726</v>
+        <v>6806894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8226,10 +8234,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215858</v>
+        <v>129215805</v>
       </c>
       <c r="B78" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8237,34 +8245,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434135</v>
+        <v>434761</v>
       </c>
       <c r="R78" t="n">
-        <v>6806556</v>
+        <v>6806449</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8323,32 +8339,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215801</v>
+        <v>129215773</v>
       </c>
       <c r="B79" t="n">
-        <v>57722</v>
+        <v>56917</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8356,7 +8372,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8366,10 +8382,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434883</v>
+        <v>434241</v>
       </c>
       <c r="R79" t="n">
-        <v>6806894</v>
+        <v>6806606</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8428,10 +8444,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215805</v>
+        <v>129215887</v>
       </c>
       <c r="B80" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8439,42 +8455,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434761</v>
+        <v>434936</v>
       </c>
       <c r="R80" t="n">
-        <v>6806449</v>
+        <v>6806726</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8533,53 +8541,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129215773</v>
+        <v>129215858</v>
       </c>
       <c r="B81" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434241</v>
+        <v>434135</v>
       </c>
       <c r="R81" t="n">
-        <v>6806606</v>
+        <v>6806556</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215886</v>
+        <v>129215803</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8649,34 +8649,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434934</v>
+        <v>434895</v>
       </c>
       <c r="R82" t="n">
-        <v>6806762</v>
+        <v>6806664</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8735,10 +8743,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215863</v>
+        <v>129215804</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8746,34 +8754,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434279</v>
+        <v>434880</v>
       </c>
       <c r="R83" t="n">
-        <v>6806587</v>
+        <v>6806584</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,10 +8848,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215853</v>
+        <v>129215886</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8867,10 +8883,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434280</v>
+        <v>434934</v>
       </c>
       <c r="R84" t="n">
-        <v>6806556</v>
+        <v>6806762</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8929,10 +8945,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215843</v>
+        <v>129215741</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8940,21 +8956,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8964,10 +8980,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434628</v>
+        <v>434844</v>
       </c>
       <c r="R85" t="n">
-        <v>6806457</v>
+        <v>6806852</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9026,10 +9042,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215741</v>
+        <v>129215863</v>
       </c>
       <c r="B86" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9037,21 +9053,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9061,10 +9077,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434844</v>
+        <v>434279</v>
       </c>
       <c r="R86" t="n">
-        <v>6806852</v>
+        <v>6806587</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9123,10 +9139,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215850</v>
+        <v>129215853</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9158,10 +9174,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434376</v>
+        <v>434280</v>
       </c>
       <c r="R87" t="n">
-        <v>6806560</v>
+        <v>6806556</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9220,10 +9236,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215861</v>
+        <v>129215850</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9249,19 +9265,16 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434259</v>
+        <v>434376</v>
       </c>
       <c r="R88" t="n">
-        <v>6806607</v>
+        <v>6806560</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9302,7 +9315,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9321,10 +9333,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215803</v>
+        <v>129215843</v>
       </c>
       <c r="B89" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9332,42 +9344,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434895</v>
+        <v>434628</v>
       </c>
       <c r="R89" t="n">
-        <v>6806664</v>
+        <v>6806457</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9426,10 +9430,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215804</v>
+        <v>129215861</v>
       </c>
       <c r="B90" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9437,31 +9441,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9469,10 +9468,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434880</v>
+        <v>434259</v>
       </c>
       <c r="R90" t="n">
-        <v>6806584</v>
+        <v>6806607</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9513,6 +9512,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>129215771</v>
       </c>
       <c r="B91" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>129215768</v>
       </c>
       <c r="B92" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>129215787</v>
       </c>
       <c r="B93" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>129215774</v>
       </c>
       <c r="B94" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>129215872</v>
       </c>
       <c r="B95" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>129215883</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>129215860</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>129215865</v>
       </c>
       <c r="B98" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10352,53 +10352,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215776</v>
+        <v>129215759</v>
       </c>
       <c r="B99" t="n">
-        <v>56915</v>
+        <v>79631</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434445</v>
+        <v>434930</v>
       </c>
       <c r="R99" t="n">
-        <v>6806699</v>
+        <v>6806768</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10457,10 +10449,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215777</v>
+        <v>129215776</v>
       </c>
       <c r="B100" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10490,7 +10482,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -10500,10 +10492,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434432</v>
+        <v>434445</v>
       </c>
       <c r="R100" t="n">
-        <v>6806670</v>
+        <v>6806699</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10562,10 +10554,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215818</v>
+        <v>129215777</v>
       </c>
       <c r="B101" t="n">
-        <v>58095</v>
+        <v>56917</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10573,21 +10565,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10595,7 +10587,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10605,10 +10597,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434849</v>
+        <v>434432</v>
       </c>
       <c r="R101" t="n">
-        <v>6806700</v>
+        <v>6806670</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10667,45 +10659,53 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215759</v>
+        <v>129215818</v>
       </c>
       <c r="B102" t="n">
-        <v>79629</v>
+        <v>58097</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434930</v>
+        <v>434849</v>
       </c>
       <c r="R102" t="n">
-        <v>6806768</v>
+        <v>6806700</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10764,10 +10764,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215884</v>
+        <v>129215873</v>
       </c>
       <c r="B103" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10799,10 +10799,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434890</v>
+        <v>434463</v>
       </c>
       <c r="R103" t="n">
-        <v>6806827</v>
+        <v>6806664</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10861,10 +10861,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129215825</v>
+        <v>129215884</v>
       </c>
       <c r="B104" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10872,21 +10872,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10896,10 +10896,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434799</v>
+        <v>434890</v>
       </c>
       <c r="R104" t="n">
-        <v>6806687</v>
+        <v>6806827</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129215802</v>
+        <v>129215825</v>
       </c>
       <c r="B105" t="n">
-        <v>57722</v>
+        <v>78798</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10969,42 +10969,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434910</v>
+        <v>434799</v>
       </c>
       <c r="R105" t="n">
-        <v>6806898</v>
+        <v>6806687</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11066,7 +11058,7 @@
         <v>129215784</v>
       </c>
       <c r="B106" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11168,10 +11160,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129215873</v>
+        <v>129215802</v>
       </c>
       <c r="B107" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11179,34 +11171,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>434463</v>
+        <v>434910</v>
       </c>
       <c r="R107" t="n">
-        <v>6806664</v>
+        <v>6806898</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215848</v>
+        <v>129215849</v>
       </c>
       <c r="B108" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434473</v>
+        <v>434437</v>
       </c>
       <c r="R108" t="n">
-        <v>6806453</v>
+        <v>6806501</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11362,10 +11362,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215879</v>
+        <v>129215848</v>
       </c>
       <c r="B109" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434627</v>
+        <v>434473</v>
       </c>
       <c r="R109" t="n">
-        <v>6806787</v>
+        <v>6806453</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11459,10 +11459,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215892</v>
+        <v>129215879</v>
       </c>
       <c r="B110" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11494,10 +11494,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434884</v>
+        <v>434627</v>
       </c>
       <c r="R110" t="n">
-        <v>6806606</v>
+        <v>6806787</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11556,53 +11556,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215765</v>
+        <v>129215892</v>
       </c>
       <c r="B111" t="n">
-        <v>56915</v>
+        <v>79041</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434630</v>
+        <v>434884</v>
       </c>
       <c r="R111" t="n">
-        <v>6806465</v>
+        <v>6806606</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11661,32 +11653,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215769</v>
+        <v>129215794</v>
       </c>
       <c r="B112" t="n">
-        <v>56915</v>
+        <v>57887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11694,7 +11686,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11704,10 +11696,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434382</v>
+        <v>434852</v>
       </c>
       <c r="R112" t="n">
-        <v>6806548</v>
+        <v>6806551</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11766,45 +11758,53 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215849</v>
+        <v>129215765</v>
       </c>
       <c r="B113" t="n">
-        <v>79039</v>
+        <v>56917</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434437</v>
+        <v>434630</v>
       </c>
       <c r="R113" t="n">
-        <v>6806501</v>
+        <v>6806465</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11863,32 +11863,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215794</v>
+        <v>129215769</v>
       </c>
       <c r="B114" t="n">
-        <v>57885</v>
+        <v>56917</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11896,7 +11896,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434852</v>
+        <v>434382</v>
       </c>
       <c r="R114" t="n">
-        <v>6806551</v>
+        <v>6806548</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215900</v>
+        <v>129215797</v>
       </c>
       <c r="B115" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11979,34 +11979,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434775</v>
+        <v>434602</v>
       </c>
       <c r="R115" t="n">
-        <v>6806423</v>
+        <v>6806495</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12065,10 +12073,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215867</v>
+        <v>129215900</v>
       </c>
       <c r="B116" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12100,10 +12108,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434375</v>
+        <v>434775</v>
       </c>
       <c r="R116" t="n">
-        <v>6806574</v>
+        <v>6806423</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12162,10 +12170,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215844</v>
+        <v>129215867</v>
       </c>
       <c r="B117" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12197,10 +12205,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434623</v>
+        <v>434375</v>
       </c>
       <c r="R117" t="n">
-        <v>6806466</v>
+        <v>6806574</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12259,10 +12267,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215868</v>
+        <v>129215734</v>
       </c>
       <c r="B118" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12270,21 +12278,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12294,10 +12302,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434415</v>
+        <v>434546</v>
       </c>
       <c r="R118" t="n">
-        <v>6806576</v>
+        <v>6806737</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12356,10 +12364,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215734</v>
+        <v>129215844</v>
       </c>
       <c r="B119" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12367,21 +12375,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12391,10 +12399,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434546</v>
+        <v>434623</v>
       </c>
       <c r="R119" t="n">
-        <v>6806737</v>
+        <v>6806466</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12453,10 +12461,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215796</v>
+        <v>129215868</v>
       </c>
       <c r="B120" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12464,42 +12472,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434635</v>
+        <v>434415</v>
       </c>
       <c r="R120" t="n">
-        <v>6806453</v>
+        <v>6806576</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12558,10 +12558,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215797</v>
+        <v>129215812</v>
       </c>
       <c r="B121" t="n">
-        <v>57722</v>
+        <v>78799</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,42 +12569,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434602</v>
+        <v>434922</v>
       </c>
       <c r="R121" t="n">
-        <v>6806495</v>
+        <v>6806746</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,10 +12655,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215812</v>
+        <v>129215754</v>
       </c>
       <c r="B122" t="n">
-        <v>78797</v>
+        <v>79631</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12674,21 +12666,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12698,10 +12690,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434922</v>
+        <v>434774</v>
       </c>
       <c r="R122" t="n">
-        <v>6806746</v>
+        <v>6806803</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12760,10 +12752,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215754</v>
+        <v>129215796</v>
       </c>
       <c r="B123" t="n">
-        <v>79629</v>
+        <v>57724</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12771,34 +12763,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434774</v>
+        <v>434635</v>
       </c>
       <c r="R123" t="n">
-        <v>6806803</v>
+        <v>6806453</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12857,10 +12857,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129215901</v>
+        <v>129215852</v>
       </c>
       <c r="B124" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434918</v>
+        <v>434335</v>
       </c>
       <c r="R124" t="n">
-        <v>6806737</v>
+        <v>6806532</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129215745</v>
+        <v>129215901</v>
       </c>
       <c r="B125" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,21 +12965,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434934</v>
+        <v>434918</v>
       </c>
       <c r="R125" t="n">
-        <v>6806753</v>
+        <v>6806737</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13051,10 +13051,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129215752</v>
+        <v>129215889</v>
       </c>
       <c r="B126" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13062,21 +13062,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434263</v>
+        <v>434813</v>
       </c>
       <c r="R126" t="n">
-        <v>6806561</v>
+        <v>6806692</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13148,10 +13148,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129215751</v>
+        <v>129215745</v>
       </c>
       <c r="B127" t="n">
-        <v>79629</v>
+        <v>79660</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13159,21 +13159,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434673</v>
+        <v>434934</v>
       </c>
       <c r="R127" t="n">
-        <v>6806460</v>
+        <v>6806753</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,10 +13245,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129215852</v>
+        <v>129215871</v>
       </c>
       <c r="B128" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434335</v>
+        <v>434443</v>
       </c>
       <c r="R128" t="n">
-        <v>6806532</v>
+        <v>6806595</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129215889</v>
+        <v>129215752</v>
       </c>
       <c r="B129" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13353,21 +13353,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>434813</v>
+        <v>434263</v>
       </c>
       <c r="R129" t="n">
-        <v>6806692</v>
+        <v>6806561</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129215871</v>
+        <v>129215751</v>
       </c>
       <c r="B130" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,21 +13450,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434443</v>
+        <v>434673</v>
       </c>
       <c r="R130" t="n">
-        <v>6806595</v>
+        <v>6806460</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215767</v>
+        <v>129215876</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434546</v>
+        <v>434591</v>
       </c>
       <c r="R2" t="n">
-        <v>6806482</v>
+        <v>6806739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,53 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215775</v>
+        <v>129215864</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434334</v>
+        <v>434319</v>
       </c>
       <c r="R3" t="n">
-        <v>6806593</v>
+        <v>6806589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215770</v>
+        <v>129215767</v>
       </c>
       <c r="B4" t="n">
         <v>56917</v>
@@ -928,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434136</v>
+        <v>434546</v>
       </c>
       <c r="R4" t="n">
-        <v>6806558</v>
+        <v>6806482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,45 +974,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215876</v>
+        <v>129215775</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434591</v>
+        <v>434334</v>
       </c>
       <c r="R5" t="n">
-        <v>6806739</v>
+        <v>6806593</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,45 +1079,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215864</v>
+        <v>129215770</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434319</v>
+        <v>434136</v>
       </c>
       <c r="R6" t="n">
-        <v>6806589</v>
+        <v>6806558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129215846</v>
+        <v>129215888</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434523</v>
+        <v>434913</v>
       </c>
       <c r="R8" t="n">
-        <v>6806496</v>
+        <v>6806699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129215888</v>
+        <v>129215846</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434913</v>
+        <v>434523</v>
       </c>
       <c r="R9" t="n">
-        <v>6806699</v>
+        <v>6806496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215795</v>
+        <v>129215903</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>88939</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,31 +1486,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1518,10 +1513,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434758</v>
+        <v>434350</v>
       </c>
       <c r="R10" t="n">
-        <v>6806435</v>
+        <v>6806600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,6 +1557,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1580,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215736</v>
+        <v>129215847</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1615,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434605</v>
+        <v>434523</v>
       </c>
       <c r="R11" t="n">
-        <v>6806750</v>
+        <v>6806508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1677,7 +1673,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215847</v>
+        <v>129215875</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1712,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434523</v>
+        <v>434516</v>
       </c>
       <c r="R12" t="n">
-        <v>6806508</v>
+        <v>6806695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1774,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215875</v>
+        <v>129215736</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1781,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434516</v>
+        <v>434605</v>
       </c>
       <c r="R13" t="n">
-        <v>6806695</v>
+        <v>6806750</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1871,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129215813</v>
+        <v>129215795</v>
       </c>
       <c r="B14" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,34 +1878,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434803</v>
+        <v>434758</v>
       </c>
       <c r="R14" t="n">
-        <v>6806683</v>
+        <v>6806435</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1968,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215903</v>
+        <v>129215813</v>
       </c>
       <c r="B15" t="n">
-        <v>88939</v>
+        <v>78799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,37 +1983,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434350</v>
+        <v>434803</v>
       </c>
       <c r="R15" t="n">
-        <v>6806600</v>
+        <v>6806683</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2050,7 +2051,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2069,45 +2069,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129215757</v>
+        <v>129215766</v>
       </c>
       <c r="B16" t="n">
-        <v>79631</v>
+        <v>56917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434905</v>
+        <v>434601</v>
       </c>
       <c r="R16" t="n">
-        <v>6806832</v>
+        <v>6806475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,10 +2174,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129215893</v>
+        <v>129215757</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,21 +2185,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2201,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434908</v>
+        <v>434905</v>
       </c>
       <c r="R17" t="n">
-        <v>6806633</v>
+        <v>6806832</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,53 +2368,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129215766</v>
+        <v>129215893</v>
       </c>
       <c r="B19" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434601</v>
+        <v>434908</v>
       </c>
       <c r="R19" t="n">
-        <v>6806475</v>
+        <v>6806633</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215800</v>
+        <v>129215737</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,42 +2476,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434596</v>
+        <v>434585</v>
       </c>
       <c r="R20" t="n">
-        <v>6806728</v>
+        <v>6806746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2570,7 +2562,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215737</v>
+        <v>129215744</v>
       </c>
       <c r="B21" t="n">
         <v>79660</v>
@@ -2599,16 +2591,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434585</v>
+        <v>434950</v>
       </c>
       <c r="R21" t="n">
-        <v>6806746</v>
+        <v>6806749</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2644,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2764,10 +2760,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215856</v>
+        <v>129215735</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2775,21 +2771,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2799,10 +2795,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434194</v>
+        <v>434571</v>
       </c>
       <c r="R23" t="n">
-        <v>6806560</v>
+        <v>6806718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2861,10 +2857,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215735</v>
+        <v>129215856</v>
       </c>
       <c r="B24" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2872,21 +2868,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2896,10 +2892,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434571</v>
+        <v>434194</v>
       </c>
       <c r="R24" t="n">
-        <v>6806718</v>
+        <v>6806560</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2958,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215744</v>
+        <v>129215878</v>
       </c>
       <c r="B25" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2969,21 +2965,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2996,10 +2992,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434950</v>
+        <v>434621</v>
       </c>
       <c r="R25" t="n">
-        <v>6806749</v>
+        <v>6806786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,7 +3055,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215878</v>
+        <v>129215859</v>
       </c>
       <c r="B26" t="n">
         <v>79041</v>
@@ -3088,19 +3084,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434621</v>
+        <v>434177</v>
       </c>
       <c r="R26" t="n">
-        <v>6806786</v>
+        <v>6806592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3141,7 +3134,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3160,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215859</v>
+        <v>129215800</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3171,34 +3163,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434177</v>
+        <v>434596</v>
       </c>
       <c r="R27" t="n">
-        <v>6806592</v>
+        <v>6806728</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3564,53 +3564,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215780</v>
+        <v>129215750</v>
       </c>
       <c r="B31" t="n">
-        <v>56917</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434449</v>
+        <v>434775</v>
       </c>
       <c r="R31" t="n">
-        <v>6806667</v>
+        <v>6806482</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3669,10 +3661,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215810</v>
+        <v>129215881</v>
       </c>
       <c r="B32" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3680,34 +3672,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434908</v>
+        <v>434834</v>
       </c>
       <c r="R32" t="n">
-        <v>6806733</v>
+        <v>6806837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3748,6 +3743,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3766,37 +3762,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215881</v>
+        <v>129215780</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3804,10 +3805,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434834</v>
+        <v>434449</v>
       </c>
       <c r="R33" t="n">
-        <v>6806837</v>
+        <v>6806667</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,7 +3849,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129215750</v>
+        <v>129215810</v>
       </c>
       <c r="B34" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3878,21 +3878,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434775</v>
+        <v>434908</v>
       </c>
       <c r="R34" t="n">
-        <v>6806482</v>
+        <v>6806733</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129215756</v>
+        <v>129215854</v>
       </c>
       <c r="B35" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3975,37 +3975,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434857</v>
+        <v>434268</v>
       </c>
       <c r="R35" t="n">
-        <v>6806824</v>
+        <v>6806557</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4046,7 +4043,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4065,10 +4061,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129215809</v>
+        <v>129215902</v>
       </c>
       <c r="B36" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4076,34 +4072,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434843</v>
+        <v>434784</v>
       </c>
       <c r="R36" t="n">
-        <v>6806853</v>
+        <v>6806543</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4138,12 +4137,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4162,10 +4167,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129215798</v>
+        <v>129215738</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4173,42 +4178,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434244</v>
+        <v>434764</v>
       </c>
       <c r="R37" t="n">
-        <v>6806571</v>
+        <v>6806804</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4267,7 +4264,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129215822</v>
+        <v>129215823</v>
       </c>
       <c r="B38" t="n">
         <v>78798</v>
@@ -4302,10 +4299,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434936</v>
+        <v>434906</v>
       </c>
       <c r="R38" t="n">
-        <v>6806756</v>
+        <v>6806734</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4364,10 +4361,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129215823</v>
+        <v>129215869</v>
       </c>
       <c r="B39" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,21 +4372,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4399,10 +4396,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434906</v>
+        <v>434432</v>
       </c>
       <c r="R39" t="n">
-        <v>6806734</v>
+        <v>6806606</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4461,10 +4458,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129215902</v>
+        <v>129215822</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,37 +4469,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434784</v>
+        <v>434936</v>
       </c>
       <c r="R40" t="n">
-        <v>6806543</v>
+        <v>6806756</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4537,18 +4531,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4567,10 +4555,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215738</v>
+        <v>129215798</v>
       </c>
       <c r="B41" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,34 +4566,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434764</v>
+        <v>434244</v>
       </c>
       <c r="R41" t="n">
-        <v>6806804</v>
+        <v>6806571</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4664,10 +4660,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215854</v>
+        <v>129215756</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,34 +4671,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434268</v>
+        <v>434857</v>
       </c>
       <c r="R42" t="n">
-        <v>6806557</v>
+        <v>6806824</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,6 +4742,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215869</v>
+        <v>129215809</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,21 +4772,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434432</v>
+        <v>434843</v>
       </c>
       <c r="R43" t="n">
-        <v>6806606</v>
+        <v>6806853</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129215799</v>
+        <v>129215882</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,42 +4869,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434142</v>
+        <v>434851</v>
       </c>
       <c r="R44" t="n">
-        <v>6806549</v>
+        <v>6806867</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,7 +4955,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129215882</v>
+        <v>129215845</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -4998,10 +4990,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434851</v>
+        <v>434585</v>
       </c>
       <c r="R45" t="n">
-        <v>6806867</v>
+        <v>6806500</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5060,10 +5052,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215845</v>
+        <v>129215799</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5071,34 +5063,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434585</v>
+        <v>434142</v>
       </c>
       <c r="R46" t="n">
-        <v>6806500</v>
+        <v>6806549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129215755</v>
+        <v>129215857</v>
       </c>
       <c r="B48" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434812</v>
+        <v>434179</v>
       </c>
       <c r="R48" t="n">
-        <v>6806771</v>
+        <v>6806557</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215760</v>
+        <v>129215904</v>
       </c>
       <c r="B49" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434895</v>
+        <v>434857</v>
       </c>
       <c r="R49" t="n">
-        <v>6806736</v>
+        <v>6806833</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,45 +5448,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215857</v>
+        <v>129215790</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434179</v>
+        <v>434809</v>
       </c>
       <c r="R50" t="n">
-        <v>6806557</v>
+        <v>6806535</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5545,45 +5553,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215904</v>
+        <v>129215786</v>
       </c>
       <c r="B51" t="n">
-        <v>79660</v>
+        <v>56917</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434857</v>
+        <v>434883</v>
       </c>
       <c r="R51" t="n">
-        <v>6806833</v>
+        <v>6806675</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5642,53 +5658,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215790</v>
+        <v>129215755</v>
       </c>
       <c r="B52" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434809</v>
+        <v>434812</v>
       </c>
       <c r="R52" t="n">
-        <v>6806535</v>
+        <v>6806771</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5747,53 +5755,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215786</v>
+        <v>129215760</v>
       </c>
       <c r="B53" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434883</v>
+        <v>434895</v>
       </c>
       <c r="R53" t="n">
-        <v>6806675</v>
+        <v>6806736</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129215841</v>
+        <v>129215896</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434433</v>
+        <v>434783</v>
       </c>
       <c r="R55" t="n">
-        <v>6806597</v>
+        <v>6806478</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,7 +6028,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6144,7 +6143,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129215896</v>
+        <v>129215841</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6179,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434783</v>
+        <v>434433</v>
       </c>
       <c r="R57" t="n">
-        <v>6806478</v>
+        <v>6806597</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6223,6 +6222,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6556,7 +6556,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215819</v>
+        <v>129215824</v>
       </c>
       <c r="B61" t="n">
         <v>78798</v>
@@ -6585,19 +6585,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434773</v>
+        <v>434922</v>
       </c>
       <c r="R61" t="n">
-        <v>6806803</v>
+        <v>6806746</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6638,7 +6635,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6754,10 +6750,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215739</v>
+        <v>129215819</v>
       </c>
       <c r="B63" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6765,34 +6761,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434817</v>
+        <v>434773</v>
       </c>
       <c r="R63" t="n">
-        <v>6806766</v>
+        <v>6806803</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6833,6 +6832,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6851,10 +6851,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215824</v>
+        <v>129215862</v>
       </c>
       <c r="B64" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6862,21 +6862,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434922</v>
+        <v>434270</v>
       </c>
       <c r="R64" t="n">
-        <v>6806746</v>
+        <v>6806602</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215885</v>
+        <v>129215739</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434884</v>
+        <v>434817</v>
       </c>
       <c r="R65" t="n">
-        <v>6806816</v>
+        <v>6806766</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215743</v>
+        <v>129215885</v>
       </c>
       <c r="B66" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434922</v>
+        <v>434884</v>
       </c>
       <c r="R66" t="n">
-        <v>6806795</v>
+        <v>6806816</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129215862</v>
+        <v>129215743</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434270</v>
+        <v>434922</v>
       </c>
       <c r="R67" t="n">
-        <v>6806602</v>
+        <v>6806795</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7239,37 +7239,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215742</v>
+        <v>129215807</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>97555</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7277,10 +7278,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434910</v>
+        <v>434541</v>
       </c>
       <c r="R68" t="n">
-        <v>6806856</v>
+        <v>6806479</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7534,10 +7535,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215821</v>
+        <v>129215742</v>
       </c>
       <c r="B71" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,34 +7546,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434913</v>
+        <v>434910</v>
       </c>
       <c r="R71" t="n">
-        <v>6806785</v>
+        <v>6806856</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7613,6 +7617,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7631,10 +7636,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215895</v>
+        <v>129215821</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,21 +7647,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7666,10 +7671,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434858</v>
+        <v>434913</v>
       </c>
       <c r="R72" t="n">
-        <v>6806562</v>
+        <v>6806785</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7825,7 +7830,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215851</v>
+        <v>129215895</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -7860,10 +7865,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434362</v>
+        <v>434858</v>
       </c>
       <c r="R74" t="n">
-        <v>6806519</v>
+        <v>6806562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7922,53 +7927,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215764</v>
+        <v>129215851</v>
       </c>
       <c r="B75" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434687</v>
+        <v>434362</v>
       </c>
       <c r="R75" t="n">
-        <v>6806459</v>
+        <v>6806519</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8027,10 +8024,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215807</v>
+        <v>129215764</v>
       </c>
       <c r="B76" t="n">
-        <v>97555</v>
+        <v>56917</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8038,27 +8035,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8066,10 +8067,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434541</v>
+        <v>434687</v>
       </c>
       <c r="R76" t="n">
-        <v>6806479</v>
+        <v>6806459</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8110,7 +8111,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8339,53 +8339,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215773</v>
+        <v>129215858</v>
       </c>
       <c r="B79" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434241</v>
+        <v>434135</v>
       </c>
       <c r="R79" t="n">
-        <v>6806606</v>
+        <v>6806556</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8541,45 +8533,53 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129215858</v>
+        <v>129215773</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434135</v>
+        <v>434241</v>
       </c>
       <c r="R81" t="n">
-        <v>6806556</v>
+        <v>6806606</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215803</v>
+        <v>129215843</v>
       </c>
       <c r="B82" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8649,42 +8649,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434895</v>
+        <v>434628</v>
       </c>
       <c r="R82" t="n">
-        <v>6806664</v>
+        <v>6806457</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8743,10 +8735,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215804</v>
+        <v>129215850</v>
       </c>
       <c r="B83" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8754,42 +8746,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434880</v>
+        <v>434376</v>
       </c>
       <c r="R83" t="n">
-        <v>6806584</v>
+        <v>6806560</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8848,10 +8832,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215886</v>
+        <v>129215741</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8859,21 +8843,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8883,10 +8867,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434934</v>
+        <v>434844</v>
       </c>
       <c r="R84" t="n">
-        <v>6806762</v>
+        <v>6806852</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8945,10 +8929,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215741</v>
+        <v>129215853</v>
       </c>
       <c r="B85" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8956,21 +8940,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8980,10 +8964,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434844</v>
+        <v>434280</v>
       </c>
       <c r="R85" t="n">
-        <v>6806852</v>
+        <v>6806556</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9042,7 +9026,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215863</v>
+        <v>129215861</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9071,16 +9055,19 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434279</v>
+        <v>434259</v>
       </c>
       <c r="R86" t="n">
-        <v>6806587</v>
+        <v>6806607</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9121,6 +9108,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9139,7 +9127,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215853</v>
+        <v>129215886</v>
       </c>
       <c r="B87" t="n">
         <v>79041</v>
@@ -9174,10 +9162,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434280</v>
+        <v>434934</v>
       </c>
       <c r="R87" t="n">
-        <v>6806556</v>
+        <v>6806762</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9236,7 +9224,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215850</v>
+        <v>129215863</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -9271,10 +9259,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434376</v>
+        <v>434279</v>
       </c>
       <c r="R88" t="n">
-        <v>6806560</v>
+        <v>6806587</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9333,10 +9321,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215843</v>
+        <v>129215803</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9344,34 +9332,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434628</v>
+        <v>434895</v>
       </c>
       <c r="R89" t="n">
-        <v>6806457</v>
+        <v>6806664</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9430,10 +9426,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215861</v>
+        <v>129215804</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9441,26 +9437,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -9468,10 +9469,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434259</v>
+        <v>434880</v>
       </c>
       <c r="R90" t="n">
-        <v>6806607</v>
+        <v>6806584</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9512,7 +9513,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10158,7 +10158,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129215860</v>
+        <v>129215865</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434241</v>
+        <v>434358</v>
       </c>
       <c r="R97" t="n">
-        <v>6806618</v>
+        <v>6806608</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10255,7 +10255,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215865</v>
+        <v>129215860</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10290,10 +10290,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434358</v>
+        <v>434241</v>
       </c>
       <c r="R98" t="n">
-        <v>6806608</v>
+        <v>6806618</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10352,45 +10352,53 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215759</v>
+        <v>129215818</v>
       </c>
       <c r="B99" t="n">
-        <v>79631</v>
+        <v>58097</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434930</v>
+        <v>434849</v>
       </c>
       <c r="R99" t="n">
-        <v>6806768</v>
+        <v>6806700</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,53 +10457,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215776</v>
+        <v>129215759</v>
       </c>
       <c r="B100" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434445</v>
+        <v>434930</v>
       </c>
       <c r="R100" t="n">
-        <v>6806699</v>
+        <v>6806768</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10554,7 +10554,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215777</v>
+        <v>129215776</v>
       </c>
       <c r="B101" t="n">
         <v>56917</v>
@@ -10587,7 +10587,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10597,10 +10597,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434432</v>
+        <v>434445</v>
       </c>
       <c r="R101" t="n">
-        <v>6806670</v>
+        <v>6806699</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10659,10 +10659,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215818</v>
+        <v>129215777</v>
       </c>
       <c r="B102" t="n">
-        <v>58097</v>
+        <v>56917</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10670,21 +10670,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10692,7 +10692,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -10702,10 +10702,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434849</v>
+        <v>434432</v>
       </c>
       <c r="R102" t="n">
-        <v>6806700</v>
+        <v>6806670</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10764,7 +10764,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215873</v>
+        <v>129215884</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -10799,10 +10799,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434463</v>
+        <v>434890</v>
       </c>
       <c r="R103" t="n">
-        <v>6806664</v>
+        <v>6806827</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10861,7 +10861,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129215884</v>
+        <v>129215873</v>
       </c>
       <c r="B104" t="n">
         <v>79041</v>
@@ -10896,10 +10896,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434890</v>
+        <v>434463</v>
       </c>
       <c r="R104" t="n">
-        <v>6806827</v>
+        <v>6806664</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11055,32 +11055,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129215784</v>
+        <v>129215802</v>
       </c>
       <c r="B106" t="n">
-        <v>56917</v>
+        <v>57724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11088,7 +11088,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -11098,10 +11098,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>434853</v>
+        <v>434910</v>
       </c>
       <c r="R106" t="n">
-        <v>6806697</v>
+        <v>6806898</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11160,32 +11160,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129215802</v>
+        <v>129215784</v>
       </c>
       <c r="B107" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11193,7 +11193,7 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -11203,10 +11203,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>434910</v>
+        <v>434853</v>
       </c>
       <c r="R107" t="n">
-        <v>6806898</v>
+        <v>6806697</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11265,7 +11265,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215849</v>
+        <v>129215848</v>
       </c>
       <c r="B108" t="n">
         <v>79041</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434437</v>
+        <v>434473</v>
       </c>
       <c r="R108" t="n">
-        <v>6806501</v>
+        <v>6806453</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11362,7 +11362,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215848</v>
+        <v>129215879</v>
       </c>
       <c r="B109" t="n">
         <v>79041</v>
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434473</v>
+        <v>434627</v>
       </c>
       <c r="R109" t="n">
-        <v>6806453</v>
+        <v>6806787</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11459,7 +11459,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215879</v>
+        <v>129215849</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11494,10 +11494,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434627</v>
+        <v>434437</v>
       </c>
       <c r="R110" t="n">
-        <v>6806787</v>
+        <v>6806501</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11653,32 +11653,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215794</v>
+        <v>129215765</v>
       </c>
       <c r="B112" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11686,7 +11686,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -11696,10 +11696,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434852</v>
+        <v>434630</v>
       </c>
       <c r="R112" t="n">
-        <v>6806551</v>
+        <v>6806465</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11758,7 +11758,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215765</v>
+        <v>129215769</v>
       </c>
       <c r="B113" t="n">
         <v>56917</v>
@@ -11801,10 +11801,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434630</v>
+        <v>434382</v>
       </c>
       <c r="R113" t="n">
-        <v>6806465</v>
+        <v>6806548</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11863,32 +11863,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215769</v>
+        <v>129215794</v>
       </c>
       <c r="B114" t="n">
-        <v>56917</v>
+        <v>57887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11896,7 +11896,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434382</v>
+        <v>434852</v>
       </c>
       <c r="R114" t="n">
-        <v>6806548</v>
+        <v>6806551</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215797</v>
+        <v>129215844</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11979,42 +11979,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434602</v>
+        <v>434623</v>
       </c>
       <c r="R115" t="n">
-        <v>6806495</v>
+        <v>6806466</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12073,10 +12065,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215900</v>
+        <v>129215734</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12084,21 +12076,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12108,10 +12100,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434775</v>
+        <v>434546</v>
       </c>
       <c r="R116" t="n">
-        <v>6806423</v>
+        <v>6806737</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12170,7 +12162,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215867</v>
+        <v>129215868</v>
       </c>
       <c r="B117" t="n">
         <v>79041</v>
@@ -12205,10 +12197,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434375</v>
+        <v>434415</v>
       </c>
       <c r="R117" t="n">
-        <v>6806574</v>
+        <v>6806576</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12267,10 +12259,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215734</v>
+        <v>129215900</v>
       </c>
       <c r="B118" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12278,21 +12270,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12302,10 +12294,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434546</v>
+        <v>434775</v>
       </c>
       <c r="R118" t="n">
-        <v>6806737</v>
+        <v>6806423</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12364,7 +12356,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215844</v>
+        <v>129215867</v>
       </c>
       <c r="B119" t="n">
         <v>79041</v>
@@ -12399,10 +12391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434623</v>
+        <v>434375</v>
       </c>
       <c r="R119" t="n">
-        <v>6806466</v>
+        <v>6806574</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12461,10 +12453,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215868</v>
+        <v>129215796</v>
       </c>
       <c r="B120" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12472,34 +12464,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434415</v>
+        <v>434635</v>
       </c>
       <c r="R120" t="n">
-        <v>6806576</v>
+        <v>6806453</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12558,10 +12558,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215812</v>
+        <v>129215797</v>
       </c>
       <c r="B121" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,34 +12569,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434922</v>
+        <v>434602</v>
       </c>
       <c r="R121" t="n">
-        <v>6806746</v>
+        <v>6806495</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12655,10 +12663,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215754</v>
+        <v>129215812</v>
       </c>
       <c r="B122" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12666,21 +12674,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12690,10 +12698,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434774</v>
+        <v>434922</v>
       </c>
       <c r="R122" t="n">
-        <v>6806803</v>
+        <v>6806746</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12752,10 +12760,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215796</v>
+        <v>129215754</v>
       </c>
       <c r="B123" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12763,42 +12771,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434635</v>
+        <v>434774</v>
       </c>
       <c r="R123" t="n">
-        <v>6806453</v>
+        <v>6806803</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12857,7 +12857,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129215852</v>
+        <v>129215901</v>
       </c>
       <c r="B124" t="n">
         <v>79041</v>
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434335</v>
+        <v>434918</v>
       </c>
       <c r="R124" t="n">
-        <v>6806532</v>
+        <v>6806737</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129215901</v>
+        <v>129215745</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,21 +12965,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434918</v>
+        <v>434934</v>
       </c>
       <c r="R125" t="n">
-        <v>6806737</v>
+        <v>6806753</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13051,7 +13051,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129215889</v>
+        <v>129215871</v>
       </c>
       <c r="B126" t="n">
         <v>79041</v>
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434813</v>
+        <v>434443</v>
       </c>
       <c r="R126" t="n">
-        <v>6806692</v>
+        <v>6806595</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13148,10 +13148,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129215745</v>
+        <v>129215852</v>
       </c>
       <c r="B127" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13159,21 +13159,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434934</v>
+        <v>434335</v>
       </c>
       <c r="R127" t="n">
-        <v>6806753</v>
+        <v>6806532</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,7 +13245,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129215871</v>
+        <v>129215889</v>
       </c>
       <c r="B128" t="n">
         <v>79041</v>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434443</v>
+        <v>434813</v>
       </c>
       <c r="R128" t="n">
-        <v>6806595</v>
+        <v>6806692</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215876</v>
+        <v>129215767</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434591</v>
+        <v>434546</v>
       </c>
       <c r="R2" t="n">
-        <v>6806739</v>
+        <v>6806482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +780,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215864</v>
+        <v>129215775</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434319</v>
+        <v>434334</v>
       </c>
       <c r="R3" t="n">
-        <v>6806589</v>
+        <v>6806593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +885,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215767</v>
+        <v>129215770</v>
       </c>
       <c r="B4" t="n">
         <v>56917</v>
@@ -912,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434546</v>
+        <v>434136</v>
       </c>
       <c r="R4" t="n">
-        <v>6806482</v>
+        <v>6806558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,53 +990,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215775</v>
+        <v>129215761</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434334</v>
+        <v>434924</v>
       </c>
       <c r="R5" t="n">
-        <v>6806593</v>
+        <v>6806749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,53 +1087,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215770</v>
+        <v>129215876</v>
       </c>
       <c r="B6" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434136</v>
+        <v>434591</v>
       </c>
       <c r="R6" t="n">
-        <v>6806558</v>
+        <v>6806739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215761</v>
+        <v>129215864</v>
       </c>
       <c r="B7" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434924</v>
+        <v>434319</v>
       </c>
       <c r="R7" t="n">
-        <v>6806749</v>
+        <v>6806589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215903</v>
+        <v>129215813</v>
       </c>
       <c r="B10" t="n">
-        <v>88939</v>
+        <v>78799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,37 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434350</v>
+        <v>434803</v>
       </c>
       <c r="R10" t="n">
-        <v>6806600</v>
+        <v>6806683</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1554,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1576,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215847</v>
+        <v>129215903</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>88939</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,34 +1583,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434523</v>
+        <v>434350</v>
       </c>
       <c r="R11" t="n">
-        <v>6806508</v>
+        <v>6806600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,6 +1654,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215875</v>
+        <v>129215847</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434516</v>
+        <v>434523</v>
       </c>
       <c r="R12" t="n">
-        <v>6806695</v>
+        <v>6806508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215736</v>
+        <v>129215875</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434605</v>
+        <v>434516</v>
       </c>
       <c r="R13" t="n">
-        <v>6806750</v>
+        <v>6806695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129215795</v>
+        <v>129215736</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,42 +1878,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434758</v>
+        <v>434605</v>
       </c>
       <c r="R14" t="n">
-        <v>6806435</v>
+        <v>6806750</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1972,10 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215813</v>
+        <v>129215795</v>
       </c>
       <c r="B15" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,34 +1975,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434803</v>
+        <v>434758</v>
       </c>
       <c r="R15" t="n">
-        <v>6806683</v>
+        <v>6806435</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,53 +2069,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129215766</v>
+        <v>129215890</v>
       </c>
       <c r="B16" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434601</v>
+        <v>434799</v>
       </c>
       <c r="R16" t="n">
-        <v>6806475</v>
+        <v>6806670</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,10 +2166,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129215757</v>
+        <v>129215893</v>
       </c>
       <c r="B17" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,21 +2177,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2209,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434905</v>
+        <v>434908</v>
       </c>
       <c r="R17" t="n">
-        <v>6806832</v>
+        <v>6806633</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,45 +2263,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129215890</v>
+        <v>129215766</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434799</v>
+        <v>434601</v>
       </c>
       <c r="R18" t="n">
-        <v>6806670</v>
+        <v>6806475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129215893</v>
+        <v>129215757</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434908</v>
+        <v>434905</v>
       </c>
       <c r="R19" t="n">
-        <v>6806633</v>
+        <v>6806832</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215737</v>
+        <v>129215793</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,34 +2476,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434585</v>
+        <v>434920</v>
       </c>
       <c r="R20" t="n">
-        <v>6806746</v>
+        <v>6806792</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,10 +2570,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215744</v>
+        <v>129215758</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,37 +2581,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434950</v>
+        <v>434928</v>
       </c>
       <c r="R21" t="n">
-        <v>6806749</v>
+        <v>6806794</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,7 +2649,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2667,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215877</v>
+        <v>129215737</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2674,21 +2678,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2698,10 +2702,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434596</v>
+        <v>434585</v>
       </c>
       <c r="R22" t="n">
-        <v>6806729</v>
+        <v>6806746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2760,7 +2764,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215735</v>
+        <v>129215744</v>
       </c>
       <c r="B23" t="n">
         <v>79660</v>
@@ -2789,16 +2793,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434571</v>
+        <v>434950</v>
       </c>
       <c r="R23" t="n">
-        <v>6806718</v>
+        <v>6806749</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,6 +2846,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2857,7 +2865,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215856</v>
+        <v>129215877</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -2892,10 +2900,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434194</v>
+        <v>434596</v>
       </c>
       <c r="R24" t="n">
-        <v>6806560</v>
+        <v>6806729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,10 +2962,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215878</v>
+        <v>129215735</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2965,37 +2973,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434621</v>
+        <v>434571</v>
       </c>
       <c r="R25" t="n">
-        <v>6806786</v>
+        <v>6806718</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3036,7 +3041,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3055,7 +3059,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215859</v>
+        <v>129215856</v>
       </c>
       <c r="B26" t="n">
         <v>79041</v>
@@ -3090,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434177</v>
+        <v>434194</v>
       </c>
       <c r="R26" t="n">
-        <v>6806592</v>
+        <v>6806560</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3152,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215800</v>
+        <v>129215878</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3163,31 +3167,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3195,10 +3194,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434596</v>
+        <v>434621</v>
       </c>
       <c r="R27" t="n">
-        <v>6806728</v>
+        <v>6806786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3239,6 +3238,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3257,53 +3257,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215782</v>
+        <v>129215859</v>
       </c>
       <c r="B28" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434568</v>
+        <v>434177</v>
       </c>
       <c r="R28" t="n">
-        <v>6806730</v>
+        <v>6806592</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3362,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215793</v>
+        <v>129215800</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3373,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3395,7 +3387,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3405,10 +3397,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434920</v>
+        <v>434596</v>
       </c>
       <c r="R29" t="n">
-        <v>6806792</v>
+        <v>6806728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3467,45 +3459,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215758</v>
+        <v>129215782</v>
       </c>
       <c r="B30" t="n">
-        <v>79631</v>
+        <v>56917</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434928</v>
+        <v>434568</v>
       </c>
       <c r="R30" t="n">
-        <v>6806794</v>
+        <v>6806730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215798</v>
+        <v>129215756</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4566,31 +4566,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4598,10 +4593,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434244</v>
+        <v>434857</v>
       </c>
       <c r="R41" t="n">
-        <v>6806571</v>
+        <v>6806824</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4642,6 +4637,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4660,10 +4656,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215756</v>
+        <v>129215809</v>
       </c>
       <c r="B42" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4671,37 +4667,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434857</v>
+        <v>434843</v>
       </c>
       <c r="R42" t="n">
-        <v>6806824</v>
+        <v>6806853</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4742,7 +4735,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4761,10 +4753,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215809</v>
+        <v>129215798</v>
       </c>
       <c r="B43" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,34 +4764,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434843</v>
+        <v>434244</v>
       </c>
       <c r="R43" t="n">
-        <v>6806853</v>
+        <v>6806571</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215807</v>
+        <v>129215764</v>
       </c>
       <c r="B68" t="n">
-        <v>97555</v>
+        <v>56917</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7250,27 +7250,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7278,10 +7282,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434541</v>
+        <v>434687</v>
       </c>
       <c r="R68" t="n">
-        <v>6806479</v>
+        <v>6806459</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7322,7 +7326,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8024,10 +8027,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215764</v>
+        <v>129215807</v>
       </c>
       <c r="B76" t="n">
-        <v>56917</v>
+        <v>97555</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8035,31 +8038,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8067,10 +8066,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434687</v>
+        <v>434541</v>
       </c>
       <c r="R76" t="n">
-        <v>6806459</v>
+        <v>6806479</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8111,6 +8110,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8129,10 +8129,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215801</v>
+        <v>129215858</v>
       </c>
       <c r="B77" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8140,42 +8140,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434883</v>
+        <v>434135</v>
       </c>
       <c r="R77" t="n">
-        <v>6806894</v>
+        <v>6806556</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8234,10 +8226,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215805</v>
+        <v>129215887</v>
       </c>
       <c r="B78" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8245,42 +8237,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434761</v>
+        <v>434936</v>
       </c>
       <c r="R78" t="n">
-        <v>6806449</v>
+        <v>6806726</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8339,10 +8323,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215858</v>
+        <v>129215801</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8350,34 +8334,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434135</v>
+        <v>434883</v>
       </c>
       <c r="R79" t="n">
-        <v>6806556</v>
+        <v>6806894</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8436,10 +8428,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215887</v>
+        <v>129215805</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8447,34 +8439,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434936</v>
+        <v>434761</v>
       </c>
       <c r="R80" t="n">
-        <v>6806726</v>
+        <v>6806449</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9321,32 +9321,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215803</v>
+        <v>129215771</v>
       </c>
       <c r="B89" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9354,7 +9354,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434895</v>
+        <v>434229</v>
       </c>
       <c r="R89" t="n">
-        <v>6806664</v>
+        <v>6806613</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9426,32 +9426,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215804</v>
+        <v>129215768</v>
       </c>
       <c r="B90" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9459,7 +9459,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -9469,10 +9469,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434880</v>
+        <v>434422</v>
       </c>
       <c r="R90" t="n">
-        <v>6806584</v>
+        <v>6806522</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9531,7 +9531,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215771</v>
+        <v>129215787</v>
       </c>
       <c r="B91" t="n">
         <v>56917</v>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434229</v>
+        <v>434813</v>
       </c>
       <c r="R91" t="n">
-        <v>6806613</v>
+        <v>6806656</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9636,7 +9636,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215768</v>
+        <v>129215774</v>
       </c>
       <c r="B92" t="n">
         <v>56917</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434422</v>
+        <v>434307</v>
       </c>
       <c r="R92" t="n">
-        <v>6806522</v>
+        <v>6806608</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9741,32 +9741,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215787</v>
+        <v>129215803</v>
       </c>
       <c r="B93" t="n">
-        <v>56917</v>
+        <v>57724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434813</v>
+        <v>434895</v>
       </c>
       <c r="R93" t="n">
-        <v>6806656</v>
+        <v>6806664</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,32 +9846,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215774</v>
+        <v>129215804</v>
       </c>
       <c r="B94" t="n">
-        <v>56917</v>
+        <v>57724</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9879,7 +9879,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434307</v>
+        <v>434880</v>
       </c>
       <c r="R94" t="n">
-        <v>6806608</v>
+        <v>6806584</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10457,45 +10457,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215759</v>
+        <v>129215776</v>
       </c>
       <c r="B100" t="n">
-        <v>79631</v>
+        <v>56917</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434930</v>
+        <v>434445</v>
       </c>
       <c r="R100" t="n">
-        <v>6806768</v>
+        <v>6806699</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10554,7 +10562,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215776</v>
+        <v>129215777</v>
       </c>
       <c r="B101" t="n">
         <v>56917</v>
@@ -10587,7 +10595,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10597,10 +10605,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434445</v>
+        <v>434432</v>
       </c>
       <c r="R101" t="n">
-        <v>6806699</v>
+        <v>6806670</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10659,53 +10667,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215777</v>
+        <v>129215759</v>
       </c>
       <c r="B102" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434432</v>
+        <v>434930</v>
       </c>
       <c r="R102" t="n">
-        <v>6806670</v>
+        <v>6806768</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215848</v>
+        <v>129215794</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11276,34 +11276,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434473</v>
+        <v>434852</v>
       </c>
       <c r="R108" t="n">
-        <v>6806453</v>
+        <v>6806551</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11362,7 +11370,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215879</v>
+        <v>129215848</v>
       </c>
       <c r="B109" t="n">
         <v>79041</v>
@@ -11397,10 +11405,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434627</v>
+        <v>434473</v>
       </c>
       <c r="R109" t="n">
-        <v>6806787</v>
+        <v>6806453</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11459,7 +11467,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215849</v>
+        <v>129215879</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11494,10 +11502,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434437</v>
+        <v>434627</v>
       </c>
       <c r="R110" t="n">
-        <v>6806501</v>
+        <v>6806787</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11556,7 +11564,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215892</v>
+        <v>129215849</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11591,10 +11599,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434884</v>
+        <v>434437</v>
       </c>
       <c r="R111" t="n">
-        <v>6806606</v>
+        <v>6806501</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11653,53 +11661,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215765</v>
+        <v>129215892</v>
       </c>
       <c r="B112" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434630</v>
+        <v>434884</v>
       </c>
       <c r="R112" t="n">
-        <v>6806465</v>
+        <v>6806606</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11758,7 +11758,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215769</v>
+        <v>129215765</v>
       </c>
       <c r="B113" t="n">
         <v>56917</v>
@@ -11801,10 +11801,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434382</v>
+        <v>434630</v>
       </c>
       <c r="R113" t="n">
-        <v>6806548</v>
+        <v>6806465</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11863,32 +11863,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215794</v>
+        <v>129215769</v>
       </c>
       <c r="B114" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11896,7 +11896,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434852</v>
+        <v>434382</v>
       </c>
       <c r="R114" t="n">
-        <v>6806551</v>
+        <v>6806548</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215767</v>
+        <v>129215876</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434546</v>
+        <v>434591</v>
       </c>
       <c r="R2" t="n">
-        <v>6806482</v>
+        <v>6806739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,53 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215775</v>
+        <v>129215864</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434334</v>
+        <v>434319</v>
       </c>
       <c r="R3" t="n">
-        <v>6806593</v>
+        <v>6806589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,53 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215770</v>
+        <v>129215761</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434136</v>
+        <v>434924</v>
       </c>
       <c r="R4" t="n">
-        <v>6806558</v>
+        <v>6806749</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,45 +966,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215761</v>
+        <v>129215767</v>
       </c>
       <c r="B5" t="n">
-        <v>79631</v>
+        <v>56917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434924</v>
+        <v>434546</v>
       </c>
       <c r="R5" t="n">
-        <v>6806749</v>
+        <v>6806482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,45 +1071,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215876</v>
+        <v>129215775</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434591</v>
+        <v>434334</v>
       </c>
       <c r="R6" t="n">
-        <v>6806739</v>
+        <v>6806593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,45 +1176,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215864</v>
+        <v>129215770</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434319</v>
+        <v>434136</v>
       </c>
       <c r="R7" t="n">
-        <v>6806589</v>
+        <v>6806558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129215888</v>
+        <v>129215846</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434913</v>
+        <v>434523</v>
       </c>
       <c r="R8" t="n">
-        <v>6806699</v>
+        <v>6806496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129215846</v>
+        <v>129215888</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434523</v>
+        <v>434913</v>
       </c>
       <c r="R9" t="n">
-        <v>6806496</v>
+        <v>6806699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215813</v>
+        <v>129215903</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>88940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,34 +1486,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434803</v>
+        <v>434350</v>
       </c>
       <c r="R10" t="n">
-        <v>6806683</v>
+        <v>6806600</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,6 +1557,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1572,10 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215903</v>
+        <v>129215795</v>
       </c>
       <c r="B11" t="n">
-        <v>88939</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,26 +1587,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1610,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434350</v>
+        <v>434758</v>
       </c>
       <c r="R11" t="n">
-        <v>6806600</v>
+        <v>6806435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,7 +1663,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1673,10 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215847</v>
+        <v>129215736</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,21 +1692,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1708,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434523</v>
+        <v>434605</v>
       </c>
       <c r="R12" t="n">
-        <v>6806508</v>
+        <v>6806750</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,7 +1778,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215875</v>
+        <v>129215847</v>
       </c>
       <c r="B13" t="n">
         <v>79041</v>
@@ -1805,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434516</v>
+        <v>434523</v>
       </c>
       <c r="R13" t="n">
-        <v>6806695</v>
+        <v>6806508</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,10 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129215736</v>
+        <v>129215875</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,21 +1886,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434605</v>
+        <v>434516</v>
       </c>
       <c r="R14" t="n">
-        <v>6806750</v>
+        <v>6806695</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,10 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215795</v>
+        <v>129215813</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,42 +1983,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434758</v>
+        <v>434803</v>
       </c>
       <c r="R15" t="n">
-        <v>6806435</v>
+        <v>6806683</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129215890</v>
+        <v>129215893</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434799</v>
+        <v>434908</v>
       </c>
       <c r="R16" t="n">
-        <v>6806670</v>
+        <v>6806633</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129215893</v>
+        <v>129215890</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434908</v>
+        <v>434799</v>
       </c>
       <c r="R17" t="n">
-        <v>6806633</v>
+        <v>6806670</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215793</v>
+        <v>129215800</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2498,7 +2498,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434920</v>
+        <v>434596</v>
       </c>
       <c r="R20" t="n">
-        <v>6806792</v>
+        <v>6806728</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2570,10 +2570,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215758</v>
+        <v>129215793</v>
       </c>
       <c r="B21" t="n">
-        <v>79631</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2581,34 +2581,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434928</v>
+        <v>434920</v>
       </c>
       <c r="R21" t="n">
-        <v>6806794</v>
+        <v>6806792</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2764,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215744</v>
+        <v>129215877</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2775,37 +2783,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434950</v>
+        <v>434596</v>
       </c>
       <c r="R23" t="n">
-        <v>6806749</v>
+        <v>6806729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,7 +2851,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2865,7 +2869,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215877</v>
+        <v>129215856</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -2900,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434596</v>
+        <v>434194</v>
       </c>
       <c r="R24" t="n">
-        <v>6806729</v>
+        <v>6806560</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,10 +3063,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215856</v>
+        <v>129215744</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,34 +3074,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434194</v>
+        <v>434950</v>
       </c>
       <c r="R26" t="n">
-        <v>6806560</v>
+        <v>6806749</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3138,6 +3145,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3354,32 +3362,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215800</v>
+        <v>129215782</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3387,7 +3395,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3397,10 +3405,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434596</v>
+        <v>434568</v>
       </c>
       <c r="R29" t="n">
-        <v>6806728</v>
+        <v>6806730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3459,53 +3467,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215782</v>
+        <v>129215758</v>
       </c>
       <c r="B30" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434568</v>
+        <v>434928</v>
       </c>
       <c r="R30" t="n">
-        <v>6806730</v>
+        <v>6806794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215750</v>
+        <v>129215881</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3575,34 +3575,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434775</v>
+        <v>434834</v>
       </c>
       <c r="R31" t="n">
-        <v>6806482</v>
+        <v>6806837</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,6 +3646,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3661,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215881</v>
+        <v>129215750</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3672,37 +3676,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434834</v>
+        <v>434775</v>
       </c>
       <c r="R32" t="n">
-        <v>6806837</v>
+        <v>6806482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3743,7 +3744,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129215854</v>
+        <v>129215822</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3999,10 +3999,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434268</v>
+        <v>434936</v>
       </c>
       <c r="R35" t="n">
-        <v>6806557</v>
+        <v>6806756</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129215902</v>
+        <v>129215823</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4072,37 +4072,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434784</v>
+        <v>434906</v>
       </c>
       <c r="R36" t="n">
-        <v>6806543</v>
+        <v>6806734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4137,18 +4134,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4167,10 +4158,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129215738</v>
+        <v>129215902</v>
       </c>
       <c r="B37" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4178,34 +4169,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434764</v>
+        <v>434784</v>
       </c>
       <c r="R37" t="n">
-        <v>6806804</v>
+        <v>6806543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4240,12 +4234,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129215823</v>
+        <v>129215738</v>
       </c>
       <c r="B38" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434906</v>
+        <v>434764</v>
       </c>
       <c r="R38" t="n">
-        <v>6806734</v>
+        <v>6806804</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129215869</v>
+        <v>129215854</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434432</v>
+        <v>434268</v>
       </c>
       <c r="R39" t="n">
-        <v>6806606</v>
+        <v>6806557</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129215822</v>
+        <v>129215869</v>
       </c>
       <c r="B40" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4469,21 +4469,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434936</v>
+        <v>434432</v>
       </c>
       <c r="R40" t="n">
-        <v>6806756</v>
+        <v>6806606</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215756</v>
+        <v>129215798</v>
       </c>
       <c r="B41" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4566,26 +4566,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4593,10 +4598,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434857</v>
+        <v>434244</v>
       </c>
       <c r="R41" t="n">
-        <v>6806824</v>
+        <v>6806571</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4637,7 +4642,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4656,10 +4660,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215809</v>
+        <v>129215756</v>
       </c>
       <c r="B42" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4667,34 +4671,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434843</v>
+        <v>434857</v>
       </c>
       <c r="R42" t="n">
-        <v>6806853</v>
+        <v>6806824</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4735,6 +4742,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4753,10 +4761,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215798</v>
+        <v>129215809</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4764,42 +4772,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434244</v>
+        <v>434843</v>
       </c>
       <c r="R43" t="n">
-        <v>6806571</v>
+        <v>6806853</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129215857</v>
+        <v>129215755</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434179</v>
+        <v>434812</v>
       </c>
       <c r="R48" t="n">
-        <v>6806557</v>
+        <v>6806771</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215904</v>
+        <v>129215760</v>
       </c>
       <c r="B49" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434857</v>
+        <v>434895</v>
       </c>
       <c r="R49" t="n">
-        <v>6806833</v>
+        <v>6806736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,53 +5448,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215790</v>
+        <v>129215808</v>
       </c>
       <c r="B50" t="n">
-        <v>56917</v>
+        <v>78799</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434809</v>
+        <v>434355</v>
       </c>
       <c r="R50" t="n">
-        <v>6806535</v>
+        <v>6806519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5553,53 +5545,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215786</v>
+        <v>129215857</v>
       </c>
       <c r="B51" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434883</v>
+        <v>434179</v>
       </c>
       <c r="R51" t="n">
-        <v>6806675</v>
+        <v>6806557</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,10 +5642,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215755</v>
+        <v>129215904</v>
       </c>
       <c r="B52" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5669,21 +5653,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5693,10 +5677,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434812</v>
+        <v>434857</v>
       </c>
       <c r="R52" t="n">
-        <v>6806771</v>
+        <v>6806833</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,45 +5739,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215760</v>
+        <v>129215790</v>
       </c>
       <c r="B53" t="n">
-        <v>79631</v>
+        <v>56917</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434895</v>
+        <v>434809</v>
       </c>
       <c r="R53" t="n">
-        <v>6806736</v>
+        <v>6806535</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,45 +5844,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129215808</v>
+        <v>129215786</v>
       </c>
       <c r="B54" t="n">
-        <v>78799</v>
+        <v>56917</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434355</v>
+        <v>434883</v>
       </c>
       <c r="R54" t="n">
-        <v>6806519</v>
+        <v>6806675</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129215896</v>
+        <v>129215841</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434783</v>
+        <v>434433</v>
       </c>
       <c r="R55" t="n">
-        <v>6806478</v>
+        <v>6806597</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,6 +6028,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6143,7 +6144,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129215841</v>
+        <v>129215896</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6178,10 +6179,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434433</v>
+        <v>434783</v>
       </c>
       <c r="R57" t="n">
-        <v>6806597</v>
+        <v>6806478</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,7 +6223,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6556,7 +6556,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215824</v>
+        <v>129215819</v>
       </c>
       <c r="B61" t="n">
         <v>78798</v>
@@ -6585,16 +6585,19 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434922</v>
+        <v>434773</v>
       </c>
       <c r="R61" t="n">
-        <v>6806746</v>
+        <v>6806803</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6635,6 +6638,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6750,10 +6754,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215819</v>
+        <v>129215739</v>
       </c>
       <c r="B63" t="n">
-        <v>78798</v>
+        <v>79660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6761,37 +6765,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434773</v>
+        <v>434817</v>
       </c>
       <c r="R63" t="n">
-        <v>6806803</v>
+        <v>6806766</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6832,7 +6833,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6851,10 +6851,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215862</v>
+        <v>129215824</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6862,21 +6862,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434270</v>
+        <v>434922</v>
       </c>
       <c r="R64" t="n">
-        <v>6806602</v>
+        <v>6806746</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215739</v>
+        <v>129215885</v>
       </c>
       <c r="B65" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434817</v>
+        <v>434884</v>
       </c>
       <c r="R65" t="n">
-        <v>6806766</v>
+        <v>6806816</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215885</v>
+        <v>129215743</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434884</v>
+        <v>434922</v>
       </c>
       <c r="R66" t="n">
-        <v>6806816</v>
+        <v>6806795</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129215743</v>
+        <v>129215862</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434922</v>
+        <v>434270</v>
       </c>
       <c r="R67" t="n">
-        <v>6806795</v>
+        <v>6806602</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7239,42 +7239,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215764</v>
+        <v>129215742</v>
       </c>
       <c r="B68" t="n">
-        <v>56917</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7282,10 +7277,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434687</v>
+        <v>434910</v>
       </c>
       <c r="R68" t="n">
-        <v>6806459</v>
+        <v>6806856</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7326,6 +7321,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7538,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215742</v>
+        <v>129215821</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7549,37 +7545,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434910</v>
+        <v>434913</v>
       </c>
       <c r="R71" t="n">
-        <v>6806856</v>
+        <v>6806785</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7620,7 +7613,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7639,10 +7631,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215821</v>
+        <v>129215895</v>
       </c>
       <c r="B72" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7650,21 +7642,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7674,10 +7666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434913</v>
+        <v>434858</v>
       </c>
       <c r="R72" t="n">
-        <v>6806785</v>
+        <v>6806562</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,7 +7825,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215895</v>
+        <v>129215851</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -7868,10 +7860,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434858</v>
+        <v>434362</v>
       </c>
       <c r="R74" t="n">
-        <v>6806562</v>
+        <v>6806519</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7930,45 +7922,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215851</v>
+        <v>129215764</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434362</v>
+        <v>434687</v>
       </c>
       <c r="R75" t="n">
-        <v>6806519</v>
+        <v>6806459</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8030,7 +8030,7 @@
         <v>129215807</v>
       </c>
       <c r="B76" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8129,10 +8129,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215858</v>
+        <v>129215801</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8140,34 +8140,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434135</v>
+        <v>434883</v>
       </c>
       <c r="R77" t="n">
-        <v>6806556</v>
+        <v>6806894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8226,10 +8234,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215887</v>
+        <v>129215805</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8237,34 +8245,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434936</v>
+        <v>434761</v>
       </c>
       <c r="R78" t="n">
-        <v>6806726</v>
+        <v>6806449</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8323,10 +8339,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215801</v>
+        <v>129215887</v>
       </c>
       <c r="B79" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8334,42 +8350,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434883</v>
+        <v>434936</v>
       </c>
       <c r="R79" t="n">
-        <v>6806894</v>
+        <v>6806726</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8428,10 +8436,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215805</v>
+        <v>129215858</v>
       </c>
       <c r="B80" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8439,42 +8447,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434761</v>
+        <v>434135</v>
       </c>
       <c r="R80" t="n">
-        <v>6806449</v>
+        <v>6806556</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8638,7 +8638,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215843</v>
+        <v>129215886</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434628</v>
+        <v>434934</v>
       </c>
       <c r="R82" t="n">
-        <v>6806457</v>
+        <v>6806762</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8735,10 +8735,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215850</v>
+        <v>129215741</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8746,21 +8746,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434376</v>
+        <v>434844</v>
       </c>
       <c r="R83" t="n">
-        <v>6806560</v>
+        <v>6806852</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,10 +8832,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215741</v>
+        <v>129215863</v>
       </c>
       <c r="B84" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8843,21 +8843,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434844</v>
+        <v>434279</v>
       </c>
       <c r="R84" t="n">
-        <v>6806852</v>
+        <v>6806587</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215861</v>
+        <v>129215850</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9055,19 +9055,16 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434259</v>
+        <v>434376</v>
       </c>
       <c r="R86" t="n">
-        <v>6806607</v>
+        <v>6806560</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9108,7 +9105,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9127,7 +9123,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215886</v>
+        <v>129215843</v>
       </c>
       <c r="B87" t="n">
         <v>79041</v>
@@ -9162,10 +9158,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434934</v>
+        <v>434628</v>
       </c>
       <c r="R87" t="n">
-        <v>6806762</v>
+        <v>6806457</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9224,7 +9220,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215863</v>
+        <v>129215861</v>
       </c>
       <c r="B88" t="n">
         <v>79041</v>
@@ -9253,16 +9249,19 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434279</v>
+        <v>434259</v>
       </c>
       <c r="R88" t="n">
-        <v>6806587</v>
+        <v>6806607</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9303,6 +9302,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9321,32 +9321,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215771</v>
+        <v>129215803</v>
       </c>
       <c r="B89" t="n">
-        <v>56917</v>
+        <v>57724</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9354,7 +9354,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434229</v>
+        <v>434895</v>
       </c>
       <c r="R89" t="n">
-        <v>6806613</v>
+        <v>6806664</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9426,32 +9426,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215768</v>
+        <v>129215804</v>
       </c>
       <c r="B90" t="n">
-        <v>56917</v>
+        <v>57724</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9459,7 +9459,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -9469,10 +9469,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434422</v>
+        <v>434880</v>
       </c>
       <c r="R90" t="n">
-        <v>6806522</v>
+        <v>6806584</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9531,7 +9531,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215787</v>
+        <v>129215771</v>
       </c>
       <c r="B91" t="n">
         <v>56917</v>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434813</v>
+        <v>434229</v>
       </c>
       <c r="R91" t="n">
-        <v>6806656</v>
+        <v>6806613</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9636,7 +9636,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215774</v>
+        <v>129215768</v>
       </c>
       <c r="B92" t="n">
         <v>56917</v>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434307</v>
+        <v>434422</v>
       </c>
       <c r="R92" t="n">
-        <v>6806608</v>
+        <v>6806522</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9741,32 +9741,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215803</v>
+        <v>129215787</v>
       </c>
       <c r="B93" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434895</v>
+        <v>434813</v>
       </c>
       <c r="R93" t="n">
-        <v>6806664</v>
+        <v>6806656</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,32 +9846,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215804</v>
+        <v>129215774</v>
       </c>
       <c r="B94" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9879,7 +9879,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434880</v>
+        <v>434307</v>
       </c>
       <c r="R94" t="n">
-        <v>6806584</v>
+        <v>6806608</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10158,7 +10158,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129215865</v>
+        <v>129215860</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434358</v>
+        <v>434241</v>
       </c>
       <c r="R97" t="n">
-        <v>6806608</v>
+        <v>6806618</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10255,7 +10255,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215860</v>
+        <v>129215865</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10290,10 +10290,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434241</v>
+        <v>434358</v>
       </c>
       <c r="R98" t="n">
-        <v>6806618</v>
+        <v>6806608</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10352,10 +10352,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215818</v>
+        <v>129215776</v>
       </c>
       <c r="B99" t="n">
-        <v>58097</v>
+        <v>56917</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10363,21 +10363,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10385,7 +10385,7 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434849</v>
+        <v>434445</v>
       </c>
       <c r="R99" t="n">
-        <v>6806700</v>
+        <v>6806699</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10457,7 +10457,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215776</v>
+        <v>129215777</v>
       </c>
       <c r="B100" t="n">
         <v>56917</v>
@@ -10490,7 +10490,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -10500,10 +10500,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434445</v>
+        <v>434432</v>
       </c>
       <c r="R100" t="n">
-        <v>6806699</v>
+        <v>6806670</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10562,10 +10562,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215777</v>
+        <v>129215818</v>
       </c>
       <c r="B101" t="n">
-        <v>56917</v>
+        <v>58097</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10573,21 +10573,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10595,7 +10595,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10605,10 +10605,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434432</v>
+        <v>434849</v>
       </c>
       <c r="R101" t="n">
-        <v>6806670</v>
+        <v>6806700</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10764,7 +10764,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215884</v>
+        <v>129215873</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -10799,10 +10799,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434890</v>
+        <v>434463</v>
       </c>
       <c r="R103" t="n">
-        <v>6806827</v>
+        <v>6806664</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10861,7 +10861,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129215873</v>
+        <v>129215884</v>
       </c>
       <c r="B104" t="n">
         <v>79041</v>
@@ -10896,10 +10896,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434463</v>
+        <v>434890</v>
       </c>
       <c r="R104" t="n">
-        <v>6806664</v>
+        <v>6806827</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11370,45 +11370,53 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215848</v>
+        <v>129215765</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434473</v>
+        <v>434630</v>
       </c>
       <c r="R109" t="n">
-        <v>6806453</v>
+        <v>6806465</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11467,45 +11475,53 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215879</v>
+        <v>129215769</v>
       </c>
       <c r="B110" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434627</v>
+        <v>434382</v>
       </c>
       <c r="R110" t="n">
-        <v>6806787</v>
+        <v>6806548</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11661,7 +11677,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215892</v>
+        <v>129215848</v>
       </c>
       <c r="B112" t="n">
         <v>79041</v>
@@ -11696,10 +11712,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434884</v>
+        <v>434473</v>
       </c>
       <c r="R112" t="n">
-        <v>6806606</v>
+        <v>6806453</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11758,53 +11774,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215765</v>
+        <v>129215879</v>
       </c>
       <c r="B113" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434630</v>
+        <v>434627</v>
       </c>
       <c r="R113" t="n">
-        <v>6806465</v>
+        <v>6806787</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11863,53 +11871,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215769</v>
+        <v>129215892</v>
       </c>
       <c r="B114" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434382</v>
+        <v>434884</v>
       </c>
       <c r="R114" t="n">
-        <v>6806548</v>
+        <v>6806606</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11968,7 +11968,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215844</v>
+        <v>129215900</v>
       </c>
       <c r="B115" t="n">
         <v>79041</v>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434623</v>
+        <v>434775</v>
       </c>
       <c r="R115" t="n">
-        <v>6806466</v>
+        <v>6806423</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215734</v>
+        <v>129215867</v>
       </c>
       <c r="B116" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12076,21 +12076,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12100,10 +12100,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434546</v>
+        <v>434375</v>
       </c>
       <c r="R116" t="n">
-        <v>6806737</v>
+        <v>6806574</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12162,10 +12162,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215868</v>
+        <v>129215734</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12173,21 +12173,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434415</v>
+        <v>434546</v>
       </c>
       <c r="R117" t="n">
-        <v>6806576</v>
+        <v>6806737</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12259,7 +12259,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215900</v>
+        <v>129215844</v>
       </c>
       <c r="B118" t="n">
         <v>79041</v>
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434775</v>
+        <v>434623</v>
       </c>
       <c r="R118" t="n">
-        <v>6806423</v>
+        <v>6806466</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12356,7 +12356,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215867</v>
+        <v>129215868</v>
       </c>
       <c r="B119" t="n">
         <v>79041</v>
@@ -12391,10 +12391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434375</v>
+        <v>434415</v>
       </c>
       <c r="R119" t="n">
-        <v>6806574</v>
+        <v>6806576</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12857,10 +12857,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129215901</v>
+        <v>129215752</v>
       </c>
       <c r="B124" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12868,21 +12868,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434918</v>
+        <v>434263</v>
       </c>
       <c r="R124" t="n">
-        <v>6806737</v>
+        <v>6806561</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129215745</v>
+        <v>129215751</v>
       </c>
       <c r="B125" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,21 +12965,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434934</v>
+        <v>434673</v>
       </c>
       <c r="R125" t="n">
-        <v>6806753</v>
+        <v>6806460</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13051,7 +13051,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129215871</v>
+        <v>129215852</v>
       </c>
       <c r="B126" t="n">
         <v>79041</v>
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434443</v>
+        <v>434335</v>
       </c>
       <c r="R126" t="n">
-        <v>6806595</v>
+        <v>6806532</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13148,7 +13148,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129215852</v>
+        <v>129215901</v>
       </c>
       <c r="B127" t="n">
         <v>79041</v>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434335</v>
+        <v>434918</v>
       </c>
       <c r="R127" t="n">
-        <v>6806532</v>
+        <v>6806737</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129215752</v>
+        <v>129215745</v>
       </c>
       <c r="B129" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13353,21 +13353,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>434263</v>
+        <v>434934</v>
       </c>
       <c r="R129" t="n">
-        <v>6806561</v>
+        <v>6806753</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129215751</v>
+        <v>129215871</v>
       </c>
       <c r="B130" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,21 +13450,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434673</v>
+        <v>434443</v>
       </c>
       <c r="R130" t="n">
-        <v>6806460</v>
+        <v>6806595</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215876</v>
+        <v>129215761</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434591</v>
+        <v>434924</v>
       </c>
       <c r="R2" t="n">
-        <v>6806739</v>
+        <v>6806749</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215864</v>
+        <v>129215876</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434319</v>
+        <v>434591</v>
       </c>
       <c r="R3" t="n">
-        <v>6806589</v>
+        <v>6806739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215761</v>
+        <v>129215864</v>
       </c>
       <c r="B4" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434924</v>
+        <v>434319</v>
       </c>
       <c r="R4" t="n">
-        <v>6806749</v>
+        <v>6806589</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129215846</v>
+        <v>129215888</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434523</v>
+        <v>434913</v>
       </c>
       <c r="R8" t="n">
-        <v>6806496</v>
+        <v>6806699</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129215888</v>
+        <v>129215846</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434913</v>
+        <v>434523</v>
       </c>
       <c r="R9" t="n">
-        <v>6806699</v>
+        <v>6806496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215903</v>
+        <v>129215795</v>
       </c>
       <c r="B10" t="n">
-        <v>88940</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,26 +1486,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1513,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434350</v>
+        <v>434758</v>
       </c>
       <c r="R10" t="n">
-        <v>6806600</v>
+        <v>6806435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1562,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1576,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215795</v>
+        <v>129215903</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>88940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,31 +1591,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1619,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434758</v>
+        <v>434350</v>
       </c>
       <c r="R11" t="n">
-        <v>6806435</v>
+        <v>6806600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1662,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2069,45 +2069,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129215893</v>
+        <v>129215766</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434908</v>
+        <v>434601</v>
       </c>
       <c r="R16" t="n">
-        <v>6806633</v>
+        <v>6806475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,53 +2271,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129215766</v>
+        <v>129215893</v>
       </c>
       <c r="B18" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434601</v>
+        <v>434908</v>
       </c>
       <c r="R18" t="n">
-        <v>6806475</v>
+        <v>6806633</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215800</v>
+        <v>129215737</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,42 +2476,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434596</v>
+        <v>434585</v>
       </c>
       <c r="R20" t="n">
-        <v>6806728</v>
+        <v>6806746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2570,10 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215793</v>
+        <v>129215877</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2581,42 +2573,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434920</v>
+        <v>434596</v>
       </c>
       <c r="R21" t="n">
-        <v>6806792</v>
+        <v>6806729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215737</v>
+        <v>129215856</v>
       </c>
       <c r="B22" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2710,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434585</v>
+        <v>434194</v>
       </c>
       <c r="R22" t="n">
-        <v>6806746</v>
+        <v>6806560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215877</v>
+        <v>129215735</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2807,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434596</v>
+        <v>434571</v>
       </c>
       <c r="R23" t="n">
-        <v>6806729</v>
+        <v>6806718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2869,10 +2853,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215856</v>
+        <v>129215744</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2880,34 +2864,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434194</v>
+        <v>434950</v>
       </c>
       <c r="R24" t="n">
-        <v>6806560</v>
+        <v>6806749</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2948,6 +2935,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2966,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215735</v>
+        <v>129215758</v>
       </c>
       <c r="B25" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2977,21 +2965,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3001,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434571</v>
+        <v>434928</v>
       </c>
       <c r="R25" t="n">
-        <v>6806718</v>
+        <v>6806794</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3063,10 +3051,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215744</v>
+        <v>129215800</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3074,26 +3062,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3101,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434950</v>
+        <v>434596</v>
       </c>
       <c r="R26" t="n">
-        <v>6806749</v>
+        <v>6806728</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,7 +3138,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3164,10 +3156,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215878</v>
+        <v>129215793</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3175,26 +3167,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3202,10 +3199,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434621</v>
+        <v>434920</v>
       </c>
       <c r="R27" t="n">
-        <v>6806786</v>
+        <v>6806792</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3246,7 +3243,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3265,7 +3261,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215859</v>
+        <v>129215878</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3294,16 +3290,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434177</v>
+        <v>434621</v>
       </c>
       <c r="R28" t="n">
-        <v>6806592</v>
+        <v>6806786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3344,6 +3343,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3362,53 +3362,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215782</v>
+        <v>129215859</v>
       </c>
       <c r="B29" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434568</v>
+        <v>434177</v>
       </c>
       <c r="R29" t="n">
-        <v>6806730</v>
+        <v>6806592</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3467,45 +3459,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215758</v>
+        <v>129215782</v>
       </c>
       <c r="B30" t="n">
-        <v>79631</v>
+        <v>56917</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434928</v>
+        <v>434568</v>
       </c>
       <c r="R30" t="n">
-        <v>6806794</v>
+        <v>6806730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129215854</v>
+        <v>129215869</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434268</v>
+        <v>434432</v>
       </c>
       <c r="R39" t="n">
-        <v>6806557</v>
+        <v>6806606</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129215869</v>
+        <v>129215854</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434432</v>
+        <v>434268</v>
       </c>
       <c r="R40" t="n">
-        <v>6806606</v>
+        <v>6806557</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129215882</v>
+        <v>129215799</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,34 +4869,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434851</v>
+        <v>434142</v>
       </c>
       <c r="R44" t="n">
-        <v>6806867</v>
+        <v>6806549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4955,7 +4963,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129215845</v>
+        <v>129215882</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -4990,10 +4998,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434585</v>
+        <v>434851</v>
       </c>
       <c r="R45" t="n">
-        <v>6806500</v>
+        <v>6806867</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5052,10 +5060,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215799</v>
+        <v>129215845</v>
       </c>
       <c r="B46" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,42 +5071,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434142</v>
+        <v>434585</v>
       </c>
       <c r="R46" t="n">
-        <v>6806549</v>
+        <v>6806500</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129215755</v>
+        <v>129215857</v>
       </c>
       <c r="B48" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434812</v>
+        <v>434179</v>
       </c>
       <c r="R48" t="n">
-        <v>6806771</v>
+        <v>6806557</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,10 +5351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215760</v>
+        <v>129215904</v>
       </c>
       <c r="B49" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5386,10 +5386,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434895</v>
+        <v>434857</v>
       </c>
       <c r="R49" t="n">
-        <v>6806736</v>
+        <v>6806833</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,45 +5448,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215808</v>
+        <v>129215790</v>
       </c>
       <c r="B50" t="n">
-        <v>78799</v>
+        <v>56917</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434355</v>
+        <v>434809</v>
       </c>
       <c r="R50" t="n">
-        <v>6806519</v>
+        <v>6806535</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5545,45 +5553,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215857</v>
+        <v>129215786</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434179</v>
+        <v>434883</v>
       </c>
       <c r="R51" t="n">
-        <v>6806557</v>
+        <v>6806675</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5642,10 +5658,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215904</v>
+        <v>129215755</v>
       </c>
       <c r="B52" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5653,21 +5669,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5677,10 +5693,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434857</v>
+        <v>434812</v>
       </c>
       <c r="R52" t="n">
-        <v>6806833</v>
+        <v>6806771</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5739,53 +5755,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215790</v>
+        <v>129215760</v>
       </c>
       <c r="B53" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434809</v>
+        <v>434895</v>
       </c>
       <c r="R53" t="n">
-        <v>6806535</v>
+        <v>6806736</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5844,53 +5852,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129215786</v>
+        <v>129215808</v>
       </c>
       <c r="B54" t="n">
-        <v>56917</v>
+        <v>78799</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434883</v>
+        <v>434355</v>
       </c>
       <c r="R54" t="n">
-        <v>6806675</v>
+        <v>6806519</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129215841</v>
+        <v>129215896</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434433</v>
+        <v>434783</v>
       </c>
       <c r="R55" t="n">
-        <v>6806597</v>
+        <v>6806478</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,7 +6028,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6144,7 +6143,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129215896</v>
+        <v>129215841</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6179,10 +6178,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434783</v>
+        <v>434433</v>
       </c>
       <c r="R57" t="n">
-        <v>6806478</v>
+        <v>6806597</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6223,6 +6222,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215819</v>
+        <v>129215880</v>
       </c>
       <c r="B61" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6567,37 +6567,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434773</v>
+        <v>434845</v>
       </c>
       <c r="R61" t="n">
-        <v>6806803</v>
+        <v>6806812</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6638,7 +6635,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6657,7 +6653,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129215880</v>
+        <v>129215862</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6692,10 +6688,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434845</v>
+        <v>434270</v>
       </c>
       <c r="R62" t="n">
-        <v>6806812</v>
+        <v>6806602</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6754,10 +6750,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215739</v>
+        <v>129215885</v>
       </c>
       <c r="B63" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6765,21 +6761,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6789,10 +6785,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434817</v>
+        <v>434884</v>
       </c>
       <c r="R63" t="n">
-        <v>6806766</v>
+        <v>6806816</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6851,7 +6847,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215824</v>
+        <v>129215819</v>
       </c>
       <c r="B64" t="n">
         <v>78798</v>
@@ -6880,16 +6876,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434922</v>
+        <v>434773</v>
       </c>
       <c r="R64" t="n">
-        <v>6806746</v>
+        <v>6806803</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6930,6 +6929,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215885</v>
+        <v>129215739</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434884</v>
+        <v>434817</v>
       </c>
       <c r="R65" t="n">
-        <v>6806816</v>
+        <v>6806766</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215743</v>
+        <v>129215824</v>
       </c>
       <c r="B66" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7083,7 +7083,7 @@
         <v>434922</v>
       </c>
       <c r="R66" t="n">
-        <v>6806795</v>
+        <v>6806746</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129215862</v>
+        <v>129215743</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434270</v>
+        <v>434922</v>
       </c>
       <c r="R67" t="n">
-        <v>6806602</v>
+        <v>6806795</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215742</v>
+        <v>129215899</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7250,37 +7250,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434910</v>
+        <v>434763</v>
       </c>
       <c r="R68" t="n">
-        <v>6806856</v>
+        <v>6806436</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7321,7 +7318,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7340,45 +7336,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129215891</v>
+        <v>129215764</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434812</v>
+        <v>434687</v>
       </c>
       <c r="R69" t="n">
-        <v>6806610</v>
+        <v>6806459</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7437,10 +7441,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129215898</v>
+        <v>129215742</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,34 +7452,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434759</v>
+        <v>434910</v>
       </c>
       <c r="R70" t="n">
-        <v>6806455</v>
+        <v>6806856</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7516,6 +7523,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7534,10 +7542,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215821</v>
+        <v>129215898</v>
       </c>
       <c r="B71" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,21 +7553,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7569,10 +7577,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434913</v>
+        <v>434759</v>
       </c>
       <c r="R71" t="n">
-        <v>6806785</v>
+        <v>6806455</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7631,10 +7639,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215895</v>
+        <v>129215821</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7642,21 +7650,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7666,10 +7674,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434858</v>
+        <v>434913</v>
       </c>
       <c r="R72" t="n">
-        <v>6806562</v>
+        <v>6806785</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7728,7 +7736,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129215899</v>
+        <v>129215891</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7763,10 +7771,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434763</v>
+        <v>434812</v>
       </c>
       <c r="R73" t="n">
-        <v>6806436</v>
+        <v>6806610</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7825,7 +7833,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215851</v>
+        <v>129215895</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -7860,10 +7868,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434362</v>
+        <v>434858</v>
       </c>
       <c r="R74" t="n">
-        <v>6806519</v>
+        <v>6806562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7922,53 +7930,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215764</v>
+        <v>129215851</v>
       </c>
       <c r="B75" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434687</v>
+        <v>434362</v>
       </c>
       <c r="R75" t="n">
-        <v>6806459</v>
+        <v>6806519</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8030,7 +8030,7 @@
         <v>129215807</v>
       </c>
       <c r="B76" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8129,10 +8129,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215801</v>
+        <v>129215858</v>
       </c>
       <c r="B77" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8140,42 +8140,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434883</v>
+        <v>434135</v>
       </c>
       <c r="R77" t="n">
-        <v>6806894</v>
+        <v>6806556</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8234,10 +8226,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215805</v>
+        <v>129215887</v>
       </c>
       <c r="B78" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8245,42 +8237,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434761</v>
+        <v>434936</v>
       </c>
       <c r="R78" t="n">
-        <v>6806449</v>
+        <v>6806726</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8339,10 +8323,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215887</v>
+        <v>129215805</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8350,34 +8334,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434936</v>
+        <v>434761</v>
       </c>
       <c r="R79" t="n">
-        <v>6806726</v>
+        <v>6806449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8436,10 +8428,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215858</v>
+        <v>129215801</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8447,34 +8439,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434135</v>
+        <v>434883</v>
       </c>
       <c r="R80" t="n">
-        <v>6806556</v>
+        <v>6806894</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215886</v>
+        <v>129215741</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8649,21 +8649,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8673,10 +8673,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434934</v>
+        <v>434844</v>
       </c>
       <c r="R82" t="n">
-        <v>6806762</v>
+        <v>6806852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8735,10 +8735,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215741</v>
+        <v>129215863</v>
       </c>
       <c r="B83" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8746,21 +8746,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434844</v>
+        <v>434279</v>
       </c>
       <c r="R83" t="n">
-        <v>6806852</v>
+        <v>6806587</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,7 +8832,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215863</v>
+        <v>129215850</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434279</v>
+        <v>434376</v>
       </c>
       <c r="R84" t="n">
-        <v>6806587</v>
+        <v>6806560</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8929,7 +8929,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215853</v>
+        <v>129215843</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -8964,10 +8964,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434280</v>
+        <v>434628</v>
       </c>
       <c r="R85" t="n">
-        <v>6806556</v>
+        <v>6806457</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9026,10 +9026,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215850</v>
+        <v>129215803</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9037,34 +9037,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434376</v>
+        <v>434895</v>
       </c>
       <c r="R86" t="n">
-        <v>6806560</v>
+        <v>6806664</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9123,10 +9131,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215843</v>
+        <v>129215804</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9134,34 +9142,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434628</v>
+        <v>434880</v>
       </c>
       <c r="R87" t="n">
-        <v>6806457</v>
+        <v>6806584</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9220,37 +9236,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215861</v>
+        <v>129215771</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9258,10 +9279,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434259</v>
+        <v>434229</v>
       </c>
       <c r="R88" t="n">
-        <v>6806607</v>
+        <v>6806613</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9302,7 +9323,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9321,32 +9341,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215803</v>
+        <v>129215768</v>
       </c>
       <c r="B89" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9354,7 +9374,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -9364,10 +9384,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434895</v>
+        <v>434422</v>
       </c>
       <c r="R89" t="n">
-        <v>6806664</v>
+        <v>6806522</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9426,32 +9446,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215804</v>
+        <v>129215787</v>
       </c>
       <c r="B90" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9459,7 +9479,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -9469,10 +9489,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434880</v>
+        <v>434813</v>
       </c>
       <c r="R90" t="n">
-        <v>6806584</v>
+        <v>6806656</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9531,7 +9551,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215771</v>
+        <v>129215774</v>
       </c>
       <c r="B91" t="n">
         <v>56917</v>
@@ -9574,10 +9594,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434229</v>
+        <v>434307</v>
       </c>
       <c r="R91" t="n">
-        <v>6806613</v>
+        <v>6806608</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9636,53 +9656,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215768</v>
+        <v>129215853</v>
       </c>
       <c r="B92" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434422</v>
+        <v>434280</v>
       </c>
       <c r="R92" t="n">
-        <v>6806522</v>
+        <v>6806556</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9741,42 +9753,37 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215787</v>
+        <v>129215861</v>
       </c>
       <c r="B93" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -9784,10 +9791,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434813</v>
+        <v>434259</v>
       </c>
       <c r="R93" t="n">
-        <v>6806656</v>
+        <v>6806607</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9828,6 +9835,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9846,53 +9854,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215774</v>
+        <v>129215886</v>
       </c>
       <c r="B94" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434307</v>
+        <v>434934</v>
       </c>
       <c r="R94" t="n">
-        <v>6806608</v>
+        <v>6806762</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10052,7 +10052,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129215883</v>
+        <v>129215865</v>
       </c>
       <c r="B96" t="n">
         <v>79041</v>
@@ -10081,19 +10081,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>434920</v>
+        <v>434358</v>
       </c>
       <c r="R96" t="n">
-        <v>6806876</v>
+        <v>6806608</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10128,18 +10125,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10158,45 +10149,53 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129215860</v>
+        <v>129215776</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434241</v>
+        <v>434445</v>
       </c>
       <c r="R97" t="n">
-        <v>6806618</v>
+        <v>6806699</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10255,45 +10254,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215865</v>
+        <v>129215777</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434358</v>
+        <v>434432</v>
       </c>
       <c r="R98" t="n">
-        <v>6806608</v>
+        <v>6806670</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10352,10 +10359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215776</v>
+        <v>129215818</v>
       </c>
       <c r="B99" t="n">
-        <v>56917</v>
+        <v>58097</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10363,21 +10370,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10385,7 +10392,7 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -10395,10 +10402,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434445</v>
+        <v>434849</v>
       </c>
       <c r="R99" t="n">
-        <v>6806699</v>
+        <v>6806700</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10457,53 +10464,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215777</v>
+        <v>129215759</v>
       </c>
       <c r="B100" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434432</v>
+        <v>434930</v>
       </c>
       <c r="R100" t="n">
-        <v>6806670</v>
+        <v>6806768</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10562,42 +10561,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215818</v>
+        <v>129215883</v>
       </c>
       <c r="B101" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -10605,10 +10599,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434849</v>
+        <v>434920</v>
       </c>
       <c r="R101" t="n">
-        <v>6806700</v>
+        <v>6806876</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10643,12 +10637,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10667,10 +10667,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215759</v>
+        <v>129215860</v>
       </c>
       <c r="B102" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10678,21 +10678,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10702,10 +10702,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434930</v>
+        <v>434241</v>
       </c>
       <c r="R102" t="n">
-        <v>6806768</v>
+        <v>6806618</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10764,10 +10764,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215873</v>
+        <v>129215825</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10775,21 +10775,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10799,10 +10799,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434463</v>
+        <v>434799</v>
       </c>
       <c r="R103" t="n">
-        <v>6806664</v>
+        <v>6806687</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129215825</v>
+        <v>129215873</v>
       </c>
       <c r="B105" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434799</v>
+        <v>434463</v>
       </c>
       <c r="R105" t="n">
-        <v>6806687</v>
+        <v>6806664</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215794</v>
+        <v>129215848</v>
       </c>
       <c r="B108" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11276,42 +11276,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434852</v>
+        <v>434473</v>
       </c>
       <c r="R108" t="n">
-        <v>6806551</v>
+        <v>6806453</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11370,53 +11362,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215765</v>
+        <v>129215879</v>
       </c>
       <c r="B109" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434630</v>
+        <v>434627</v>
       </c>
       <c r="R109" t="n">
-        <v>6806465</v>
+        <v>6806787</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11475,53 +11459,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215769</v>
+        <v>129215849</v>
       </c>
       <c r="B110" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434382</v>
+        <v>434437</v>
       </c>
       <c r="R110" t="n">
-        <v>6806548</v>
+        <v>6806501</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11580,7 +11556,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215849</v>
+        <v>129215892</v>
       </c>
       <c r="B111" t="n">
         <v>79041</v>
@@ -11615,10 +11591,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434437</v>
+        <v>434884</v>
       </c>
       <c r="R111" t="n">
-        <v>6806501</v>
+        <v>6806606</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11677,45 +11653,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215848</v>
+        <v>129215765</v>
       </c>
       <c r="B112" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434473</v>
+        <v>434630</v>
       </c>
       <c r="R112" t="n">
-        <v>6806453</v>
+        <v>6806465</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11774,45 +11758,53 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215879</v>
+        <v>129215769</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434627</v>
+        <v>434382</v>
       </c>
       <c r="R113" t="n">
-        <v>6806787</v>
+        <v>6806548</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11871,10 +11863,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215892</v>
+        <v>129215794</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11882,34 +11874,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434884</v>
+        <v>434852</v>
       </c>
       <c r="R114" t="n">
-        <v>6806606</v>
+        <v>6806551</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215900</v>
+        <v>129215796</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11979,34 +11979,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434775</v>
+        <v>434635</v>
       </c>
       <c r="R115" t="n">
-        <v>6806423</v>
+        <v>6806453</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12065,10 +12073,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215867</v>
+        <v>129215797</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12076,34 +12084,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434375</v>
+        <v>434602</v>
       </c>
       <c r="R116" t="n">
-        <v>6806574</v>
+        <v>6806495</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12162,10 +12178,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215734</v>
+        <v>129215812</v>
       </c>
       <c r="B117" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12173,21 +12189,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12197,10 +12213,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434546</v>
+        <v>434922</v>
       </c>
       <c r="R117" t="n">
-        <v>6806737</v>
+        <v>6806746</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12259,10 +12275,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215844</v>
+        <v>129215754</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12270,21 +12286,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12294,10 +12310,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434623</v>
+        <v>434774</v>
       </c>
       <c r="R118" t="n">
-        <v>6806466</v>
+        <v>6806803</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12356,7 +12372,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215868</v>
+        <v>129215867</v>
       </c>
       <c r="B119" t="n">
         <v>79041</v>
@@ -12391,10 +12407,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434415</v>
+        <v>434375</v>
       </c>
       <c r="R119" t="n">
-        <v>6806576</v>
+        <v>6806574</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12453,10 +12469,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215796</v>
+        <v>129215734</v>
       </c>
       <c r="B120" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12464,42 +12480,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434635</v>
+        <v>434546</v>
       </c>
       <c r="R120" t="n">
-        <v>6806453</v>
+        <v>6806737</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12558,10 +12566,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215797</v>
+        <v>129215868</v>
       </c>
       <c r="B121" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,42 +12577,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434602</v>
+        <v>434415</v>
       </c>
       <c r="R121" t="n">
-        <v>6806495</v>
+        <v>6806576</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,10 +12663,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215812</v>
+        <v>129215900</v>
       </c>
       <c r="B122" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12674,21 +12674,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12698,10 +12698,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434922</v>
+        <v>434775</v>
       </c>
       <c r="R122" t="n">
-        <v>6806746</v>
+        <v>6806423</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215754</v>
+        <v>129215844</v>
       </c>
       <c r="B123" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12771,21 +12771,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12795,10 +12795,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434774</v>
+        <v>434623</v>
       </c>
       <c r="R123" t="n">
-        <v>6806803</v>
+        <v>6806466</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12857,10 +12857,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129215752</v>
+        <v>129215852</v>
       </c>
       <c r="B124" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12868,21 +12868,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434263</v>
+        <v>434335</v>
       </c>
       <c r="R124" t="n">
-        <v>6806561</v>
+        <v>6806532</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12954,10 +12954,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129215751</v>
+        <v>129215901</v>
       </c>
       <c r="B125" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12965,21 +12965,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12989,10 +12989,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434673</v>
+        <v>434918</v>
       </c>
       <c r="R125" t="n">
-        <v>6806460</v>
+        <v>6806737</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13051,10 +13051,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129215852</v>
+        <v>129215745</v>
       </c>
       <c r="B126" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13062,21 +13062,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434335</v>
+        <v>434934</v>
       </c>
       <c r="R126" t="n">
-        <v>6806532</v>
+        <v>6806753</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13148,7 +13148,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129215901</v>
+        <v>129215871</v>
       </c>
       <c r="B127" t="n">
         <v>79041</v>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434918</v>
+        <v>434443</v>
       </c>
       <c r="R127" t="n">
-        <v>6806737</v>
+        <v>6806595</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,10 +13245,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129215889</v>
+        <v>129215752</v>
       </c>
       <c r="B128" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434813</v>
+        <v>434263</v>
       </c>
       <c r="R128" t="n">
-        <v>6806692</v>
+        <v>6806561</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,10 +13342,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129215745</v>
+        <v>129215751</v>
       </c>
       <c r="B129" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13353,21 +13353,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>434934</v>
+        <v>434673</v>
       </c>
       <c r="R129" t="n">
-        <v>6806753</v>
+        <v>6806460</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129215871</v>
+        <v>129215889</v>
       </c>
       <c r="B130" t="n">
         <v>79041</v>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434443</v>
+        <v>434813</v>
       </c>
       <c r="R130" t="n">
-        <v>6806595</v>
+        <v>6806692</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215761</v>
+        <v>129215767</v>
       </c>
       <c r="B2" t="n">
-        <v>79631</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434924</v>
+        <v>434546</v>
       </c>
       <c r="R2" t="n">
-        <v>6806749</v>
+        <v>6806482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +780,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215876</v>
+        <v>129215775</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434591</v>
+        <v>434334</v>
       </c>
       <c r="R3" t="n">
-        <v>6806739</v>
+        <v>6806593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +885,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215864</v>
+        <v>129215770</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434319</v>
+        <v>434136</v>
       </c>
       <c r="R4" t="n">
-        <v>6806589</v>
+        <v>6806558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,53 +990,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215767</v>
+        <v>129215761</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434546</v>
+        <v>434924</v>
       </c>
       <c r="R5" t="n">
-        <v>6806482</v>
+        <v>6806749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,53 +1087,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215775</v>
+        <v>129215876</v>
       </c>
       <c r="B6" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434334</v>
+        <v>434591</v>
       </c>
       <c r="R6" t="n">
-        <v>6806593</v>
+        <v>6806739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,53 +1184,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215770</v>
+        <v>129215864</v>
       </c>
       <c r="B7" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434136</v>
+        <v>434319</v>
       </c>
       <c r="R7" t="n">
-        <v>6806558</v>
+        <v>6806589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1281,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129215888</v>
+        <v>129215846</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434913</v>
+        <v>434523</v>
       </c>
       <c r="R8" t="n">
-        <v>6806699</v>
+        <v>6806496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129215846</v>
+        <v>129215888</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434523</v>
+        <v>434913</v>
       </c>
       <c r="R9" t="n">
-        <v>6806496</v>
+        <v>6806699</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215795</v>
+        <v>129215736</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,42 +1486,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434758</v>
+        <v>434605</v>
       </c>
       <c r="R10" t="n">
-        <v>6806435</v>
+        <v>6806750</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215903</v>
+        <v>129215813</v>
       </c>
       <c r="B11" t="n">
-        <v>88940</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1591,37 +1583,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434350</v>
+        <v>434803</v>
       </c>
       <c r="R11" t="n">
-        <v>6806600</v>
+        <v>6806683</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,7 +1651,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1681,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215736</v>
+        <v>129215903</v>
       </c>
       <c r="B12" t="n">
-        <v>79660</v>
+        <v>88940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,34 +1680,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434605</v>
+        <v>434350</v>
       </c>
       <c r="R12" t="n">
-        <v>6806750</v>
+        <v>6806600</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1751,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1972,10 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215813</v>
+        <v>129215795</v>
       </c>
       <c r="B15" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,34 +1975,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434803</v>
+        <v>434758</v>
       </c>
       <c r="R15" t="n">
-        <v>6806683</v>
+        <v>6806435</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2069,53 +2069,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129215766</v>
+        <v>129215893</v>
       </c>
       <c r="B16" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434601</v>
+        <v>434908</v>
       </c>
       <c r="R16" t="n">
-        <v>6806475</v>
+        <v>6806633</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,45 +2263,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129215893</v>
+        <v>129215766</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434908</v>
+        <v>434601</v>
       </c>
       <c r="R18" t="n">
-        <v>6806633</v>
+        <v>6806475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215737</v>
+        <v>129215877</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434585</v>
+        <v>434596</v>
       </c>
       <c r="R20" t="n">
-        <v>6806746</v>
+        <v>6806729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215877</v>
+        <v>129215856</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434596</v>
+        <v>434194</v>
       </c>
       <c r="R21" t="n">
-        <v>6806729</v>
+        <v>6806560</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215856</v>
+        <v>129215878</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2688,16 +2688,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434194</v>
+        <v>434621</v>
       </c>
       <c r="R22" t="n">
-        <v>6806560</v>
+        <v>6806786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2738,6 +2741,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2756,10 +2760,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215735</v>
+        <v>129215859</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2771,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2795,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434571</v>
+        <v>434177</v>
       </c>
       <c r="R23" t="n">
-        <v>6806718</v>
+        <v>6806592</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,7 +2857,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215744</v>
+        <v>129215737</v>
       </c>
       <c r="B24" t="n">
         <v>79660</v>
@@ -2882,19 +2886,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434950</v>
+        <v>434585</v>
       </c>
       <c r="R24" t="n">
-        <v>6806749</v>
+        <v>6806746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2935,7 +2936,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215758</v>
+        <v>129215735</v>
       </c>
       <c r="B25" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434928</v>
+        <v>434571</v>
       </c>
       <c r="R25" t="n">
-        <v>6806794</v>
+        <v>6806718</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215800</v>
+        <v>129215744</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3062,31 +3062,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3094,10 +3089,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434596</v>
+        <v>434950</v>
       </c>
       <c r="R26" t="n">
-        <v>6806728</v>
+        <v>6806749</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3138,6 +3133,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3156,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215793</v>
+        <v>129215800</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3167,21 +3163,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3189,7 +3185,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3199,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434920</v>
+        <v>434596</v>
       </c>
       <c r="R27" t="n">
-        <v>6806792</v>
+        <v>6806728</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3261,10 +3257,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215878</v>
+        <v>129215793</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3272,26 +3268,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3299,10 +3300,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434621</v>
+        <v>434920</v>
       </c>
       <c r="R28" t="n">
-        <v>6806786</v>
+        <v>6806792</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3343,7 +3344,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3362,45 +3362,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215859</v>
+        <v>129215782</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434177</v>
+        <v>434568</v>
       </c>
       <c r="R29" t="n">
-        <v>6806592</v>
+        <v>6806730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3459,53 +3467,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215782</v>
+        <v>129215758</v>
       </c>
       <c r="B30" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434568</v>
+        <v>434928</v>
       </c>
       <c r="R30" t="n">
-        <v>6806730</v>
+        <v>6806794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215881</v>
+        <v>129215810</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3575,37 +3575,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434834</v>
+        <v>434908</v>
       </c>
       <c r="R31" t="n">
-        <v>6806837</v>
+        <v>6806733</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3646,7 +3643,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3665,10 +3661,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215750</v>
+        <v>129215881</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,34 +3672,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434775</v>
+        <v>434834</v>
       </c>
       <c r="R32" t="n">
-        <v>6806482</v>
+        <v>6806837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3744,6 +3743,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3762,53 +3762,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215780</v>
+        <v>129215750</v>
       </c>
       <c r="B33" t="n">
-        <v>56917</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434449</v>
+        <v>434775</v>
       </c>
       <c r="R33" t="n">
-        <v>6806667</v>
+        <v>6806482</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3867,45 +3859,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129215810</v>
+        <v>129215780</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>56917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434908</v>
+        <v>434449</v>
       </c>
       <c r="R34" t="n">
-        <v>6806733</v>
+        <v>6806667</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129215822</v>
+        <v>129215756</v>
       </c>
       <c r="B35" t="n">
-        <v>78798</v>
+        <v>79631</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3975,34 +3975,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434936</v>
+        <v>434857</v>
       </c>
       <c r="R35" t="n">
-        <v>6806756</v>
+        <v>6806824</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4043,6 +4046,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4061,10 +4065,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129215823</v>
+        <v>129215809</v>
       </c>
       <c r="B36" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4072,21 +4076,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4096,10 +4100,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434906</v>
+        <v>434843</v>
       </c>
       <c r="R36" t="n">
-        <v>6806734</v>
+        <v>6806853</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4158,10 +4162,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129215902</v>
+        <v>129215822</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4169,37 +4173,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434784</v>
+        <v>434936</v>
       </c>
       <c r="R37" t="n">
-        <v>6806543</v>
+        <v>6806756</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4234,18 +4235,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4264,10 +4259,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129215738</v>
+        <v>129215823</v>
       </c>
       <c r="B38" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,21 +4270,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4299,10 +4294,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434764</v>
+        <v>434906</v>
       </c>
       <c r="R38" t="n">
-        <v>6806804</v>
+        <v>6806734</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4361,7 +4356,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129215869</v>
+        <v>129215902</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4390,16 +4385,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434432</v>
+        <v>434784</v>
       </c>
       <c r="R39" t="n">
-        <v>6806606</v>
+        <v>6806543</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4434,12 +4432,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4555,10 +4559,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215798</v>
+        <v>129215869</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4566,42 +4570,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434244</v>
+        <v>434432</v>
       </c>
       <c r="R41" t="n">
-        <v>6806571</v>
+        <v>6806606</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4660,10 +4656,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215756</v>
+        <v>129215738</v>
       </c>
       <c r="B42" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4671,37 +4667,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434857</v>
+        <v>434764</v>
       </c>
       <c r="R42" t="n">
-        <v>6806824</v>
+        <v>6806804</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4742,7 +4735,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4761,10 +4753,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215809</v>
+        <v>129215798</v>
       </c>
       <c r="B43" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,34 +4764,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434843</v>
+        <v>434244</v>
       </c>
       <c r="R43" t="n">
-        <v>6806853</v>
+        <v>6806571</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4858,10 +4858,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129215799</v>
+        <v>129215882</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,42 +4869,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434142</v>
+        <v>434851</v>
       </c>
       <c r="R44" t="n">
-        <v>6806549</v>
+        <v>6806867</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,7 +4955,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129215882</v>
+        <v>129215845</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -4998,10 +4990,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434851</v>
+        <v>434585</v>
       </c>
       <c r="R45" t="n">
-        <v>6806867</v>
+        <v>6806500</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5060,10 +5052,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215845</v>
+        <v>129215799</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5071,34 +5063,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434585</v>
+        <v>434142</v>
       </c>
       <c r="R46" t="n">
-        <v>6806500</v>
+        <v>6806549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5351,45 +5351,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215904</v>
+        <v>129215790</v>
       </c>
       <c r="B49" t="n">
-        <v>79660</v>
+        <v>56917</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434857</v>
+        <v>434809</v>
       </c>
       <c r="R49" t="n">
-        <v>6806833</v>
+        <v>6806535</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5448,7 +5456,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215790</v>
+        <v>129215786</v>
       </c>
       <c r="B50" t="n">
         <v>56917</v>
@@ -5491,10 +5499,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434809</v>
+        <v>434883</v>
       </c>
       <c r="R50" t="n">
-        <v>6806535</v>
+        <v>6806675</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5553,53 +5561,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215786</v>
+        <v>129215755</v>
       </c>
       <c r="B51" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434883</v>
+        <v>434812</v>
       </c>
       <c r="R51" t="n">
-        <v>6806675</v>
+        <v>6806771</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,7 +5658,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215755</v>
+        <v>129215760</v>
       </c>
       <c r="B52" t="n">
         <v>79631</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434812</v>
+        <v>434895</v>
       </c>
       <c r="R52" t="n">
-        <v>6806771</v>
+        <v>6806736</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,10 +5755,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215760</v>
+        <v>129215808</v>
       </c>
       <c r="B53" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5766,21 +5766,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434895</v>
+        <v>434355</v>
       </c>
       <c r="R53" t="n">
-        <v>6806736</v>
+        <v>6806519</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,10 +5852,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129215808</v>
+        <v>129215904</v>
       </c>
       <c r="B54" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5863,21 +5863,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434355</v>
+        <v>434857</v>
       </c>
       <c r="R54" t="n">
-        <v>6806519</v>
+        <v>6806833</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129215896</v>
+        <v>129215841</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434783</v>
+        <v>434433</v>
       </c>
       <c r="R55" t="n">
-        <v>6806478</v>
+        <v>6806597</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6028,6 +6028,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6143,7 +6144,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129215841</v>
+        <v>129215896</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6178,10 +6179,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434433</v>
+        <v>434783</v>
       </c>
       <c r="R57" t="n">
-        <v>6806597</v>
+        <v>6806478</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,7 +6223,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215880</v>
+        <v>129215739</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6567,21 +6567,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434845</v>
+        <v>434817</v>
       </c>
       <c r="R61" t="n">
-        <v>6806812</v>
+        <v>6806766</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129215862</v>
+        <v>129215743</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6688,10 +6688,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434270</v>
+        <v>434922</v>
       </c>
       <c r="R62" t="n">
-        <v>6806602</v>
+        <v>6806795</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6750,10 +6750,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215885</v>
+        <v>129215819</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6761,34 +6761,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434884</v>
+        <v>434773</v>
       </c>
       <c r="R63" t="n">
-        <v>6806816</v>
+        <v>6806803</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6829,6 +6832,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6847,10 +6851,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215819</v>
+        <v>129215880</v>
       </c>
       <c r="B64" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6858,37 +6862,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434773</v>
+        <v>434845</v>
       </c>
       <c r="R64" t="n">
-        <v>6806803</v>
+        <v>6806812</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6929,7 +6930,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215739</v>
+        <v>129215824</v>
       </c>
       <c r="B65" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434817</v>
+        <v>434922</v>
       </c>
       <c r="R65" t="n">
-        <v>6806766</v>
+        <v>6806746</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215824</v>
+        <v>129215885</v>
       </c>
       <c r="B66" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434922</v>
+        <v>434884</v>
       </c>
       <c r="R66" t="n">
-        <v>6806746</v>
+        <v>6806816</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7142,10 +7142,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129215743</v>
+        <v>129215862</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7153,21 +7153,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434922</v>
+        <v>434270</v>
       </c>
       <c r="R67" t="n">
-        <v>6806795</v>
+        <v>6806602</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7239,10 +7239,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215899</v>
+        <v>129215742</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7250,34 +7250,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434763</v>
+        <v>434910</v>
       </c>
       <c r="R68" t="n">
-        <v>6806436</v>
+        <v>6806856</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7318,6 +7321,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7336,53 +7340,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129215764</v>
+        <v>129215891</v>
       </c>
       <c r="B69" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434687</v>
+        <v>434812</v>
       </c>
       <c r="R69" t="n">
-        <v>6806459</v>
+        <v>6806610</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7441,10 +7437,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129215742</v>
+        <v>129215898</v>
       </c>
       <c r="B70" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7452,37 +7448,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434910</v>
+        <v>434759</v>
       </c>
       <c r="R70" t="n">
-        <v>6806856</v>
+        <v>6806455</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7523,7 +7516,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7542,10 +7534,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215898</v>
+        <v>129215821</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7553,21 +7545,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7577,10 +7569,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434759</v>
+        <v>434913</v>
       </c>
       <c r="R71" t="n">
-        <v>6806455</v>
+        <v>6806785</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7639,10 +7631,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215821</v>
+        <v>129215895</v>
       </c>
       <c r="B72" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7650,21 +7642,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7674,10 +7666,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434913</v>
+        <v>434858</v>
       </c>
       <c r="R72" t="n">
-        <v>6806785</v>
+        <v>6806562</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7736,7 +7728,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129215891</v>
+        <v>129215899</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7771,10 +7763,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434812</v>
+        <v>434763</v>
       </c>
       <c r="R73" t="n">
-        <v>6806610</v>
+        <v>6806436</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7833,7 +7825,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215895</v>
+        <v>129215851</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -7868,10 +7860,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434858</v>
+        <v>434362</v>
       </c>
       <c r="R74" t="n">
-        <v>6806562</v>
+        <v>6806519</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7930,45 +7922,53 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215851</v>
+        <v>129215764</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434362</v>
+        <v>434687</v>
       </c>
       <c r="R75" t="n">
-        <v>6806519</v>
+        <v>6806459</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8030,7 +8030,7 @@
         <v>129215807</v>
       </c>
       <c r="B76" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215858</v>
+        <v>129215887</v>
       </c>
       <c r="B77" t="n">
         <v>79041</v>
@@ -8164,10 +8164,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434135</v>
+        <v>434936</v>
       </c>
       <c r="R77" t="n">
-        <v>6806556</v>
+        <v>6806726</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8226,7 +8226,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215887</v>
+        <v>129215858</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8261,10 +8261,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434936</v>
+        <v>434135</v>
       </c>
       <c r="R78" t="n">
-        <v>6806726</v>
+        <v>6806556</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8323,7 +8323,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215805</v>
+        <v>129215801</v>
       </c>
       <c r="B79" t="n">
         <v>57724</v>
@@ -8356,7 +8356,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434761</v>
+        <v>434883</v>
       </c>
       <c r="R79" t="n">
-        <v>6806449</v>
+        <v>6806894</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8428,7 +8428,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215801</v>
+        <v>129215805</v>
       </c>
       <c r="B80" t="n">
         <v>57724</v>
@@ -8461,7 +8461,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434883</v>
+        <v>434761</v>
       </c>
       <c r="R80" t="n">
-        <v>6806894</v>
+        <v>6806449</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8638,10 +8638,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215741</v>
+        <v>129215803</v>
       </c>
       <c r="B82" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8649,34 +8649,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434844</v>
+        <v>434895</v>
       </c>
       <c r="R82" t="n">
-        <v>6806852</v>
+        <v>6806664</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8735,10 +8743,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215863</v>
+        <v>129215804</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8746,34 +8754,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434279</v>
+        <v>434880</v>
       </c>
       <c r="R83" t="n">
-        <v>6806587</v>
+        <v>6806584</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8832,7 +8848,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215850</v>
+        <v>129215886</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -8867,10 +8883,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434376</v>
+        <v>434934</v>
       </c>
       <c r="R84" t="n">
-        <v>6806560</v>
+        <v>6806762</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8929,7 +8945,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215843</v>
+        <v>129215863</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -8964,10 +8980,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434628</v>
+        <v>434279</v>
       </c>
       <c r="R85" t="n">
-        <v>6806457</v>
+        <v>6806587</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9026,10 +9042,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215803</v>
+        <v>129215853</v>
       </c>
       <c r="B86" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9037,42 +9053,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434895</v>
+        <v>434280</v>
       </c>
       <c r="R86" t="n">
-        <v>6806664</v>
+        <v>6806556</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9131,10 +9139,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215804</v>
+        <v>129215850</v>
       </c>
       <c r="B87" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9142,42 +9150,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434880</v>
+        <v>434376</v>
       </c>
       <c r="R87" t="n">
-        <v>6806584</v>
+        <v>6806560</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9236,53 +9236,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215771</v>
+        <v>129215843</v>
       </c>
       <c r="B88" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434229</v>
+        <v>434628</v>
       </c>
       <c r="R88" t="n">
-        <v>6806613</v>
+        <v>6806457</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9341,42 +9333,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215768</v>
+        <v>129215861</v>
       </c>
       <c r="B89" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9384,10 +9371,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434422</v>
+        <v>434259</v>
       </c>
       <c r="R89" t="n">
-        <v>6806522</v>
+        <v>6806607</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9428,6 +9415,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9446,53 +9434,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215787</v>
+        <v>129215741</v>
       </c>
       <c r="B90" t="n">
-        <v>56917</v>
+        <v>79660</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434813</v>
+        <v>434844</v>
       </c>
       <c r="R90" t="n">
-        <v>6806656</v>
+        <v>6806852</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,7 +9531,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215774</v>
+        <v>129215771</v>
       </c>
       <c r="B91" t="n">
         <v>56917</v>
@@ -9594,10 +9574,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434307</v>
+        <v>434229</v>
       </c>
       <c r="R91" t="n">
-        <v>6806608</v>
+        <v>6806613</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9656,45 +9636,53 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215853</v>
+        <v>129215768</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434280</v>
+        <v>434422</v>
       </c>
       <c r="R92" t="n">
-        <v>6806556</v>
+        <v>6806522</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9753,37 +9741,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215861</v>
+        <v>129215787</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -9791,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434259</v>
+        <v>434813</v>
       </c>
       <c r="R93" t="n">
-        <v>6806607</v>
+        <v>6806656</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9835,7 +9828,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -9854,45 +9846,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215886</v>
+        <v>129215774</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434934</v>
+        <v>434307</v>
       </c>
       <c r="R94" t="n">
-        <v>6806762</v>
+        <v>6806608</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10052,45 +10052,53 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129215865</v>
+        <v>129215818</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>434358</v>
+        <v>434849</v>
       </c>
       <c r="R96" t="n">
-        <v>6806608</v>
+        <v>6806700</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10149,53 +10157,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129215776</v>
+        <v>129215759</v>
       </c>
       <c r="B97" t="n">
-        <v>56917</v>
+        <v>79631</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434445</v>
+        <v>434930</v>
       </c>
       <c r="R97" t="n">
-        <v>6806699</v>
+        <v>6806768</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10254,42 +10254,37 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215777</v>
+        <v>129215883</v>
       </c>
       <c r="B98" t="n">
-        <v>56917</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10297,10 +10292,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434432</v>
+        <v>434920</v>
       </c>
       <c r="R98" t="n">
-        <v>6806670</v>
+        <v>6806876</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10335,12 +10330,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10359,53 +10360,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215818</v>
+        <v>129215860</v>
       </c>
       <c r="B99" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434849</v>
+        <v>434241</v>
       </c>
       <c r="R99" t="n">
-        <v>6806700</v>
+        <v>6806618</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10464,10 +10457,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215759</v>
+        <v>129215865</v>
       </c>
       <c r="B100" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10475,21 +10468,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10499,10 +10492,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434930</v>
+        <v>434358</v>
       </c>
       <c r="R100" t="n">
-        <v>6806768</v>
+        <v>6806608</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10561,37 +10554,42 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215883</v>
+        <v>129215776</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -10599,10 +10597,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434920</v>
+        <v>434445</v>
       </c>
       <c r="R101" t="n">
-        <v>6806876</v>
+        <v>6806699</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10637,18 +10635,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -10667,45 +10659,53 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215860</v>
+        <v>129215777</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434241</v>
+        <v>434432</v>
       </c>
       <c r="R102" t="n">
-        <v>6806618</v>
+        <v>6806670</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10764,10 +10764,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215825</v>
+        <v>129215873</v>
       </c>
       <c r="B103" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10775,21 +10775,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10799,10 +10799,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434799</v>
+        <v>434463</v>
       </c>
       <c r="R103" t="n">
-        <v>6806687</v>
+        <v>6806664</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129215873</v>
+        <v>129215825</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434463</v>
+        <v>434799</v>
       </c>
       <c r="R105" t="n">
-        <v>6806664</v>
+        <v>6806687</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11265,7 +11265,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215848</v>
+        <v>129215849</v>
       </c>
       <c r="B108" t="n">
         <v>79041</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434473</v>
+        <v>434437</v>
       </c>
       <c r="R108" t="n">
-        <v>6806453</v>
+        <v>6806501</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11362,7 +11362,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215879</v>
+        <v>129215848</v>
       </c>
       <c r="B109" t="n">
         <v>79041</v>
@@ -11397,10 +11397,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434627</v>
+        <v>434473</v>
       </c>
       <c r="R109" t="n">
-        <v>6806787</v>
+        <v>6806453</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11459,7 +11459,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215849</v>
+        <v>129215879</v>
       </c>
       <c r="B110" t="n">
         <v>79041</v>
@@ -11494,10 +11494,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434437</v>
+        <v>434627</v>
       </c>
       <c r="R110" t="n">
-        <v>6806501</v>
+        <v>6806787</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215796</v>
+        <v>129215734</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11979,42 +11979,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434635</v>
+        <v>434546</v>
       </c>
       <c r="R115" t="n">
-        <v>6806453</v>
+        <v>6806737</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12073,10 +12065,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215797</v>
+        <v>129215900</v>
       </c>
       <c r="B116" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12084,42 +12076,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434602</v>
+        <v>434775</v>
       </c>
       <c r="R116" t="n">
-        <v>6806495</v>
+        <v>6806423</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12178,10 +12162,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215812</v>
+        <v>129215867</v>
       </c>
       <c r="B117" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12189,21 +12173,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12213,10 +12197,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434922</v>
+        <v>434375</v>
       </c>
       <c r="R117" t="n">
-        <v>6806746</v>
+        <v>6806574</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12275,10 +12259,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215754</v>
+        <v>129215844</v>
       </c>
       <c r="B118" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12286,21 +12270,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12310,10 +12294,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434774</v>
+        <v>434623</v>
       </c>
       <c r="R118" t="n">
-        <v>6806803</v>
+        <v>6806466</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12372,7 +12356,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215867</v>
+        <v>129215868</v>
       </c>
       <c r="B119" t="n">
         <v>79041</v>
@@ -12407,10 +12391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434375</v>
+        <v>434415</v>
       </c>
       <c r="R119" t="n">
-        <v>6806574</v>
+        <v>6806576</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12469,10 +12453,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215734</v>
+        <v>129215796</v>
       </c>
       <c r="B120" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12480,34 +12464,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434546</v>
+        <v>434635</v>
       </c>
       <c r="R120" t="n">
-        <v>6806737</v>
+        <v>6806453</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12566,10 +12558,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215868</v>
+        <v>129215797</v>
       </c>
       <c r="B121" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12577,34 +12569,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434415</v>
+        <v>434602</v>
       </c>
       <c r="R121" t="n">
-        <v>6806576</v>
+        <v>6806495</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,10 +12663,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215900</v>
+        <v>129215812</v>
       </c>
       <c r="B122" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12674,21 +12674,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12698,10 +12698,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434775</v>
+        <v>434922</v>
       </c>
       <c r="R122" t="n">
-        <v>6806423</v>
+        <v>6806746</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12760,10 +12760,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215844</v>
+        <v>129215754</v>
       </c>
       <c r="B123" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12771,21 +12771,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12795,10 +12795,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434623</v>
+        <v>434774</v>
       </c>
       <c r="R123" t="n">
-        <v>6806466</v>
+        <v>6806803</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13051,10 +13051,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129215745</v>
+        <v>129215889</v>
       </c>
       <c r="B126" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13062,21 +13062,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13086,10 +13086,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434934</v>
+        <v>434813</v>
       </c>
       <c r="R126" t="n">
-        <v>6806753</v>
+        <v>6806692</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13245,10 +13245,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129215752</v>
+        <v>129215745</v>
       </c>
       <c r="B128" t="n">
-        <v>79631</v>
+        <v>79660</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434263</v>
+        <v>434934</v>
       </c>
       <c r="R128" t="n">
-        <v>6806561</v>
+        <v>6806753</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13342,7 +13342,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129215751</v>
+        <v>129215752</v>
       </c>
       <c r="B129" t="n">
         <v>79631</v>
@@ -13377,10 +13377,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>434673</v>
+        <v>434263</v>
       </c>
       <c r="R129" t="n">
-        <v>6806460</v>
+        <v>6806561</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13439,10 +13439,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129215889</v>
+        <v>129215751</v>
       </c>
       <c r="B130" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13450,21 +13450,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434813</v>
+        <v>434673</v>
       </c>
       <c r="R130" t="n">
-        <v>6806692</v>
+        <v>6806460</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129215767</v>
+        <v>129215876</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434546</v>
+        <v>434591</v>
       </c>
       <c r="R2" t="n">
-        <v>6806482</v>
+        <v>6806739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,53 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215775</v>
+        <v>129215864</v>
       </c>
       <c r="B3" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434334</v>
+        <v>434319</v>
       </c>
       <c r="R3" t="n">
-        <v>6806593</v>
+        <v>6806589</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215770</v>
+        <v>129215767</v>
       </c>
       <c r="B4" t="n">
         <v>56917</v>
@@ -928,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434136</v>
+        <v>434546</v>
       </c>
       <c r="R4" t="n">
-        <v>6806558</v>
+        <v>6806482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,45 +974,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215761</v>
+        <v>129215775</v>
       </c>
       <c r="B5" t="n">
-        <v>79631</v>
+        <v>56917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434924</v>
+        <v>434334</v>
       </c>
       <c r="R5" t="n">
-        <v>6806749</v>
+        <v>6806593</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,45 +1079,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215876</v>
+        <v>129215770</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434591</v>
+        <v>434136</v>
       </c>
       <c r="R6" t="n">
-        <v>6806739</v>
+        <v>6806558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215864</v>
+        <v>129215761</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,21 +1195,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434319</v>
+        <v>434924</v>
       </c>
       <c r="R7" t="n">
-        <v>6806589</v>
+        <v>6806749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
         <v>129215846</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129215888</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>129215736</v>
       </c>
       <c r="B10" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215813</v>
+        <v>129215847</v>
       </c>
       <c r="B11" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,21 +1583,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434803</v>
+        <v>434523</v>
       </c>
       <c r="R11" t="n">
-        <v>6806683</v>
+        <v>6806508</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215903</v>
+        <v>129215875</v>
       </c>
       <c r="B12" t="n">
-        <v>88940</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,37 +1680,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434350</v>
+        <v>434516</v>
       </c>
       <c r="R12" t="n">
-        <v>6806600</v>
+        <v>6806695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,7 +1748,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1770,10 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215847</v>
+        <v>129215795</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,34 +1777,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434523</v>
+        <v>434758</v>
       </c>
       <c r="R13" t="n">
-        <v>6806508</v>
+        <v>6806435</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129215875</v>
+        <v>129215813</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,21 +1882,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434516</v>
+        <v>434803</v>
       </c>
       <c r="R14" t="n">
-        <v>6806695</v>
+        <v>6806683</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215795</v>
+        <v>129215903</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>88943</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,31 +1979,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2007,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434758</v>
+        <v>434350</v>
       </c>
       <c r="R15" t="n">
-        <v>6806435</v>
+        <v>6806600</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,6 +2050,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>129215893</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>129215890</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>129215757</v>
       </c>
       <c r="B19" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215877</v>
+        <v>129215737</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434596</v>
+        <v>434585</v>
       </c>
       <c r="R20" t="n">
-        <v>6806729</v>
+        <v>6806746</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215856</v>
+        <v>129215877</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434194</v>
+        <v>434596</v>
       </c>
       <c r="R21" t="n">
-        <v>6806560</v>
+        <v>6806729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215878</v>
+        <v>129215856</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2688,19 +2688,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434621</v>
+        <v>434194</v>
       </c>
       <c r="R22" t="n">
-        <v>6806786</v>
+        <v>6806560</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2738,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2760,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215859</v>
+        <v>129215735</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2771,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2795,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434177</v>
+        <v>434571</v>
       </c>
       <c r="R23" t="n">
-        <v>6806592</v>
+        <v>6806718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2857,10 +2853,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215737</v>
+        <v>129215744</v>
       </c>
       <c r="B24" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2886,16 +2882,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434585</v>
+        <v>434950</v>
       </c>
       <c r="R24" t="n">
-        <v>6806746</v>
+        <v>6806749</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,6 +2935,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2954,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215735</v>
+        <v>129215878</v>
       </c>
       <c r="B25" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2965,34 +2965,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434571</v>
+        <v>434621</v>
       </c>
       <c r="R25" t="n">
-        <v>6806718</v>
+        <v>6806786</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,6 +3036,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3051,10 +3055,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215744</v>
+        <v>129215859</v>
       </c>
       <c r="B26" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3062,37 +3066,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434950</v>
+        <v>434177</v>
       </c>
       <c r="R26" t="n">
-        <v>6806749</v>
+        <v>6806592</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3133,7 +3134,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>129215758</v>
       </c>
       <c r="B30" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215810</v>
+        <v>129215881</v>
       </c>
       <c r="B31" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3575,34 +3575,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434908</v>
+        <v>434834</v>
       </c>
       <c r="R31" t="n">
-        <v>6806733</v>
+        <v>6806837</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3643,6 +3646,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3661,10 +3665,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215881</v>
+        <v>129215750</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3672,37 +3676,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434834</v>
+        <v>434775</v>
       </c>
       <c r="R32" t="n">
-        <v>6806837</v>
+        <v>6806482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3743,7 +3744,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3762,45 +3762,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215750</v>
+        <v>129215780</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>56917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434775</v>
+        <v>434449</v>
       </c>
       <c r="R33" t="n">
-        <v>6806482</v>
+        <v>6806667</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,53 +3867,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129215780</v>
+        <v>129215810</v>
       </c>
       <c r="B34" t="n">
-        <v>56917</v>
+        <v>78801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434449</v>
+        <v>434908</v>
       </c>
       <c r="R34" t="n">
-        <v>6806667</v>
+        <v>6806733</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3967,7 +3967,7 @@
         <v>129215756</v>
       </c>
       <c r="B35" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>129215809</v>
       </c>
       <c r="B36" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129215822</v>
+        <v>129215798</v>
       </c>
       <c r="B37" t="n">
-        <v>78798</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4173,34 +4173,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434936</v>
+        <v>434244</v>
       </c>
       <c r="R37" t="n">
-        <v>6806756</v>
+        <v>6806571</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4259,10 +4267,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129215823</v>
+        <v>129215822</v>
       </c>
       <c r="B38" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4294,10 +4302,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434906</v>
+        <v>434936</v>
       </c>
       <c r="R38" t="n">
-        <v>6806734</v>
+        <v>6806756</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4356,10 +4364,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129215902</v>
+        <v>129215823</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4367,37 +4375,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434784</v>
+        <v>434906</v>
       </c>
       <c r="R39" t="n">
-        <v>6806543</v>
+        <v>6806734</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4432,18 +4437,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4462,10 +4461,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129215854</v>
+        <v>129215902</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4491,16 +4490,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434268</v>
+        <v>434784</v>
       </c>
       <c r="R40" t="n">
-        <v>6806557</v>
+        <v>6806543</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4535,12 +4537,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4559,10 +4567,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215869</v>
+        <v>129215738</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4570,21 +4578,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4594,10 +4602,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434432</v>
+        <v>434764</v>
       </c>
       <c r="R41" t="n">
-        <v>6806606</v>
+        <v>6806804</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4656,10 +4664,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215738</v>
+        <v>129215854</v>
       </c>
       <c r="B42" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4667,21 +4675,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4691,10 +4699,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434764</v>
+        <v>434268</v>
       </c>
       <c r="R42" t="n">
-        <v>6806804</v>
+        <v>6806557</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4753,10 +4761,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215798</v>
+        <v>129215869</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4764,42 +4772,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434244</v>
+        <v>434432</v>
       </c>
       <c r="R43" t="n">
-        <v>6806571</v>
+        <v>6806606</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4861,7 +4861,7 @@
         <v>129215882</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>129215845</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>129215753</v>
       </c>
       <c r="B47" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129215857</v>
+        <v>129215755</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5265,21 +5265,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434179</v>
+        <v>434812</v>
       </c>
       <c r="R48" t="n">
-        <v>6806557</v>
+        <v>6806771</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5351,53 +5351,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215790</v>
+        <v>129215760</v>
       </c>
       <c r="B49" t="n">
-        <v>56917</v>
+        <v>79633</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434809</v>
+        <v>434895</v>
       </c>
       <c r="R49" t="n">
-        <v>6806535</v>
+        <v>6806736</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5456,53 +5448,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215786</v>
+        <v>129215808</v>
       </c>
       <c r="B50" t="n">
-        <v>56917</v>
+        <v>78801</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434883</v>
+        <v>434355</v>
       </c>
       <c r="R50" t="n">
-        <v>6806675</v>
+        <v>6806519</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5561,10 +5545,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215755</v>
+        <v>129215857</v>
       </c>
       <c r="B51" t="n">
-        <v>79631</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5572,21 +5556,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5596,10 +5580,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434812</v>
+        <v>434179</v>
       </c>
       <c r="R51" t="n">
-        <v>6806771</v>
+        <v>6806557</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,10 +5642,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215760</v>
+        <v>129215904</v>
       </c>
       <c r="B52" t="n">
-        <v>79631</v>
+        <v>79662</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5669,21 +5653,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5693,10 +5677,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434895</v>
+        <v>434857</v>
       </c>
       <c r="R52" t="n">
-        <v>6806736</v>
+        <v>6806833</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5755,45 +5739,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215808</v>
+        <v>129215790</v>
       </c>
       <c r="B53" t="n">
-        <v>78799</v>
+        <v>56917</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434355</v>
+        <v>434809</v>
       </c>
       <c r="R53" t="n">
-        <v>6806519</v>
+        <v>6806535</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,45 +5844,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129215904</v>
+        <v>129215786</v>
       </c>
       <c r="B54" t="n">
-        <v>79660</v>
+        <v>56917</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434857</v>
+        <v>434883</v>
       </c>
       <c r="R54" t="n">
-        <v>6806833</v>
+        <v>6806675</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5952,7 +5952,7 @@
         <v>129215841</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>129215874</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>129215896</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215739</v>
+        <v>129215819</v>
       </c>
       <c r="B61" t="n">
-        <v>79660</v>
+        <v>78800</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6567,34 +6567,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434817</v>
+        <v>434773</v>
       </c>
       <c r="R61" t="n">
-        <v>6806766</v>
+        <v>6806803</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6635,6 +6638,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6653,10 +6657,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129215743</v>
+        <v>129215880</v>
       </c>
       <c r="B62" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6664,21 +6668,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6688,10 +6692,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434922</v>
+        <v>434845</v>
       </c>
       <c r="R62" t="n">
-        <v>6806795</v>
+        <v>6806812</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6750,10 +6754,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215819</v>
+        <v>129215739</v>
       </c>
       <c r="B63" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6761,37 +6765,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434773</v>
+        <v>434817</v>
       </c>
       <c r="R63" t="n">
-        <v>6806803</v>
+        <v>6806766</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6832,7 +6833,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6851,10 +6851,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215880</v>
+        <v>129215824</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6862,21 +6862,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434845</v>
+        <v>434922</v>
       </c>
       <c r="R64" t="n">
-        <v>6806812</v>
+        <v>6806746</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215824</v>
+        <v>129215885</v>
       </c>
       <c r="B65" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434922</v>
+        <v>434884</v>
       </c>
       <c r="R65" t="n">
-        <v>6806746</v>
+        <v>6806816</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215885</v>
+        <v>129215743</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7056,21 +7056,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434884</v>
+        <v>434922</v>
       </c>
       <c r="R66" t="n">
-        <v>6806816</v>
+        <v>6806795</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7145,7 +7145,7 @@
         <v>129215862</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7239,37 +7239,42 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215742</v>
+        <v>129215764</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>56917</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7277,10 +7282,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434910</v>
+        <v>434687</v>
       </c>
       <c r="R68" t="n">
-        <v>6806856</v>
+        <v>6806459</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7321,7 +7326,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7340,45 +7344,49 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129215891</v>
+        <v>129215807</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>97587</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434812</v>
+        <v>434541</v>
       </c>
       <c r="R69" t="n">
-        <v>6806610</v>
+        <v>6806479</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7419,6 +7427,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7437,10 +7446,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129215898</v>
+        <v>129215742</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7448,34 +7457,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434759</v>
+        <v>434910</v>
       </c>
       <c r="R70" t="n">
-        <v>6806455</v>
+        <v>6806856</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7516,6 +7528,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7534,10 +7547,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215821</v>
+        <v>129215891</v>
       </c>
       <c r="B71" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7545,21 +7558,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7569,10 +7582,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434913</v>
+        <v>434812</v>
       </c>
       <c r="R71" t="n">
-        <v>6806785</v>
+        <v>6806610</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7631,10 +7644,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215895</v>
+        <v>129215898</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7666,10 +7679,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434858</v>
+        <v>434759</v>
       </c>
       <c r="R72" t="n">
-        <v>6806562</v>
+        <v>6806455</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7728,10 +7741,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129215899</v>
+        <v>129215821</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7739,21 +7752,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7763,10 +7776,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434763</v>
+        <v>434913</v>
       </c>
       <c r="R73" t="n">
-        <v>6806436</v>
+        <v>6806785</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7825,10 +7838,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215851</v>
+        <v>129215895</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7860,10 +7873,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434362</v>
+        <v>434858</v>
       </c>
       <c r="R74" t="n">
-        <v>6806519</v>
+        <v>6806562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7922,53 +7935,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215764</v>
+        <v>129215899</v>
       </c>
       <c r="B75" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434687</v>
+        <v>434763</v>
       </c>
       <c r="R75" t="n">
-        <v>6806459</v>
+        <v>6806436</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8027,49 +8032,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215807</v>
+        <v>129215851</v>
       </c>
       <c r="B76" t="n">
-        <v>97583</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434541</v>
+        <v>434362</v>
       </c>
       <c r="R76" t="n">
-        <v>6806479</v>
+        <v>6806519</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8110,7 +8111,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8129,10 +8129,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215887</v>
+        <v>129215801</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8140,34 +8140,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434936</v>
+        <v>434883</v>
       </c>
       <c r="R77" t="n">
-        <v>6806726</v>
+        <v>6806894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8226,10 +8234,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215858</v>
+        <v>129215805</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8237,34 +8245,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434135</v>
+        <v>434761</v>
       </c>
       <c r="R78" t="n">
-        <v>6806556</v>
+        <v>6806449</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8323,32 +8339,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215801</v>
+        <v>129215773</v>
       </c>
       <c r="B79" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8356,7 +8372,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8366,10 +8382,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434883</v>
+        <v>434241</v>
       </c>
       <c r="R79" t="n">
-        <v>6806894</v>
+        <v>6806606</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8428,10 +8444,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215805</v>
+        <v>129215887</v>
       </c>
       <c r="B80" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8439,42 +8455,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434761</v>
+        <v>434936</v>
       </c>
       <c r="R80" t="n">
-        <v>6806449</v>
+        <v>6806726</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8533,53 +8541,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129215773</v>
+        <v>129215858</v>
       </c>
       <c r="B81" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434241</v>
+        <v>434135</v>
       </c>
       <c r="R81" t="n">
-        <v>6806606</v>
+        <v>6806556</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8638,32 +8638,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215803</v>
+        <v>129215771</v>
       </c>
       <c r="B82" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8671,7 +8671,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -8681,10 +8681,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434895</v>
+        <v>434229</v>
       </c>
       <c r="R82" t="n">
-        <v>6806664</v>
+        <v>6806613</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8743,32 +8743,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215804</v>
+        <v>129215768</v>
       </c>
       <c r="B83" t="n">
-        <v>57724</v>
+        <v>56917</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8776,7 +8776,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434880</v>
+        <v>434422</v>
       </c>
       <c r="R83" t="n">
-        <v>6806584</v>
+        <v>6806522</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8848,45 +8848,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215886</v>
+        <v>129215787</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434934</v>
+        <v>434813</v>
       </c>
       <c r="R84" t="n">
-        <v>6806762</v>
+        <v>6806656</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8945,45 +8953,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215863</v>
+        <v>129215774</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434279</v>
+        <v>434307</v>
       </c>
       <c r="R85" t="n">
-        <v>6806587</v>
+        <v>6806608</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9042,10 +9058,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215853</v>
+        <v>129215886</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9077,10 +9093,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434280</v>
+        <v>434934</v>
       </c>
       <c r="R86" t="n">
-        <v>6806556</v>
+        <v>6806762</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9139,10 +9155,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215850</v>
+        <v>129215741</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9150,21 +9166,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9174,10 +9190,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434376</v>
+        <v>434844</v>
       </c>
       <c r="R87" t="n">
-        <v>6806560</v>
+        <v>6806852</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9236,10 +9252,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215843</v>
+        <v>129215863</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9271,10 +9287,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434628</v>
+        <v>434279</v>
       </c>
       <c r="R88" t="n">
-        <v>6806457</v>
+        <v>6806587</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9333,10 +9349,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215861</v>
+        <v>129215853</v>
       </c>
       <c r="B89" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9362,19 +9378,16 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434259</v>
+        <v>434280</v>
       </c>
       <c r="R89" t="n">
-        <v>6806607</v>
+        <v>6806556</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9415,7 +9428,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9434,10 +9446,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215741</v>
+        <v>129215850</v>
       </c>
       <c r="B90" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9445,21 +9457,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9469,10 +9481,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434844</v>
+        <v>434376</v>
       </c>
       <c r="R90" t="n">
-        <v>6806852</v>
+        <v>6806560</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9531,53 +9543,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215771</v>
+        <v>129215843</v>
       </c>
       <c r="B91" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434229</v>
+        <v>434628</v>
       </c>
       <c r="R91" t="n">
-        <v>6806613</v>
+        <v>6806457</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9636,42 +9640,37 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215768</v>
+        <v>129215861</v>
       </c>
       <c r="B92" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9679,10 +9678,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434422</v>
+        <v>434259</v>
       </c>
       <c r="R92" t="n">
-        <v>6806522</v>
+        <v>6806607</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9723,6 +9722,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9741,32 +9741,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215787</v>
+        <v>129215803</v>
       </c>
       <c r="B93" t="n">
-        <v>56917</v>
+        <v>57724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434813</v>
+        <v>434895</v>
       </c>
       <c r="R93" t="n">
-        <v>6806656</v>
+        <v>6806664</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9846,32 +9846,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215774</v>
+        <v>129215804</v>
       </c>
       <c r="B94" t="n">
-        <v>56917</v>
+        <v>57724</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9879,7 +9879,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -9889,10 +9889,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434307</v>
+        <v>434880</v>
       </c>
       <c r="R94" t="n">
-        <v>6806608</v>
+        <v>6806584</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9954,7 +9954,7 @@
         <v>129215872</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10052,42 +10052,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129215818</v>
+        <v>129215883</v>
       </c>
       <c r="B96" t="n">
-        <v>58097</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10095,10 +10090,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>434849</v>
+        <v>434920</v>
       </c>
       <c r="R96" t="n">
-        <v>6806700</v>
+        <v>6806876</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10133,12 +10128,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10157,10 +10158,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129215759</v>
+        <v>129215860</v>
       </c>
       <c r="B97" t="n">
-        <v>79631</v>
+        <v>79043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10168,21 +10169,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10192,10 +10193,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434930</v>
+        <v>434241</v>
       </c>
       <c r="R97" t="n">
-        <v>6806768</v>
+        <v>6806618</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10254,10 +10255,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215883</v>
+        <v>129215865</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10283,19 +10284,16 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434920</v>
+        <v>434358</v>
       </c>
       <c r="R98" t="n">
-        <v>6806876</v>
+        <v>6806608</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10330,18 +10328,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10360,45 +10352,53 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215860</v>
+        <v>129215776</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434241</v>
+        <v>434445</v>
       </c>
       <c r="R99" t="n">
-        <v>6806618</v>
+        <v>6806699</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10457,45 +10457,53 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215865</v>
+        <v>129215777</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>56917</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434358</v>
+        <v>434432</v>
       </c>
       <c r="R100" t="n">
-        <v>6806608</v>
+        <v>6806670</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10554,10 +10562,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215776</v>
+        <v>129215818</v>
       </c>
       <c r="B101" t="n">
-        <v>56917</v>
+        <v>58097</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10565,21 +10573,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10587,7 +10595,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10597,10 +10605,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434445</v>
+        <v>434849</v>
       </c>
       <c r="R101" t="n">
-        <v>6806699</v>
+        <v>6806700</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10659,53 +10667,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215777</v>
+        <v>129215759</v>
       </c>
       <c r="B102" t="n">
-        <v>56917</v>
+        <v>79633</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434432</v>
+        <v>434930</v>
       </c>
       <c r="R102" t="n">
-        <v>6806670</v>
+        <v>6806768</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10767,7 +10767,7 @@
         <v>129215873</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>129215884</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>129215825</v>
       </c>
       <c r="B105" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11265,10 +11265,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215849</v>
+        <v>129215794</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11276,34 +11276,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434437</v>
+        <v>434852</v>
       </c>
       <c r="R108" t="n">
-        <v>6806501</v>
+        <v>6806551</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11362,10 +11370,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215848</v>
+        <v>129215849</v>
       </c>
       <c r="B109" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11397,10 +11405,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434473</v>
+        <v>434437</v>
       </c>
       <c r="R109" t="n">
-        <v>6806453</v>
+        <v>6806501</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11459,10 +11467,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215879</v>
+        <v>129215848</v>
       </c>
       <c r="B110" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11494,10 +11502,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434627</v>
+        <v>434473</v>
       </c>
       <c r="R110" t="n">
-        <v>6806787</v>
+        <v>6806453</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11556,10 +11564,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215892</v>
+        <v>129215879</v>
       </c>
       <c r="B111" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11591,10 +11599,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434884</v>
+        <v>434627</v>
       </c>
       <c r="R111" t="n">
-        <v>6806606</v>
+        <v>6806787</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11653,53 +11661,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215765</v>
+        <v>129215892</v>
       </c>
       <c r="B112" t="n">
-        <v>56917</v>
+        <v>79043</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434630</v>
+        <v>434884</v>
       </c>
       <c r="R112" t="n">
-        <v>6806465</v>
+        <v>6806606</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11758,7 +11758,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215769</v>
+        <v>129215765</v>
       </c>
       <c r="B113" t="n">
         <v>56917</v>
@@ -11801,10 +11801,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434382</v>
+        <v>434630</v>
       </c>
       <c r="R113" t="n">
-        <v>6806548</v>
+        <v>6806465</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11863,32 +11863,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215794</v>
+        <v>129215769</v>
       </c>
       <c r="B114" t="n">
-        <v>57887</v>
+        <v>56917</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11896,7 +11896,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -11906,10 +11906,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434852</v>
+        <v>434382</v>
       </c>
       <c r="R114" t="n">
-        <v>6806551</v>
+        <v>6806548</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11968,10 +11968,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215734</v>
+        <v>129215812</v>
       </c>
       <c r="B115" t="n">
-        <v>79660</v>
+        <v>78801</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11979,21 +11979,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434546</v>
+        <v>434922</v>
       </c>
       <c r="R115" t="n">
-        <v>6806737</v>
+        <v>6806746</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215900</v>
+        <v>129215754</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12076,21 +12076,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12100,10 +12100,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434775</v>
+        <v>434774</v>
       </c>
       <c r="R116" t="n">
-        <v>6806423</v>
+        <v>6806803</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12162,10 +12162,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215867</v>
+        <v>129215900</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434375</v>
+        <v>434775</v>
       </c>
       <c r="R117" t="n">
-        <v>6806574</v>
+        <v>6806423</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215844</v>
+        <v>129215867</v>
       </c>
       <c r="B118" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434623</v>
+        <v>434375</v>
       </c>
       <c r="R118" t="n">
-        <v>6806466</v>
+        <v>6806574</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12356,10 +12356,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215868</v>
+        <v>129215734</v>
       </c>
       <c r="B119" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12367,21 +12367,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12391,10 +12391,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434415</v>
+        <v>434546</v>
       </c>
       <c r="R119" t="n">
-        <v>6806576</v>
+        <v>6806737</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12453,10 +12453,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215796</v>
+        <v>129215844</v>
       </c>
       <c r="B120" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12464,42 +12464,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434635</v>
+        <v>434623</v>
       </c>
       <c r="R120" t="n">
-        <v>6806453</v>
+        <v>6806466</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12558,10 +12550,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215797</v>
+        <v>129215868</v>
       </c>
       <c r="B121" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12569,42 +12561,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434602</v>
+        <v>434415</v>
       </c>
       <c r="R121" t="n">
-        <v>6806495</v>
+        <v>6806576</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12663,10 +12647,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215812</v>
+        <v>129215796</v>
       </c>
       <c r="B122" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12674,34 +12658,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434922</v>
+        <v>434635</v>
       </c>
       <c r="R122" t="n">
-        <v>6806746</v>
+        <v>6806453</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12760,10 +12752,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215754</v>
+        <v>129215797</v>
       </c>
       <c r="B123" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12771,34 +12763,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434774</v>
+        <v>434602</v>
       </c>
       <c r="R123" t="n">
-        <v>6806803</v>
+        <v>6806495</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12860,7 +12860,7 @@
         <v>129215852</v>
       </c>
       <c r="B124" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>129215901</v>
       </c>
       <c r="B125" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         <v>129215889</v>
       </c>
       <c r="B126" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13148,10 +13148,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129215871</v>
+        <v>129215745</v>
       </c>
       <c r="B127" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13159,21 +13159,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434443</v>
+        <v>434934</v>
       </c>
       <c r="R127" t="n">
-        <v>6806595</v>
+        <v>6806753</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13245,10 +13245,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129215745</v>
+        <v>129215871</v>
       </c>
       <c r="B128" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13256,21 +13256,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13280,10 +13280,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434934</v>
+        <v>434443</v>
       </c>
       <c r="R128" t="n">
-        <v>6806753</v>
+        <v>6806595</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13345,7 +13345,7 @@
         <v>129215752</v>
       </c>
       <c r="B129" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>129215751</v>
       </c>
       <c r="B130" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY133"/>
+  <dimension ref="A1:AZ133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215903</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215841</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215843</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215845</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215846</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215847</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215848</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215849</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215850</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215851</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215852</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215853</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215854</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215856</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215857</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215858</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215859</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215860</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2621,6 +2721,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215861</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2718,6 +2823,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215862</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2815,6 +2925,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215863</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2912,6 +3027,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215864</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3009,6 +3129,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215865</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3106,6 +3231,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215867</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3203,6 +3333,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215868</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3300,6 +3435,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215869</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3397,6 +3537,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215871</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3498,6 +3643,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215872</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3595,6 +3745,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215873</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3692,6 +3847,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215874</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3789,6 +3949,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215875</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3886,6 +4051,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215876</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3983,6 +4153,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215877</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4084,6 +4259,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215878</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4181,6 +4361,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215879</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4278,6 +4463,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215880</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4379,6 +4569,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215881</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4476,6 +4671,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215882</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4582,6 +4782,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215883</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4679,6 +4884,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215884</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4776,6 +4986,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215885</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4873,6 +5088,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215886</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4970,6 +5190,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215887</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5067,6 +5292,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215888</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5164,6 +5394,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215889</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5261,6 +5496,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215890</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5358,6 +5598,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215891</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5455,6 +5700,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215892</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5552,6 +5802,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215893</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5649,6 +5904,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215895</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5746,6 +6006,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215896</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5843,6 +6108,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215898</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5940,6 +6210,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215899</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6037,6 +6312,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215900</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6134,6 +6414,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215901</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6240,6 +6525,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215902</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6341,6 +6631,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215819</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6438,6 +6733,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215821</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6535,6 +6835,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215822</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6632,6 +6937,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215823</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6729,6 +7039,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215824</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6826,6 +7141,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215825</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6923,6 +7243,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215734</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7020,6 +7345,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215735</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7117,6 +7447,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215736</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7214,6 +7549,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215737</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7311,6 +7651,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215738</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7408,6 +7753,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215739</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7505,6 +7855,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215741</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7606,6 +7961,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215742</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7703,6 +8063,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215743</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7804,6 +8169,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215744</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7901,6 +8271,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215745</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7998,6 +8373,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215749</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8095,6 +8475,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215750</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8192,6 +8577,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215904</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8297,6 +8687,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215795</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8402,6 +8797,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215796</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8507,6 +8907,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215797</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8612,6 +9017,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215798</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8717,6 +9127,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215799</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8822,6 +9237,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215800</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8927,6 +9347,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215801</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9032,6 +9457,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215802</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9137,6 +9567,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215803</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9242,6 +9677,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215804</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9347,6 +9787,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215805</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9452,6 +9897,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215764</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9557,6 +10007,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215765</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9662,6 +10117,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215766</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9767,6 +10227,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215767</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9872,6 +10337,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215768</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9977,6 +10447,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215769</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10082,6 +10557,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215770</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10187,6 +10667,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215771</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10292,6 +10777,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215772</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10397,6 +10887,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215773</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10502,6 +10997,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215774</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10607,6 +11107,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215775</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10712,6 +11217,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215776</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10817,6 +11327,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215777</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10922,6 +11437,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215779</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11027,6 +11547,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215780</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11132,6 +11657,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215781</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11237,6 +11767,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215782</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11342,6 +11877,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215783</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11447,6 +11987,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215784</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11552,6 +12097,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215785</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11657,6 +12207,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215786</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11762,6 +12317,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215787</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11867,6 +12427,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215790</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11972,6 +12537,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215818</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12077,6 +12647,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215793</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12182,6 +12757,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215794</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12284,6 +12864,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215807</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12381,6 +12966,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215808</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12478,6 +13068,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215809</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12575,6 +13170,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215810</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12672,6 +13272,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215812</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12769,6 +13374,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215813</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12866,6 +13476,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215751</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12963,6 +13578,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215752</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13060,6 +13680,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215753</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13157,6 +13782,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215754</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13254,6 +13884,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215755</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13355,6 +13990,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215756</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13452,6 +14092,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215757</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13549,6 +14194,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215758</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13646,6 +14296,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215759</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13743,6 +14398,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215760</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13840,8 +14500,147 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215761</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>